--- a/sql/ShirtReport_20260528.xlsx
+++ b/sql/ShirtReport_20260528.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitProjects\Clothing Order Transfers\sql\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{95D157F0-486F-44A0-9EE2-F0BC1EE1E86D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{90734484-455D-4AA5-BFC8-4D0DF69016D3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="57480" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{C6DD1FE0-0DEB-424C-975A-A7850825C9B9}"/>
+    <workbookView xWindow="57480" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{FEC75489-9D19-4F4A-AB1D-91138E8CC854}"/>
   </bookViews>
   <sheets>
     <sheet name="On Hand" sheetId="1" r:id="rId1"/>
@@ -726,7 +726,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -747,6 +747,7 @@
     <xf numFmtId="164" fontId="1" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="164" fontId="0" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="164" fontId="1" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="164" fontId="1" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="164" fontId="3" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="164" fontId="3" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
@@ -1090,7 +1091,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BB7A5832-232D-4BBB-B7DD-9EC8A609EFBD}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{92106CA9-CACD-4590-81B1-619AC7AFF18D}">
   <dimension ref="A1:Q21"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -1230,9 +1231,13 @@
         <v>14</v>
       </c>
       <c r="C4" s="10"/>
-      <c r="D4" s="9"/>
+      <c r="D4" s="9">
+        <v>-5</v>
+      </c>
       <c r="E4" s="10"/>
-      <c r="F4" s="9"/>
+      <c r="F4" s="9">
+        <v>-5</v>
+      </c>
       <c r="G4" s="10"/>
       <c r="H4" s="9">
         <v>15</v>
@@ -1268,7 +1273,9 @@
       <c r="F5" s="12">
         <v>3</v>
       </c>
-      <c r="G5" s="10"/>
+      <c r="G5" s="10">
+        <v>3</v>
+      </c>
       <c r="H5" s="12"/>
       <c r="I5" s="10"/>
       <c r="J5" s="12"/>
@@ -1280,7 +1287,9 @@
       <c r="P5" s="13">
         <v>5</v>
       </c>
-      <c r="Q5" s="10"/>
+      <c r="Q5" s="14">
+        <v>3</v>
+      </c>
     </row>
     <row r="6" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A6" s="7" t="s">
@@ -1299,7 +1308,9 @@
       <c r="J6" s="9">
         <v>2</v>
       </c>
-      <c r="K6" s="10"/>
+      <c r="K6" s="10">
+        <v>2</v>
+      </c>
       <c r="L6" s="9"/>
       <c r="M6" s="10"/>
       <c r="N6" s="9">
@@ -1309,7 +1320,9 @@
       <c r="P6" s="11">
         <v>6</v>
       </c>
-      <c r="Q6" s="10"/>
+      <c r="Q6" s="14">
+        <v>2</v>
+      </c>
     </row>
     <row r="7" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A7" s="8" t="s">
@@ -1320,27 +1333,37 @@
       <c r="D7" s="12">
         <v>2</v>
       </c>
-      <c r="E7" s="10"/>
+      <c r="E7" s="10">
+        <v>2</v>
+      </c>
       <c r="F7" s="12">
         <v>2</v>
       </c>
-      <c r="G7" s="10"/>
+      <c r="G7" s="10">
+        <v>2</v>
+      </c>
       <c r="H7" s="12"/>
       <c r="I7" s="10"/>
       <c r="J7" s="12">
         <v>1</v>
       </c>
-      <c r="K7" s="10"/>
+      <c r="K7" s="10">
+        <v>1</v>
+      </c>
       <c r="L7" s="12"/>
       <c r="M7" s="10"/>
       <c r="N7" s="12">
         <v>1</v>
       </c>
-      <c r="O7" s="10"/>
+      <c r="O7" s="10">
+        <v>1</v>
+      </c>
       <c r="P7" s="13">
         <v>6</v>
       </c>
-      <c r="Q7" s="10"/>
+      <c r="Q7" s="14">
+        <v>6</v>
+      </c>
     </row>
     <row r="8" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A8" s="7" t="s">
@@ -1351,11 +1374,15 @@
       <c r="D8" s="9">
         <v>1</v>
       </c>
-      <c r="E8" s="10"/>
+      <c r="E8" s="10">
+        <v>1</v>
+      </c>
       <c r="F8" s="9">
         <v>1</v>
       </c>
-      <c r="G8" s="10"/>
+      <c r="G8" s="10">
+        <v>1</v>
+      </c>
       <c r="H8" s="9"/>
       <c r="I8" s="10"/>
       <c r="J8" s="9"/>
@@ -1367,7 +1394,9 @@
       <c r="P8" s="11">
         <v>2</v>
       </c>
-      <c r="Q8" s="10"/>
+      <c r="Q8" s="14">
+        <v>2</v>
+      </c>
     </row>
     <row r="9" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A9" s="8" t="s">
@@ -1382,19 +1411,27 @@
       <c r="H9" s="12">
         <v>3</v>
       </c>
-      <c r="I9" s="10"/>
-      <c r="J9" s="12"/>
+      <c r="I9" s="10">
+        <v>2</v>
+      </c>
+      <c r="J9" s="12">
+        <v>-5</v>
+      </c>
       <c r="K9" s="10"/>
       <c r="L9" s="12"/>
       <c r="M9" s="10"/>
       <c r="N9" s="12">
         <v>6</v>
       </c>
-      <c r="O9" s="10"/>
+      <c r="O9" s="10">
+        <v>6</v>
+      </c>
       <c r="P9" s="13">
         <v>4</v>
       </c>
-      <c r="Q9" s="10"/>
+      <c r="Q9" s="14">
+        <v>8</v>
+      </c>
     </row>
     <row r="10" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A10" s="7" t="s">
@@ -1402,12 +1439,16 @@
       </c>
       <c r="B10" s="9"/>
       <c r="C10" s="10"/>
-      <c r="D10" s="9"/>
+      <c r="D10" s="9">
+        <v>-1</v>
+      </c>
       <c r="E10" s="10"/>
       <c r="F10" s="9">
         <v>6</v>
       </c>
-      <c r="G10" s="10"/>
+      <c r="G10" s="10">
+        <v>6</v>
+      </c>
       <c r="H10" s="9"/>
       <c r="I10" s="10"/>
       <c r="J10" s="9"/>
@@ -1419,7 +1460,9 @@
       <c r="P10" s="11">
         <v>5</v>
       </c>
-      <c r="Q10" s="10"/>
+      <c r="Q10" s="14">
+        <v>6</v>
+      </c>
     </row>
     <row r="11" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A11" s="8" t="s">
@@ -1438,13 +1481,17 @@
       <c r="L11" s="12">
         <v>1</v>
       </c>
-      <c r="M11" s="10"/>
+      <c r="M11" s="10">
+        <v>1</v>
+      </c>
       <c r="N11" s="12"/>
       <c r="O11" s="10"/>
       <c r="P11" s="13">
         <v>1</v>
       </c>
-      <c r="Q11" s="10"/>
+      <c r="Q11" s="14">
+        <v>1</v>
+      </c>
     </row>
     <row r="12" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A12" s="7" t="s">
@@ -1455,7 +1502,9 @@
       <c r="D12" s="9">
         <v>1</v>
       </c>
-      <c r="E12" s="10"/>
+      <c r="E12" s="10">
+        <v>1</v>
+      </c>
       <c r="F12" s="9"/>
       <c r="G12" s="10"/>
       <c r="H12" s="9"/>
@@ -1469,7 +1518,9 @@
       <c r="P12" s="11">
         <v>1</v>
       </c>
-      <c r="Q12" s="10"/>
+      <c r="Q12" s="14">
+        <v>1</v>
+      </c>
     </row>
     <row r="13" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A13" s="8" t="s">
@@ -1482,7 +1533,9 @@
       <c r="F13" s="12">
         <v>1</v>
       </c>
-      <c r="G13" s="10"/>
+      <c r="G13" s="10">
+        <v>1</v>
+      </c>
       <c r="H13" s="12"/>
       <c r="I13" s="10"/>
       <c r="J13" s="12"/>
@@ -1494,7 +1547,9 @@
       <c r="P13" s="13">
         <v>1</v>
       </c>
-      <c r="Q13" s="10"/>
+      <c r="Q13" s="14">
+        <v>1</v>
+      </c>
     </row>
     <row r="14" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A14" s="7" t="s">
@@ -1503,21 +1558,29 @@
       <c r="B14" s="9">
         <v>2</v>
       </c>
-      <c r="C14" s="10"/>
+      <c r="C14" s="10">
+        <v>2</v>
+      </c>
       <c r="D14" s="9"/>
       <c r="E14" s="10"/>
       <c r="F14" s="9">
         <v>2</v>
       </c>
-      <c r="G14" s="10"/>
+      <c r="G14" s="10">
+        <v>2</v>
+      </c>
       <c r="H14" s="9">
         <v>1</v>
       </c>
-      <c r="I14" s="10"/>
+      <c r="I14" s="10">
+        <v>1</v>
+      </c>
       <c r="J14" s="9">
         <v>3</v>
       </c>
-      <c r="K14" s="10"/>
+      <c r="K14" s="10">
+        <v>3</v>
+      </c>
       <c r="L14" s="9"/>
       <c r="M14" s="10"/>
       <c r="N14" s="9"/>
@@ -1525,7 +1588,9 @@
       <c r="P14" s="11">
         <v>8</v>
       </c>
-      <c r="Q14" s="10"/>
+      <c r="Q14" s="14">
+        <v>8</v>
+      </c>
     </row>
     <row r="15" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A15" s="8" t="s">
@@ -1548,11 +1613,15 @@
       <c r="N15" s="12">
         <v>4</v>
       </c>
-      <c r="O15" s="10"/>
+      <c r="O15" s="10">
+        <v>4</v>
+      </c>
       <c r="P15" s="13">
         <v>6</v>
       </c>
-      <c r="Q15" s="10"/>
+      <c r="Q15" s="14">
+        <v>4</v>
+      </c>
     </row>
     <row r="16" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A16" s="7" t="s">
@@ -1560,7 +1629,9 @@
       </c>
       <c r="B16" s="9"/>
       <c r="C16" s="10"/>
-      <c r="D16" s="9"/>
+      <c r="D16" s="9">
+        <v>-1</v>
+      </c>
       <c r="E16" s="10"/>
       <c r="F16" s="9">
         <v>1</v>
@@ -1573,11 +1644,15 @@
       <c r="L16" s="9"/>
       <c r="M16" s="10"/>
       <c r="N16" s="9"/>
-      <c r="O16" s="10"/>
+      <c r="O16" s="10">
+        <v>2</v>
+      </c>
       <c r="P16" s="11">
         <v>0</v>
       </c>
-      <c r="Q16" s="10"/>
+      <c r="Q16" s="14">
+        <v>2</v>
+      </c>
     </row>
     <row r="17" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A17" s="8" t="s">
@@ -1615,7 +1690,9 @@
       <c r="F18" s="9">
         <v>1</v>
       </c>
-      <c r="G18" s="10"/>
+      <c r="G18" s="10">
+        <v>1</v>
+      </c>
       <c r="H18" s="9"/>
       <c r="I18" s="10"/>
       <c r="J18" s="9"/>
@@ -1627,7 +1704,9 @@
       <c r="P18" s="11">
         <v>1</v>
       </c>
-      <c r="Q18" s="10"/>
+      <c r="Q18" s="14">
+        <v>1</v>
+      </c>
     </row>
     <row r="19" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A19" s="8" t="s">
@@ -1640,7 +1719,9 @@
       <c r="F19" s="12">
         <v>1</v>
       </c>
-      <c r="G19" s="10"/>
+      <c r="G19" s="10">
+        <v>1</v>
+      </c>
       <c r="H19" s="12"/>
       <c r="I19" s="10"/>
       <c r="J19" s="12"/>
@@ -1652,7 +1733,9 @@
       <c r="P19" s="13">
         <v>1</v>
       </c>
-      <c r="Q19" s="10"/>
+      <c r="Q19" s="14">
+        <v>1</v>
+      </c>
     </row>
     <row r="20" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A20" s="7" t="s">
@@ -1662,7 +1745,9 @@
       <c r="C20" s="10"/>
       <c r="D20" s="9"/>
       <c r="E20" s="10"/>
-      <c r="F20" s="9"/>
+      <c r="F20" s="9">
+        <v>-1</v>
+      </c>
       <c r="G20" s="10"/>
       <c r="H20" s="9"/>
       <c r="I20" s="10"/>
@@ -1673,46 +1758,68 @@
       <c r="N20" s="9">
         <v>1</v>
       </c>
-      <c r="O20" s="10"/>
+      <c r="O20" s="10">
+        <v>1</v>
+      </c>
       <c r="P20" s="11">
         <v>0</v>
       </c>
-      <c r="Q20" s="10"/>
+      <c r="Q20" s="14">
+        <v>1</v>
+      </c>
     </row>
     <row r="21" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A21" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="B21" s="14">
+      <c r="B21" s="15">
         <v>18</v>
       </c>
-      <c r="C21" s="15"/>
-      <c r="D21" s="14"/>
-      <c r="E21" s="15"/>
-      <c r="F21" s="14">
+      <c r="C21" s="16">
+        <v>2</v>
+      </c>
+      <c r="D21" s="15">
+        <v>-1</v>
+      </c>
+      <c r="E21" s="16">
+        <v>4</v>
+      </c>
+      <c r="F21" s="15">
         <v>14</v>
       </c>
-      <c r="G21" s="15"/>
-      <c r="H21" s="14">
+      <c r="G21" s="16">
+        <v>17</v>
+      </c>
+      <c r="H21" s="15">
         <v>19</v>
       </c>
-      <c r="I21" s="15"/>
-      <c r="J21" s="14">
+      <c r="I21" s="16">
+        <v>3</v>
+      </c>
+      <c r="J21" s="15">
         <v>6</v>
       </c>
-      <c r="K21" s="15"/>
-      <c r="L21" s="14">
+      <c r="K21" s="16">
+        <v>6</v>
+      </c>
+      <c r="L21" s="15">
         <v>22</v>
       </c>
-      <c r="M21" s="15"/>
-      <c r="N21" s="14">
+      <c r="M21" s="16">
+        <v>1</v>
+      </c>
+      <c r="N21" s="15">
         <v>19</v>
       </c>
-      <c r="O21" s="15"/>
-      <c r="P21" s="14">
+      <c r="O21" s="16">
+        <v>14</v>
+      </c>
+      <c r="P21" s="15">
         <v>97</v>
       </c>
-      <c r="Q21" s="15"/>
+      <c r="Q21" s="16">
+        <v>47</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="9">
@@ -1731,7 +1838,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AF367798-70D1-494F-8FF3-942E2AC61089}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F4A16563-D352-40CE-8BA8-00122A0B69EF}">
   <dimension ref="A1:J280"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -1792,18 +1899,18 @@
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A3" s="16" t="s">
+      <c r="A3" s="17" t="s">
         <v>15</v>
       </c>
-      <c r="B3" s="16"/>
-      <c r="C3" s="16"/>
-      <c r="D3" s="16"/>
-      <c r="E3" s="16"/>
-      <c r="F3" s="16"/>
-      <c r="G3" s="16"/>
-      <c r="H3" s="16"/>
-      <c r="I3" s="16"/>
-      <c r="J3" s="16"/>
+      <c r="B3" s="17"/>
+      <c r="C3" s="17"/>
+      <c r="D3" s="17"/>
+      <c r="E3" s="17"/>
+      <c r="F3" s="17"/>
+      <c r="G3" s="17"/>
+      <c r="H3" s="17"/>
+      <c r="I3" s="17"/>
+      <c r="J3" s="17"/>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4" s="7" t="s">
@@ -1815,7 +1922,7 @@
       <c r="C4" s="7">
         <v>9991003</v>
       </c>
-      <c r="D4" s="17">
+      <c r="D4" s="18">
         <v>46147</v>
       </c>
       <c r="E4" s="7">
@@ -1872,44 +1979,44 @@
       <c r="J6" s="7"/>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A7" s="18" t="s">
+      <c r="A7" s="19" t="s">
         <v>45</v>
       </c>
-      <c r="B7" s="18" t="s">
-        <v>4</v>
-      </c>
-      <c r="C7" s="18">
+      <c r="B7" s="19" t="s">
+        <v>4</v>
+      </c>
+      <c r="C7" s="19">
         <v>9991003</v>
       </c>
-      <c r="D7" s="18"/>
-      <c r="E7" s="18">
-        <v>3</v>
-      </c>
-      <c r="F7" s="18"/>
-      <c r="G7" s="18"/>
-      <c r="H7" s="18">
+      <c r="D7" s="19"/>
+      <c r="E7" s="19">
+        <v>3</v>
+      </c>
+      <c r="F7" s="19"/>
+      <c r="G7" s="19"/>
+      <c r="H7" s="19">
         <v>0</v>
       </c>
-      <c r="I7" s="18">
-        <v>3</v>
-      </c>
-      <c r="J7" s="18">
+      <c r="I7" s="19">
+        <v>3</v>
+      </c>
+      <c r="J7" s="19">
         <v>3</v>
       </c>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A9" s="16" t="s">
+      <c r="A9" s="17" t="s">
         <v>16</v>
       </c>
-      <c r="B9" s="16"/>
-      <c r="C9" s="16"/>
-      <c r="D9" s="16"/>
-      <c r="E9" s="16"/>
-      <c r="F9" s="16"/>
-      <c r="G9" s="16"/>
-      <c r="H9" s="16"/>
-      <c r="I9" s="16"/>
-      <c r="J9" s="16"/>
+      <c r="B9" s="17"/>
+      <c r="C9" s="17"/>
+      <c r="D9" s="17"/>
+      <c r="E9" s="17"/>
+      <c r="F9" s="17"/>
+      <c r="G9" s="17"/>
+      <c r="H9" s="17"/>
+      <c r="I9" s="17"/>
+      <c r="J9" s="17"/>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A10" s="7" t="s">
@@ -1921,7 +2028,7 @@
       <c r="C10" s="7">
         <v>9991001</v>
       </c>
-      <c r="D10" s="17">
+      <c r="D10" s="18">
         <v>46176</v>
       </c>
       <c r="E10" s="7">
@@ -1934,52 +2041,52 @@
       <c r="J10" s="7"/>
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A11" s="20" t="s">
+      <c r="A11" s="21" t="s">
         <v>47</v>
       </c>
-      <c r="B11" s="19" t="s">
-        <v>2</v>
-      </c>
-      <c r="C11" s="19">
+      <c r="B11" s="20" t="s">
+        <v>2</v>
+      </c>
+      <c r="C11" s="20">
         <v>9991001</v>
       </c>
-      <c r="D11" s="19"/>
-      <c r="E11" s="19"/>
-      <c r="F11" s="19">
+      <c r="D11" s="20"/>
+      <c r="E11" s="20"/>
+      <c r="F11" s="20">
         <v>1411116</v>
       </c>
-      <c r="G11" s="19" t="s">
+      <c r="G11" s="20" t="s">
         <v>48</v>
       </c>
-      <c r="H11" s="19">
-        <v>1</v>
-      </c>
-      <c r="I11" s="19"/>
-      <c r="J11" s="19"/>
+      <c r="H11" s="20">
+        <v>1</v>
+      </c>
+      <c r="I11" s="20"/>
+      <c r="J11" s="20"/>
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A12" s="21" t="s">
+      <c r="A12" s="22" t="s">
         <v>45</v>
       </c>
-      <c r="B12" s="21" t="s">
-        <v>2</v>
-      </c>
-      <c r="C12" s="21">
+      <c r="B12" s="22" t="s">
+        <v>2</v>
+      </c>
+      <c r="C12" s="22">
         <v>9991001</v>
       </c>
-      <c r="D12" s="21"/>
-      <c r="E12" s="21">
-        <v>1</v>
-      </c>
-      <c r="F12" s="21"/>
-      <c r="G12" s="21"/>
-      <c r="H12" s="21">
-        <v>1</v>
-      </c>
-      <c r="I12" s="21">
+      <c r="D12" s="22"/>
+      <c r="E12" s="22">
+        <v>1</v>
+      </c>
+      <c r="F12" s="22"/>
+      <c r="G12" s="22"/>
+      <c r="H12" s="22">
+        <v>1</v>
+      </c>
+      <c r="I12" s="22">
         <v>0</v>
       </c>
-      <c r="J12" s="21"/>
+      <c r="J12" s="22"/>
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A13" s="7" t="s">
@@ -2004,52 +2111,52 @@
       <c r="J13" s="7"/>
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A14" s="20" t="s">
+      <c r="A14" s="21" t="s">
         <v>47</v>
       </c>
-      <c r="B14" s="19" t="s">
-        <v>3</v>
-      </c>
-      <c r="C14" s="19">
+      <c r="B14" s="20" t="s">
+        <v>3</v>
+      </c>
+      <c r="C14" s="20">
         <v>9991002</v>
       </c>
-      <c r="D14" s="19"/>
-      <c r="E14" s="19"/>
-      <c r="F14" s="19">
+      <c r="D14" s="20"/>
+      <c r="E14" s="20"/>
+      <c r="F14" s="20">
         <v>1411287</v>
       </c>
-      <c r="G14" s="22">
+      <c r="G14" s="23">
         <v>46361</v>
       </c>
-      <c r="H14" s="19">
-        <v>1</v>
-      </c>
-      <c r="I14" s="19"/>
-      <c r="J14" s="19"/>
+      <c r="H14" s="20">
+        <v>1</v>
+      </c>
+      <c r="I14" s="20"/>
+      <c r="J14" s="20"/>
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A15" s="21" t="s">
+      <c r="A15" s="22" t="s">
         <v>45</v>
       </c>
-      <c r="B15" s="21" t="s">
-        <v>3</v>
-      </c>
-      <c r="C15" s="21">
+      <c r="B15" s="22" t="s">
+        <v>3</v>
+      </c>
+      <c r="C15" s="22">
         <v>9991002</v>
       </c>
-      <c r="D15" s="21"/>
-      <c r="E15" s="21">
-        <v>1</v>
-      </c>
-      <c r="F15" s="21"/>
-      <c r="G15" s="21"/>
-      <c r="H15" s="21">
-        <v>1</v>
-      </c>
-      <c r="I15" s="21">
+      <c r="D15" s="22"/>
+      <c r="E15" s="22">
+        <v>1</v>
+      </c>
+      <c r="F15" s="22"/>
+      <c r="G15" s="22"/>
+      <c r="H15" s="22">
+        <v>1</v>
+      </c>
+      <c r="I15" s="22">
         <v>0</v>
       </c>
-      <c r="J15" s="21"/>
+      <c r="J15" s="22"/>
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A16" s="7" t="s">
@@ -2061,7 +2168,7 @@
       <c r="C16" s="7">
         <v>9991003</v>
       </c>
-      <c r="D16" s="17">
+      <c r="D16" s="18">
         <v>46176</v>
       </c>
       <c r="E16" s="7">
@@ -2083,7 +2190,7 @@
       <c r="C17" s="8">
         <v>9991003</v>
       </c>
-      <c r="D17" s="23">
+      <c r="D17" s="24">
         <v>46176</v>
       </c>
       <c r="E17" s="8">
@@ -2105,7 +2212,7 @@
       <c r="C18" s="7">
         <v>9991003</v>
       </c>
-      <c r="D18" s="17">
+      <c r="D18" s="18">
         <v>46176</v>
       </c>
       <c r="E18" s="7">
@@ -2118,100 +2225,100 @@
       <c r="J18" s="7"/>
     </row>
     <row r="19" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A19" s="20" t="s">
+      <c r="A19" s="21" t="s">
         <v>47</v>
       </c>
-      <c r="B19" s="19" t="s">
-        <v>4</v>
-      </c>
-      <c r="C19" s="19">
+      <c r="B19" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="C19" s="20">
         <v>9991003</v>
       </c>
-      <c r="D19" s="19"/>
-      <c r="E19" s="19"/>
-      <c r="F19" s="19">
+      <c r="D19" s="20"/>
+      <c r="E19" s="20"/>
+      <c r="F19" s="20">
         <v>1411107</v>
       </c>
-      <c r="G19" s="22">
+      <c r="G19" s="23">
         <v>46329</v>
       </c>
-      <c r="H19" s="19">
-        <v>3</v>
-      </c>
-      <c r="I19" s="19"/>
-      <c r="J19" s="19"/>
+      <c r="H19" s="20">
+        <v>3</v>
+      </c>
+      <c r="I19" s="20"/>
+      <c r="J19" s="20"/>
     </row>
     <row r="20" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A20" s="20" t="s">
+      <c r="A20" s="21" t="s">
         <v>47</v>
       </c>
-      <c r="B20" s="19" t="s">
-        <v>4</v>
-      </c>
-      <c r="C20" s="19">
+      <c r="B20" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="C20" s="20">
         <v>9991003</v>
       </c>
-      <c r="D20" s="19"/>
-      <c r="E20" s="19"/>
-      <c r="F20" s="19">
+      <c r="D20" s="20"/>
+      <c r="E20" s="20"/>
+      <c r="F20" s="20">
         <v>1411113</v>
       </c>
-      <c r="G20" s="19" t="s">
+      <c r="G20" s="20" t="s">
         <v>54</v>
       </c>
-      <c r="H20" s="19">
-        <v>2</v>
-      </c>
-      <c r="I20" s="19"/>
-      <c r="J20" s="19"/>
+      <c r="H20" s="20">
+        <v>2</v>
+      </c>
+      <c r="I20" s="20"/>
+      <c r="J20" s="20"/>
     </row>
     <row r="21" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A21" s="20" t="s">
+      <c r="A21" s="21" t="s">
         <v>47</v>
       </c>
-      <c r="B21" s="19" t="s">
-        <v>4</v>
-      </c>
-      <c r="C21" s="19">
+      <c r="B21" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="C21" s="20">
         <v>9991003</v>
       </c>
-      <c r="D21" s="19"/>
-      <c r="E21" s="19"/>
-      <c r="F21" s="19">
+      <c r="D21" s="20"/>
+      <c r="E21" s="20"/>
+      <c r="F21" s="20">
         <v>1411128</v>
       </c>
-      <c r="G21" s="19" t="s">
+      <c r="G21" s="20" t="s">
         <v>55</v>
       </c>
-      <c r="H21" s="19">
-        <v>2</v>
-      </c>
-      <c r="I21" s="19"/>
-      <c r="J21" s="19"/>
+      <c r="H21" s="20">
+        <v>2</v>
+      </c>
+      <c r="I21" s="20"/>
+      <c r="J21" s="20"/>
     </row>
     <row r="22" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A22" s="21" t="s">
+      <c r="A22" s="22" t="s">
         <v>45</v>
       </c>
-      <c r="B22" s="21" t="s">
-        <v>4</v>
-      </c>
-      <c r="C22" s="21">
+      <c r="B22" s="22" t="s">
+        <v>4</v>
+      </c>
+      <c r="C22" s="22">
         <v>9991003</v>
       </c>
-      <c r="D22" s="21"/>
-      <c r="E22" s="21">
+      <c r="D22" s="22"/>
+      <c r="E22" s="22">
         <v>7</v>
       </c>
-      <c r="F22" s="21"/>
-      <c r="G22" s="21"/>
-      <c r="H22" s="21">
+      <c r="F22" s="22"/>
+      <c r="G22" s="22"/>
+      <c r="H22" s="22">
         <v>7</v>
       </c>
-      <c r="I22" s="21">
+      <c r="I22" s="22">
         <v>0</v>
       </c>
-      <c r="J22" s="21">
+      <c r="J22" s="22">
         <v>2</v>
       </c>
     </row>
@@ -2282,100 +2389,100 @@
       <c r="J25" s="7"/>
     </row>
     <row r="26" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A26" s="20" t="s">
+      <c r="A26" s="21" t="s">
         <v>47</v>
       </c>
-      <c r="B26" s="19" t="s">
+      <c r="B26" s="20" t="s">
         <v>5</v>
       </c>
-      <c r="C26" s="19">
+      <c r="C26" s="20">
         <v>9991004</v>
       </c>
-      <c r="D26" s="19"/>
-      <c r="E26" s="19"/>
-      <c r="F26" s="19">
+      <c r="D26" s="20"/>
+      <c r="E26" s="20"/>
+      <c r="F26" s="20">
         <v>1410984</v>
       </c>
-      <c r="G26" s="19" t="s">
+      <c r="G26" s="20" t="s">
         <v>61</v>
       </c>
-      <c r="H26" s="19">
-        <v>2</v>
-      </c>
-      <c r="I26" s="19"/>
-      <c r="J26" s="19"/>
+      <c r="H26" s="20">
+        <v>2</v>
+      </c>
+      <c r="I26" s="20"/>
+      <c r="J26" s="20"/>
     </row>
     <row r="27" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A27" s="20" t="s">
+      <c r="A27" s="21" t="s">
         <v>47</v>
       </c>
-      <c r="B27" s="19" t="s">
+      <c r="B27" s="20" t="s">
         <v>5</v>
       </c>
-      <c r="C27" s="19">
+      <c r="C27" s="20">
         <v>9991004</v>
       </c>
-      <c r="D27" s="19"/>
-      <c r="E27" s="19"/>
-      <c r="F27" s="19">
+      <c r="D27" s="20"/>
+      <c r="E27" s="20"/>
+      <c r="F27" s="20">
         <v>1411173</v>
       </c>
-      <c r="G27" s="22">
+      <c r="G27" s="23">
         <v>46057</v>
       </c>
-      <c r="H27" s="19">
-        <v>1</v>
-      </c>
-      <c r="I27" s="19"/>
-      <c r="J27" s="19"/>
+      <c r="H27" s="20">
+        <v>1</v>
+      </c>
+      <c r="I27" s="20"/>
+      <c r="J27" s="20"/>
     </row>
     <row r="28" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A28" s="20" t="s">
+      <c r="A28" s="21" t="s">
         <v>47</v>
       </c>
-      <c r="B28" s="19" t="s">
+      <c r="B28" s="20" t="s">
         <v>5</v>
       </c>
-      <c r="C28" s="19">
+      <c r="C28" s="20">
         <v>9991004</v>
       </c>
-      <c r="D28" s="19"/>
-      <c r="E28" s="19"/>
-      <c r="F28" s="19">
+      <c r="D28" s="20"/>
+      <c r="E28" s="20"/>
+      <c r="F28" s="20">
         <v>1411251</v>
       </c>
-      <c r="G28" s="19" t="s">
+      <c r="G28" s="20" t="s">
         <v>50</v>
       </c>
-      <c r="H28" s="19">
-        <v>2</v>
-      </c>
-      <c r="I28" s="19"/>
-      <c r="J28" s="19"/>
+      <c r="H28" s="20">
+        <v>2</v>
+      </c>
+      <c r="I28" s="20"/>
+      <c r="J28" s="20"/>
     </row>
     <row r="29" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A29" s="21" t="s">
+      <c r="A29" s="22" t="s">
         <v>45</v>
       </c>
-      <c r="B29" s="21" t="s">
+      <c r="B29" s="22" t="s">
         <v>5</v>
       </c>
-      <c r="C29" s="21">
+      <c r="C29" s="22">
         <v>9991004</v>
       </c>
-      <c r="D29" s="21"/>
-      <c r="E29" s="21">
+      <c r="D29" s="22"/>
+      <c r="E29" s="22">
         <v>5</v>
       </c>
-      <c r="F29" s="21"/>
-      <c r="G29" s="21"/>
-      <c r="H29" s="21">
+      <c r="F29" s="22"/>
+      <c r="G29" s="22"/>
+      <c r="H29" s="22">
         <v>5</v>
       </c>
-      <c r="I29" s="21">
+      <c r="I29" s="22">
         <v>0</v>
       </c>
-      <c r="J29" s="21"/>
+      <c r="J29" s="22"/>
     </row>
     <row r="30" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A30" s="7" t="s">
@@ -2400,44 +2507,44 @@
       <c r="J30" s="7"/>
     </row>
     <row r="31" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A31" s="18" t="s">
+      <c r="A31" s="19" t="s">
         <v>45</v>
       </c>
-      <c r="B31" s="18" t="s">
+      <c r="B31" s="19" t="s">
         <v>6</v>
       </c>
-      <c r="C31" s="18">
+      <c r="C31" s="19">
         <v>9991005</v>
       </c>
-      <c r="D31" s="18"/>
-      <c r="E31" s="18">
-        <v>2</v>
-      </c>
-      <c r="F31" s="18"/>
-      <c r="G31" s="18"/>
-      <c r="H31" s="18">
+      <c r="D31" s="19"/>
+      <c r="E31" s="19">
+        <v>2</v>
+      </c>
+      <c r="F31" s="19"/>
+      <c r="G31" s="19"/>
+      <c r="H31" s="19">
         <v>0</v>
       </c>
-      <c r="I31" s="18">
-        <v>2</v>
-      </c>
-      <c r="J31" s="18">
+      <c r="I31" s="19">
+        <v>2</v>
+      </c>
+      <c r="J31" s="19">
         <v>2</v>
       </c>
     </row>
     <row r="33" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A33" s="16" t="s">
+      <c r="A33" s="17" t="s">
         <v>17</v>
       </c>
-      <c r="B33" s="16"/>
-      <c r="C33" s="16"/>
-      <c r="D33" s="16"/>
-      <c r="E33" s="16"/>
-      <c r="F33" s="16"/>
-      <c r="G33" s="16"/>
-      <c r="H33" s="16"/>
-      <c r="I33" s="16"/>
-      <c r="J33" s="16"/>
+      <c r="B33" s="17"/>
+      <c r="C33" s="17"/>
+      <c r="D33" s="17"/>
+      <c r="E33" s="17"/>
+      <c r="F33" s="17"/>
+      <c r="G33" s="17"/>
+      <c r="H33" s="17"/>
+      <c r="I33" s="17"/>
+      <c r="J33" s="17"/>
     </row>
     <row r="34" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A34" s="7" t="s">
@@ -2462,28 +2569,28 @@
       <c r="J34" s="7"/>
     </row>
     <row r="35" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A35" s="18" t="s">
+      <c r="A35" s="19" t="s">
         <v>45</v>
       </c>
-      <c r="B35" s="18" t="s">
-        <v>3</v>
-      </c>
-      <c r="C35" s="18">
+      <c r="B35" s="19" t="s">
+        <v>3</v>
+      </c>
+      <c r="C35" s="19">
         <v>9991002</v>
       </c>
-      <c r="D35" s="18"/>
-      <c r="E35" s="18">
-        <v>2</v>
-      </c>
-      <c r="F35" s="18"/>
-      <c r="G35" s="18"/>
-      <c r="H35" s="18">
+      <c r="D35" s="19"/>
+      <c r="E35" s="19">
+        <v>2</v>
+      </c>
+      <c r="F35" s="19"/>
+      <c r="G35" s="19"/>
+      <c r="H35" s="19">
         <v>0</v>
       </c>
-      <c r="I35" s="18">
-        <v>2</v>
-      </c>
-      <c r="J35" s="18">
+      <c r="I35" s="19">
+        <v>2</v>
+      </c>
+      <c r="J35" s="19">
         <v>2</v>
       </c>
     </row>
@@ -2532,52 +2639,52 @@
       <c r="J37" s="8"/>
     </row>
     <row r="38" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A38" s="20" t="s">
+      <c r="A38" s="21" t="s">
         <v>47</v>
       </c>
-      <c r="B38" s="19" t="s">
-        <v>4</v>
-      </c>
-      <c r="C38" s="19">
+      <c r="B38" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="C38" s="20">
         <v>9991003</v>
       </c>
-      <c r="D38" s="19"/>
-      <c r="E38" s="19"/>
-      <c r="F38" s="19">
+      <c r="D38" s="20"/>
+      <c r="E38" s="20"/>
+      <c r="F38" s="20">
         <v>17012815</v>
       </c>
-      <c r="G38" s="22">
+      <c r="G38" s="23">
         <v>46144</v>
       </c>
-      <c r="H38" s="19">
-        <v>2</v>
-      </c>
-      <c r="I38" s="19"/>
-      <c r="J38" s="19"/>
+      <c r="H38" s="20">
+        <v>2</v>
+      </c>
+      <c r="I38" s="20"/>
+      <c r="J38" s="20"/>
     </row>
     <row r="39" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A39" s="18" t="s">
+      <c r="A39" s="19" t="s">
         <v>45</v>
       </c>
-      <c r="B39" s="18" t="s">
-        <v>4</v>
-      </c>
-      <c r="C39" s="18">
+      <c r="B39" s="19" t="s">
+        <v>4</v>
+      </c>
+      <c r="C39" s="19">
         <v>9991003</v>
       </c>
-      <c r="D39" s="18"/>
-      <c r="E39" s="18">
-        <v>4</v>
-      </c>
-      <c r="F39" s="18"/>
-      <c r="G39" s="18"/>
-      <c r="H39" s="18">
-        <v>2</v>
-      </c>
-      <c r="I39" s="18">
-        <v>2</v>
-      </c>
-      <c r="J39" s="18">
+      <c r="D39" s="19"/>
+      <c r="E39" s="19">
+        <v>4</v>
+      </c>
+      <c r="F39" s="19"/>
+      <c r="G39" s="19"/>
+      <c r="H39" s="19">
+        <v>2</v>
+      </c>
+      <c r="I39" s="19">
+        <v>2</v>
+      </c>
+      <c r="J39" s="19">
         <v>2</v>
       </c>
     </row>
@@ -2604,52 +2711,52 @@
       <c r="J40" s="7"/>
     </row>
     <row r="41" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A41" s="20" t="s">
+      <c r="A41" s="21" t="s">
         <v>47</v>
       </c>
-      <c r="B41" s="19" t="s">
+      <c r="B41" s="20" t="s">
         <v>5</v>
       </c>
-      <c r="C41" s="19">
+      <c r="C41" s="20">
         <v>9991004</v>
       </c>
-      <c r="D41" s="19"/>
-      <c r="E41" s="19"/>
-      <c r="F41" s="19">
+      <c r="D41" s="20"/>
+      <c r="E41" s="20"/>
+      <c r="F41" s="20">
         <v>17012815</v>
       </c>
-      <c r="G41" s="22">
+      <c r="G41" s="23">
         <v>46144</v>
       </c>
-      <c r="H41" s="19">
-        <v>2</v>
-      </c>
-      <c r="I41" s="19"/>
-      <c r="J41" s="19"/>
+      <c r="H41" s="20">
+        <v>2</v>
+      </c>
+      <c r="I41" s="20"/>
+      <c r="J41" s="20"/>
     </row>
     <row r="42" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A42" s="21" t="s">
+      <c r="A42" s="22" t="s">
         <v>45</v>
       </c>
-      <c r="B42" s="21" t="s">
+      <c r="B42" s="22" t="s">
         <v>5</v>
       </c>
-      <c r="C42" s="21">
+      <c r="C42" s="22">
         <v>9991004</v>
       </c>
-      <c r="D42" s="21"/>
-      <c r="E42" s="21">
-        <v>2</v>
-      </c>
-      <c r="F42" s="21"/>
-      <c r="G42" s="21"/>
-      <c r="H42" s="21">
-        <v>2</v>
-      </c>
-      <c r="I42" s="21">
+      <c r="D42" s="22"/>
+      <c r="E42" s="22">
+        <v>2</v>
+      </c>
+      <c r="F42" s="22"/>
+      <c r="G42" s="22"/>
+      <c r="H42" s="22">
+        <v>2</v>
+      </c>
+      <c r="I42" s="22">
         <v>0</v>
       </c>
-      <c r="J42" s="21"/>
+      <c r="J42" s="22"/>
     </row>
     <row r="43" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A43" s="7" t="s">
@@ -2661,7 +2768,7 @@
       <c r="C43" s="7">
         <v>9991005</v>
       </c>
-      <c r="D43" s="17">
+      <c r="D43" s="18">
         <v>46207</v>
       </c>
       <c r="E43" s="7">
@@ -2718,76 +2825,76 @@
       <c r="J45" s="7"/>
     </row>
     <row r="46" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A46" s="20" t="s">
+      <c r="A46" s="21" t="s">
         <v>47</v>
       </c>
-      <c r="B46" s="19" t="s">
+      <c r="B46" s="20" t="s">
         <v>6</v>
       </c>
-      <c r="C46" s="19">
+      <c r="C46" s="20">
         <v>9991005</v>
       </c>
-      <c r="D46" s="19"/>
-      <c r="E46" s="19"/>
-      <c r="F46" s="19">
+      <c r="D46" s="20"/>
+      <c r="E46" s="20"/>
+      <c r="F46" s="20">
         <v>17012822</v>
       </c>
-      <c r="G46" s="22">
+      <c r="G46" s="23">
         <v>46205</v>
       </c>
-      <c r="H46" s="19">
-        <v>2</v>
-      </c>
-      <c r="I46" s="19"/>
-      <c r="J46" s="19"/>
+      <c r="H46" s="20">
+        <v>2</v>
+      </c>
+      <c r="I46" s="20"/>
+      <c r="J46" s="20"/>
     </row>
     <row r="47" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A47" s="20" t="s">
+      <c r="A47" s="21" t="s">
         <v>47</v>
       </c>
-      <c r="B47" s="19" t="s">
+      <c r="B47" s="20" t="s">
         <v>6</v>
       </c>
-      <c r="C47" s="19">
+      <c r="C47" s="20">
         <v>9991005</v>
       </c>
-      <c r="D47" s="19"/>
-      <c r="E47" s="19"/>
-      <c r="F47" s="19">
+      <c r="D47" s="20"/>
+      <c r="E47" s="20"/>
+      <c r="F47" s="20">
         <v>17013005</v>
       </c>
-      <c r="G47" s="22">
+      <c r="G47" s="23">
         <v>46057</v>
       </c>
-      <c r="H47" s="19">
-        <v>1</v>
-      </c>
-      <c r="I47" s="19"/>
-      <c r="J47" s="19"/>
+      <c r="H47" s="20">
+        <v>1</v>
+      </c>
+      <c r="I47" s="20"/>
+      <c r="J47" s="20"/>
     </row>
     <row r="48" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A48" s="18" t="s">
+      <c r="A48" s="19" t="s">
         <v>45</v>
       </c>
-      <c r="B48" s="18" t="s">
+      <c r="B48" s="19" t="s">
         <v>6</v>
       </c>
-      <c r="C48" s="18">
+      <c r="C48" s="19">
         <v>9991005</v>
       </c>
-      <c r="D48" s="18"/>
-      <c r="E48" s="18">
-        <v>4</v>
-      </c>
-      <c r="F48" s="18"/>
-      <c r="G48" s="18"/>
-      <c r="H48" s="18">
-        <v>3</v>
-      </c>
-      <c r="I48" s="18">
-        <v>1</v>
-      </c>
-      <c r="J48" s="18">
+      <c r="D48" s="19"/>
+      <c r="E48" s="19">
+        <v>4</v>
+      </c>
+      <c r="F48" s="19"/>
+      <c r="G48" s="19"/>
+      <c r="H48" s="19">
+        <v>3</v>
+      </c>
+      <c r="I48" s="19">
+        <v>1</v>
+      </c>
+      <c r="J48" s="19">
         <v>1</v>
       </c>
     </row>
@@ -2814,44 +2921,44 @@
       <c r="J49" s="7"/>
     </row>
     <row r="50" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A50" s="18" t="s">
+      <c r="A50" s="19" t="s">
         <v>45</v>
       </c>
-      <c r="B50" s="18" t="s">
+      <c r="B50" s="19" t="s">
         <v>8</v>
       </c>
-      <c r="C50" s="18">
+      <c r="C50" s="19">
         <v>9991007</v>
       </c>
-      <c r="D50" s="18"/>
-      <c r="E50" s="18">
-        <v>1</v>
-      </c>
-      <c r="F50" s="18"/>
-      <c r="G50" s="18"/>
-      <c r="H50" s="18">
+      <c r="D50" s="19"/>
+      <c r="E50" s="19">
+        <v>1</v>
+      </c>
+      <c r="F50" s="19"/>
+      <c r="G50" s="19"/>
+      <c r="H50" s="19">
         <v>0</v>
       </c>
-      <c r="I50" s="18">
-        <v>1</v>
-      </c>
-      <c r="J50" s="18">
+      <c r="I50" s="19">
+        <v>1</v>
+      </c>
+      <c r="J50" s="19">
         <v>1</v>
       </c>
     </row>
     <row r="52" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A52" s="16" t="s">
+      <c r="A52" s="17" t="s">
         <v>18</v>
       </c>
-      <c r="B52" s="16"/>
-      <c r="C52" s="16"/>
-      <c r="D52" s="16"/>
-      <c r="E52" s="16"/>
-      <c r="F52" s="16"/>
-      <c r="G52" s="16"/>
-      <c r="H52" s="16"/>
-      <c r="I52" s="16"/>
-      <c r="J52" s="16"/>
+      <c r="B52" s="17"/>
+      <c r="C52" s="17"/>
+      <c r="D52" s="17"/>
+      <c r="E52" s="17"/>
+      <c r="F52" s="17"/>
+      <c r="G52" s="17"/>
+      <c r="H52" s="17"/>
+      <c r="I52" s="17"/>
+      <c r="J52" s="17"/>
     </row>
     <row r="53" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A53" s="7" t="s">
@@ -2863,7 +2970,7 @@
       <c r="C53" s="7">
         <v>9991002</v>
       </c>
-      <c r="D53" s="17">
+      <c r="D53" s="18">
         <v>46083</v>
       </c>
       <c r="E53" s="7">
@@ -2920,100 +3027,100 @@
       <c r="J55" s="7"/>
     </row>
     <row r="56" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A56" s="20" t="s">
+      <c r="A56" s="21" t="s">
         <v>47</v>
       </c>
-      <c r="B56" s="19" t="s">
-        <v>3</v>
-      </c>
-      <c r="C56" s="19">
+      <c r="B56" s="20" t="s">
+        <v>3</v>
+      </c>
+      <c r="C56" s="20">
         <v>9991002</v>
       </c>
-      <c r="D56" s="19"/>
-      <c r="E56" s="19"/>
-      <c r="F56" s="19">
+      <c r="D56" s="20"/>
+      <c r="E56" s="20"/>
+      <c r="F56" s="20">
         <v>1812074</v>
       </c>
-      <c r="G56" s="22">
+      <c r="G56" s="23">
         <v>46024</v>
       </c>
-      <c r="H56" s="19">
-        <v>1</v>
-      </c>
-      <c r="I56" s="19"/>
-      <c r="J56" s="19"/>
+      <c r="H56" s="20">
+        <v>1</v>
+      </c>
+      <c r="I56" s="20"/>
+      <c r="J56" s="20"/>
     </row>
     <row r="57" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A57" s="20" t="s">
+      <c r="A57" s="21" t="s">
         <v>47</v>
       </c>
-      <c r="B57" s="19" t="s">
-        <v>3</v>
-      </c>
-      <c r="C57" s="19">
+      <c r="B57" s="20" t="s">
+        <v>3</v>
+      </c>
+      <c r="C57" s="20">
         <v>9991002</v>
       </c>
-      <c r="D57" s="19"/>
-      <c r="E57" s="19"/>
-      <c r="F57" s="19">
+      <c r="D57" s="20"/>
+      <c r="E57" s="20"/>
+      <c r="F57" s="20">
         <v>1812077</v>
       </c>
-      <c r="G57" s="22">
+      <c r="G57" s="23">
         <v>46055</v>
       </c>
-      <c r="H57" s="19">
-        <v>1</v>
-      </c>
-      <c r="I57" s="19"/>
-      <c r="J57" s="19"/>
+      <c r="H57" s="20">
+        <v>1</v>
+      </c>
+      <c r="I57" s="20"/>
+      <c r="J57" s="20"/>
     </row>
     <row r="58" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A58" s="20" t="s">
+      <c r="A58" s="21" t="s">
         <v>47</v>
       </c>
-      <c r="B58" s="19" t="s">
-        <v>3</v>
-      </c>
-      <c r="C58" s="19">
+      <c r="B58" s="20" t="s">
+        <v>3</v>
+      </c>
+      <c r="C58" s="20">
         <v>9991002</v>
       </c>
-      <c r="D58" s="19"/>
-      <c r="E58" s="19"/>
-      <c r="F58" s="19">
+      <c r="D58" s="20"/>
+      <c r="E58" s="20"/>
+      <c r="F58" s="20">
         <v>1812240</v>
       </c>
-      <c r="G58" s="19" t="s">
+      <c r="G58" s="20" t="s">
         <v>72</v>
       </c>
-      <c r="H58" s="19">
-        <v>1</v>
-      </c>
-      <c r="I58" s="19"/>
-      <c r="J58" s="19"/>
+      <c r="H58" s="20">
+        <v>1</v>
+      </c>
+      <c r="I58" s="20"/>
+      <c r="J58" s="20"/>
     </row>
     <row r="59" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A59" s="18" t="s">
+      <c r="A59" s="19" t="s">
         <v>45</v>
       </c>
-      <c r="B59" s="18" t="s">
-        <v>3</v>
-      </c>
-      <c r="C59" s="18">
+      <c r="B59" s="19" t="s">
+        <v>3</v>
+      </c>
+      <c r="C59" s="19">
         <v>9991002</v>
       </c>
-      <c r="D59" s="18"/>
-      <c r="E59" s="18">
-        <v>4</v>
-      </c>
-      <c r="F59" s="18"/>
-      <c r="G59" s="18"/>
-      <c r="H59" s="18">
-        <v>3</v>
-      </c>
-      <c r="I59" s="18">
-        <v>1</v>
-      </c>
-      <c r="J59" s="18">
+      <c r="D59" s="19"/>
+      <c r="E59" s="19">
+        <v>4</v>
+      </c>
+      <c r="F59" s="19"/>
+      <c r="G59" s="19"/>
+      <c r="H59" s="19">
+        <v>3</v>
+      </c>
+      <c r="I59" s="19">
+        <v>1</v>
+      </c>
+      <c r="J59" s="19">
         <v>1</v>
       </c>
     </row>
@@ -3027,7 +3134,7 @@
       <c r="C60" s="7">
         <v>9991003</v>
       </c>
-      <c r="D60" s="17">
+      <c r="D60" s="18">
         <v>46176</v>
       </c>
       <c r="E60" s="7">
@@ -3106,100 +3213,100 @@
       <c r="J63" s="8"/>
     </row>
     <row r="64" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A64" s="20" t="s">
+      <c r="A64" s="21" t="s">
         <v>47</v>
       </c>
-      <c r="B64" s="19" t="s">
-        <v>4</v>
-      </c>
-      <c r="C64" s="19">
+      <c r="B64" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="C64" s="20">
         <v>9991003</v>
       </c>
-      <c r="D64" s="19"/>
-      <c r="E64" s="19"/>
-      <c r="F64" s="19">
+      <c r="D64" s="20"/>
+      <c r="E64" s="20"/>
+      <c r="F64" s="20">
         <v>1812077</v>
       </c>
-      <c r="G64" s="22">
+      <c r="G64" s="23">
         <v>46055</v>
       </c>
-      <c r="H64" s="19">
-        <v>2</v>
-      </c>
-      <c r="I64" s="19"/>
-      <c r="J64" s="19"/>
+      <c r="H64" s="20">
+        <v>2</v>
+      </c>
+      <c r="I64" s="20"/>
+      <c r="J64" s="20"/>
     </row>
     <row r="65" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A65" s="20" t="s">
+      <c r="A65" s="21" t="s">
         <v>47</v>
       </c>
-      <c r="B65" s="19" t="s">
-        <v>4</v>
-      </c>
-      <c r="C65" s="19">
+      <c r="B65" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="C65" s="20">
         <v>9991003</v>
       </c>
-      <c r="D65" s="19"/>
-      <c r="E65" s="19"/>
-      <c r="F65" s="19">
+      <c r="D65" s="20"/>
+      <c r="E65" s="20"/>
+      <c r="F65" s="20">
         <v>1812285</v>
       </c>
-      <c r="G65" s="22">
+      <c r="G65" s="23">
         <v>46177</v>
       </c>
-      <c r="H65" s="19">
-        <v>4</v>
-      </c>
-      <c r="I65" s="19"/>
-      <c r="J65" s="19"/>
+      <c r="H65" s="20">
+        <v>4</v>
+      </c>
+      <c r="I65" s="20"/>
+      <c r="J65" s="20"/>
     </row>
     <row r="66" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A66" s="20" t="s">
+      <c r="A66" s="21" t="s">
         <v>47</v>
       </c>
-      <c r="B66" s="19" t="s">
-        <v>4</v>
-      </c>
-      <c r="C66" s="19">
+      <c r="B66" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="C66" s="20">
         <v>9991003</v>
       </c>
-      <c r="D66" s="19"/>
-      <c r="E66" s="19"/>
-      <c r="F66" s="19">
+      <c r="D66" s="20"/>
+      <c r="E66" s="20"/>
+      <c r="F66" s="20">
         <v>1812398</v>
       </c>
-      <c r="G66" s="22">
+      <c r="G66" s="23">
         <v>46331</v>
       </c>
-      <c r="H66" s="19">
-        <v>2</v>
-      </c>
-      <c r="I66" s="19"/>
-      <c r="J66" s="19"/>
+      <c r="H66" s="20">
+        <v>2</v>
+      </c>
+      <c r="I66" s="20"/>
+      <c r="J66" s="20"/>
     </row>
     <row r="67" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A67" s="18" t="s">
+      <c r="A67" s="19" t="s">
         <v>45</v>
       </c>
-      <c r="B67" s="18" t="s">
-        <v>4</v>
-      </c>
-      <c r="C67" s="18">
+      <c r="B67" s="19" t="s">
+        <v>4</v>
+      </c>
+      <c r="C67" s="19">
         <v>9991003</v>
       </c>
-      <c r="D67" s="18"/>
-      <c r="E67" s="18">
+      <c r="D67" s="19"/>
+      <c r="E67" s="19">
         <v>9</v>
       </c>
-      <c r="F67" s="18"/>
-      <c r="G67" s="18"/>
-      <c r="H67" s="18">
+      <c r="F67" s="19"/>
+      <c r="G67" s="19"/>
+      <c r="H67" s="19">
         <v>8</v>
       </c>
-      <c r="I67" s="18">
-        <v>1</v>
-      </c>
-      <c r="J67" s="18">
+      <c r="I67" s="19">
+        <v>1</v>
+      </c>
+      <c r="J67" s="19">
         <v>1</v>
       </c>
     </row>
@@ -3213,7 +3320,7 @@
       <c r="C68" s="7">
         <v>9991004</v>
       </c>
-      <c r="D68" s="17">
+      <c r="D68" s="18">
         <v>46176</v>
       </c>
       <c r="E68" s="7">
@@ -3248,90 +3355,90 @@
       <c r="J69" s="8"/>
     </row>
     <row r="70" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A70" s="20" t="s">
+      <c r="A70" s="21" t="s">
         <v>47</v>
       </c>
-      <c r="B70" s="19" t="s">
+      <c r="B70" s="20" t="s">
         <v>5</v>
       </c>
-      <c r="C70" s="19">
+      <c r="C70" s="20">
         <v>9991004</v>
       </c>
-      <c r="D70" s="19"/>
-      <c r="E70" s="19"/>
-      <c r="F70" s="19">
+      <c r="D70" s="20"/>
+      <c r="E70" s="20"/>
+      <c r="F70" s="20">
         <v>1812138</v>
       </c>
-      <c r="G70" s="19" t="s">
+      <c r="G70" s="20" t="s">
         <v>78</v>
       </c>
-      <c r="H70" s="19">
-        <v>2</v>
-      </c>
-      <c r="I70" s="19"/>
-      <c r="J70" s="19"/>
+      <c r="H70" s="20">
+        <v>2</v>
+      </c>
+      <c r="I70" s="20"/>
+      <c r="J70" s="20"/>
     </row>
     <row r="71" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A71" s="20" t="s">
+      <c r="A71" s="21" t="s">
         <v>47</v>
       </c>
-      <c r="B71" s="19" t="s">
+      <c r="B71" s="20" t="s">
         <v>5</v>
       </c>
-      <c r="C71" s="19">
+      <c r="C71" s="20">
         <v>9991004</v>
       </c>
-      <c r="D71" s="19"/>
-      <c r="E71" s="19"/>
-      <c r="F71" s="19">
+      <c r="D71" s="20"/>
+      <c r="E71" s="20"/>
+      <c r="F71" s="20">
         <v>1812285</v>
       </c>
-      <c r="G71" s="22">
+      <c r="G71" s="23">
         <v>46177</v>
       </c>
-      <c r="H71" s="19">
-        <v>2</v>
-      </c>
-      <c r="I71" s="19"/>
-      <c r="J71" s="19"/>
+      <c r="H71" s="20">
+        <v>2</v>
+      </c>
+      <c r="I71" s="20"/>
+      <c r="J71" s="20"/>
     </row>
     <row r="72" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A72" s="21" t="s">
+      <c r="A72" s="22" t="s">
         <v>45</v>
       </c>
-      <c r="B72" s="21" t="s">
+      <c r="B72" s="22" t="s">
         <v>5</v>
       </c>
-      <c r="C72" s="21">
+      <c r="C72" s="22">
         <v>9991004</v>
       </c>
-      <c r="D72" s="21"/>
-      <c r="E72" s="21">
-        <v>4</v>
-      </c>
-      <c r="F72" s="21"/>
-      <c r="G72" s="21"/>
-      <c r="H72" s="21">
-        <v>4</v>
-      </c>
-      <c r="I72" s="21">
+      <c r="D72" s="22"/>
+      <c r="E72" s="22">
+        <v>4</v>
+      </c>
+      <c r="F72" s="22"/>
+      <c r="G72" s="22"/>
+      <c r="H72" s="22">
+        <v>4</v>
+      </c>
+      <c r="I72" s="22">
         <v>0</v>
       </c>
-      <c r="J72" s="21"/>
+      <c r="J72" s="22"/>
     </row>
     <row r="74" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A74" s="16" t="s">
+      <c r="A74" s="17" t="s">
         <v>79</v>
       </c>
-      <c r="B74" s="16"/>
-      <c r="C74" s="16"/>
-      <c r="D74" s="16"/>
-      <c r="E74" s="16"/>
-      <c r="F74" s="16"/>
-      <c r="G74" s="16"/>
-      <c r="H74" s="16"/>
-      <c r="I74" s="16"/>
-      <c r="J74" s="16"/>
+      <c r="B74" s="17"/>
+      <c r="C74" s="17"/>
+      <c r="D74" s="17"/>
+      <c r="E74" s="17"/>
+      <c r="F74" s="17"/>
+      <c r="G74" s="17"/>
+      <c r="H74" s="17"/>
+      <c r="I74" s="17"/>
+      <c r="J74" s="17"/>
     </row>
     <row r="75" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A75" s="7" t="s">
@@ -3356,52 +3463,52 @@
       <c r="J75" s="7"/>
     </row>
     <row r="76" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A76" s="20" t="s">
+      <c r="A76" s="21" t="s">
         <v>47</v>
       </c>
-      <c r="B76" s="19" t="s">
-        <v>2</v>
-      </c>
-      <c r="C76" s="19">
+      <c r="B76" s="20" t="s">
+        <v>2</v>
+      </c>
+      <c r="C76" s="20">
         <v>9991001</v>
       </c>
-      <c r="D76" s="19"/>
-      <c r="E76" s="19"/>
-      <c r="F76" s="19">
+      <c r="D76" s="20"/>
+      <c r="E76" s="20"/>
+      <c r="F76" s="20">
         <v>19014305</v>
       </c>
-      <c r="G76" s="19" t="s">
+      <c r="G76" s="20" t="s">
         <v>58</v>
       </c>
-      <c r="H76" s="19">
-        <v>2</v>
-      </c>
-      <c r="I76" s="19"/>
-      <c r="J76" s="19"/>
+      <c r="H76" s="20">
+        <v>2</v>
+      </c>
+      <c r="I76" s="20"/>
+      <c r="J76" s="20"/>
     </row>
     <row r="77" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A77" s="21" t="s">
+      <c r="A77" s="22" t="s">
         <v>45</v>
       </c>
-      <c r="B77" s="21" t="s">
-        <v>2</v>
-      </c>
-      <c r="C77" s="21">
+      <c r="B77" s="22" t="s">
+        <v>2</v>
+      </c>
+      <c r="C77" s="22">
         <v>9991001</v>
       </c>
-      <c r="D77" s="21"/>
-      <c r="E77" s="21">
-        <v>2</v>
-      </c>
-      <c r="F77" s="21"/>
-      <c r="G77" s="21"/>
-      <c r="H77" s="21">
-        <v>2</v>
-      </c>
-      <c r="I77" s="21">
+      <c r="D77" s="22"/>
+      <c r="E77" s="22">
+        <v>2</v>
+      </c>
+      <c r="F77" s="22"/>
+      <c r="G77" s="22"/>
+      <c r="H77" s="22">
+        <v>2</v>
+      </c>
+      <c r="I77" s="22">
         <v>0</v>
       </c>
-      <c r="J77" s="21"/>
+      <c r="J77" s="22"/>
     </row>
     <row r="78" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A78" s="7" t="s">
@@ -3413,7 +3520,7 @@
       <c r="C78" s="7">
         <v>9991002</v>
       </c>
-      <c r="D78" s="17">
+      <c r="D78" s="18">
         <v>46358</v>
       </c>
       <c r="E78" s="7">
@@ -3448,76 +3555,76 @@
       <c r="J79" s="8"/>
     </row>
     <row r="80" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A80" s="20" t="s">
+      <c r="A80" s="21" t="s">
         <v>47</v>
       </c>
-      <c r="B80" s="19" t="s">
-        <v>3</v>
-      </c>
-      <c r="C80" s="19">
+      <c r="B80" s="20" t="s">
+        <v>3</v>
+      </c>
+      <c r="C80" s="20">
         <v>9991002</v>
       </c>
-      <c r="D80" s="19"/>
-      <c r="E80" s="19"/>
-      <c r="F80" s="19">
+      <c r="D80" s="20"/>
+      <c r="E80" s="20"/>
+      <c r="F80" s="20">
         <v>19014133</v>
       </c>
-      <c r="G80" s="19" t="s">
+      <c r="G80" s="20" t="s">
         <v>85</v>
       </c>
-      <c r="H80" s="19">
-        <v>2</v>
-      </c>
-      <c r="I80" s="19"/>
-      <c r="J80" s="19"/>
+      <c r="H80" s="20">
+        <v>2</v>
+      </c>
+      <c r="I80" s="20"/>
+      <c r="J80" s="20"/>
     </row>
     <row r="81" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A81" s="20" t="s">
+      <c r="A81" s="21" t="s">
         <v>47</v>
       </c>
-      <c r="B81" s="19" t="s">
-        <v>3</v>
-      </c>
-      <c r="C81" s="19">
+      <c r="B81" s="20" t="s">
+        <v>3</v>
+      </c>
+      <c r="C81" s="20">
         <v>9991002</v>
       </c>
-      <c r="D81" s="19"/>
-      <c r="E81" s="19"/>
-      <c r="F81" s="19">
+      <c r="D81" s="20"/>
+      <c r="E81" s="20"/>
+      <c r="F81" s="20">
         <v>19014370</v>
       </c>
-      <c r="G81" s="19" t="s">
+      <c r="G81" s="20" t="s">
         <v>86</v>
       </c>
-      <c r="H81" s="19">
-        <v>3</v>
-      </c>
-      <c r="I81" s="19"/>
-      <c r="J81" s="19"/>
+      <c r="H81" s="20">
+        <v>3</v>
+      </c>
+      <c r="I81" s="20"/>
+      <c r="J81" s="20"/>
     </row>
     <row r="82" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A82" s="21" t="s">
+      <c r="A82" s="22" t="s">
         <v>45</v>
       </c>
-      <c r="B82" s="21" t="s">
-        <v>3</v>
-      </c>
-      <c r="C82" s="21">
+      <c r="B82" s="22" t="s">
+        <v>3</v>
+      </c>
+      <c r="C82" s="22">
         <v>9991002</v>
       </c>
-      <c r="D82" s="21"/>
-      <c r="E82" s="21">
+      <c r="D82" s="22"/>
+      <c r="E82" s="22">
         <v>5</v>
       </c>
-      <c r="F82" s="21"/>
-      <c r="G82" s="21"/>
-      <c r="H82" s="21">
+      <c r="F82" s="22"/>
+      <c r="G82" s="22"/>
+      <c r="H82" s="22">
         <v>5</v>
       </c>
-      <c r="I82" s="21">
+      <c r="I82" s="22">
         <v>0</v>
       </c>
-      <c r="J82" s="21"/>
+      <c r="J82" s="22"/>
     </row>
     <row r="83" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A83" s="7" t="s">
@@ -3529,7 +3636,7 @@
       <c r="C83" s="7">
         <v>9991004</v>
       </c>
-      <c r="D83" s="17">
+      <c r="D83" s="18">
         <v>46055</v>
       </c>
       <c r="E83" s="7">
@@ -3551,7 +3658,7 @@
       <c r="C84" s="8">
         <v>9991004</v>
       </c>
-      <c r="D84" s="23">
+      <c r="D84" s="24">
         <v>46175</v>
       </c>
       <c r="E84" s="8">
@@ -3573,7 +3680,7 @@
       <c r="C85" s="7">
         <v>9991004</v>
       </c>
-      <c r="D85" s="17">
+      <c r="D85" s="18">
         <v>46239</v>
       </c>
       <c r="E85" s="7">
@@ -3586,114 +3693,114 @@
       <c r="J85" s="7"/>
     </row>
     <row r="86" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A86" s="20" t="s">
+      <c r="A86" s="21" t="s">
         <v>47</v>
       </c>
-      <c r="B86" s="19" t="s">
+      <c r="B86" s="20" t="s">
         <v>5</v>
       </c>
-      <c r="C86" s="19">
+      <c r="C86" s="20">
         <v>9991004</v>
       </c>
-      <c r="D86" s="19"/>
-      <c r="E86" s="19"/>
-      <c r="F86" s="19">
+      <c r="D86" s="20"/>
+      <c r="E86" s="20"/>
+      <c r="F86" s="20">
         <v>19014076</v>
       </c>
-      <c r="G86" s="22">
+      <c r="G86" s="23">
         <v>46175</v>
       </c>
-      <c r="H86" s="19">
-        <v>1</v>
-      </c>
-      <c r="I86" s="19"/>
-      <c r="J86" s="19"/>
+      <c r="H86" s="20">
+        <v>1</v>
+      </c>
+      <c r="I86" s="20"/>
+      <c r="J86" s="20"/>
     </row>
     <row r="87" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A87" s="20" t="s">
+      <c r="A87" s="21" t="s">
         <v>47</v>
       </c>
-      <c r="B87" s="19" t="s">
+      <c r="B87" s="20" t="s">
         <v>5</v>
       </c>
-      <c r="C87" s="19">
+      <c r="C87" s="20">
         <v>9991004</v>
       </c>
-      <c r="D87" s="19"/>
-      <c r="E87" s="19"/>
-      <c r="F87" s="19">
+      <c r="D87" s="20"/>
+      <c r="E87" s="20"/>
+      <c r="F87" s="20">
         <v>19014101</v>
       </c>
-      <c r="G87" s="19" t="s">
+      <c r="G87" s="20" t="s">
         <v>89</v>
       </c>
-      <c r="H87" s="19">
-        <v>1</v>
-      </c>
-      <c r="I87" s="19"/>
-      <c r="J87" s="19"/>
+      <c r="H87" s="20">
+        <v>1</v>
+      </c>
+      <c r="I87" s="20"/>
+      <c r="J87" s="20"/>
     </row>
     <row r="88" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A88" s="20" t="s">
+      <c r="A88" s="21" t="s">
         <v>47</v>
       </c>
-      <c r="B88" s="19" t="s">
+      <c r="B88" s="20" t="s">
         <v>5</v>
       </c>
-      <c r="C88" s="19">
+      <c r="C88" s="20">
         <v>9991004</v>
       </c>
-      <c r="D88" s="19"/>
-      <c r="E88" s="19"/>
-      <c r="F88" s="19">
+      <c r="D88" s="20"/>
+      <c r="E88" s="20"/>
+      <c r="F88" s="20">
         <v>19014406</v>
       </c>
-      <c r="G88" s="19" t="s">
+      <c r="G88" s="20" t="s">
         <v>43</v>
       </c>
-      <c r="H88" s="19">
-        <v>1</v>
-      </c>
-      <c r="I88" s="19"/>
-      <c r="J88" s="19"/>
+      <c r="H88" s="20">
+        <v>1</v>
+      </c>
+      <c r="I88" s="20"/>
+      <c r="J88" s="20"/>
     </row>
     <row r="89" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A89" s="21" t="s">
+      <c r="A89" s="22" t="s">
         <v>45</v>
       </c>
-      <c r="B89" s="21" t="s">
+      <c r="B89" s="22" t="s">
         <v>5</v>
       </c>
-      <c r="C89" s="21">
+      <c r="C89" s="22">
         <v>9991004</v>
       </c>
-      <c r="D89" s="21"/>
-      <c r="E89" s="21">
-        <v>3</v>
-      </c>
-      <c r="F89" s="21"/>
-      <c r="G89" s="21"/>
-      <c r="H89" s="21">
-        <v>3</v>
-      </c>
-      <c r="I89" s="21">
+      <c r="D89" s="22"/>
+      <c r="E89" s="22">
+        <v>3</v>
+      </c>
+      <c r="F89" s="22"/>
+      <c r="G89" s="22"/>
+      <c r="H89" s="22">
+        <v>3</v>
+      </c>
+      <c r="I89" s="22">
         <v>0</v>
       </c>
-      <c r="J89" s="21"/>
+      <c r="J89" s="22"/>
     </row>
     <row r="91" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A91" s="16" t="s">
+      <c r="A91" s="17" t="s">
         <v>90</v>
       </c>
-      <c r="B91" s="16"/>
-      <c r="C91" s="16"/>
-      <c r="D91" s="16"/>
-      <c r="E91" s="16"/>
-      <c r="F91" s="16"/>
-      <c r="G91" s="16"/>
-      <c r="H91" s="16"/>
-      <c r="I91" s="16"/>
-      <c r="J91" s="16"/>
+      <c r="B91" s="17"/>
+      <c r="C91" s="17"/>
+      <c r="D91" s="17"/>
+      <c r="E91" s="17"/>
+      <c r="F91" s="17"/>
+      <c r="G91" s="17"/>
+      <c r="H91" s="17"/>
+      <c r="I91" s="17"/>
+      <c r="J91" s="17"/>
     </row>
     <row r="92" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A92" s="7" t="s">
@@ -3705,7 +3812,7 @@
       <c r="C92" s="7">
         <v>9991002</v>
       </c>
-      <c r="D92" s="17">
+      <c r="D92" s="18">
         <v>46083</v>
       </c>
       <c r="E92" s="7">
@@ -3762,100 +3869,100 @@
       <c r="J94" s="7"/>
     </row>
     <row r="95" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A95" s="20" t="s">
+      <c r="A95" s="21" t="s">
         <v>47</v>
       </c>
-      <c r="B95" s="19" t="s">
-        <v>3</v>
-      </c>
-      <c r="C95" s="19">
+      <c r="B95" s="20" t="s">
+        <v>3</v>
+      </c>
+      <c r="C95" s="20">
         <v>9991002</v>
       </c>
-      <c r="D95" s="19"/>
-      <c r="E95" s="19"/>
-      <c r="F95" s="19">
+      <c r="D95" s="20"/>
+      <c r="E95" s="20"/>
+      <c r="F95" s="20">
         <v>2111875</v>
       </c>
-      <c r="G95" s="22">
+      <c r="G95" s="23">
         <v>46175</v>
       </c>
-      <c r="H95" s="19">
-        <v>1</v>
-      </c>
-      <c r="I95" s="19"/>
-      <c r="J95" s="19"/>
+      <c r="H95" s="20">
+        <v>1</v>
+      </c>
+      <c r="I95" s="20"/>
+      <c r="J95" s="20"/>
     </row>
     <row r="96" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A96" s="20" t="s">
+      <c r="A96" s="21" t="s">
         <v>47</v>
       </c>
-      <c r="B96" s="19" t="s">
-        <v>3</v>
-      </c>
-      <c r="C96" s="19">
+      <c r="B96" s="20" t="s">
+        <v>3</v>
+      </c>
+      <c r="C96" s="20">
         <v>9991002</v>
       </c>
-      <c r="D96" s="19"/>
-      <c r="E96" s="19"/>
-      <c r="F96" s="19">
+      <c r="D96" s="20"/>
+      <c r="E96" s="20"/>
+      <c r="F96" s="20">
         <v>2111915</v>
       </c>
-      <c r="G96" s="19" t="s">
+      <c r="G96" s="20" t="s">
         <v>94</v>
       </c>
-      <c r="H96" s="19">
-        <v>1</v>
-      </c>
-      <c r="I96" s="19"/>
-      <c r="J96" s="19"/>
+      <c r="H96" s="20">
+        <v>1</v>
+      </c>
+      <c r="I96" s="20"/>
+      <c r="J96" s="20"/>
     </row>
     <row r="97" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A97" s="20" t="s">
+      <c r="A97" s="21" t="s">
         <v>47</v>
       </c>
-      <c r="B97" s="19" t="s">
-        <v>3</v>
-      </c>
-      <c r="C97" s="19">
+      <c r="B97" s="20" t="s">
+        <v>3</v>
+      </c>
+      <c r="C97" s="20">
         <v>9991002</v>
       </c>
-      <c r="D97" s="19"/>
-      <c r="E97" s="19"/>
-      <c r="F97" s="19">
+      <c r="D97" s="20"/>
+      <c r="E97" s="20"/>
+      <c r="F97" s="20">
         <v>2112032</v>
       </c>
-      <c r="G97" s="19" t="s">
+      <c r="G97" s="20" t="s">
         <v>95</v>
       </c>
-      <c r="H97" s="19">
-        <v>2</v>
-      </c>
-      <c r="I97" s="19"/>
-      <c r="J97" s="19"/>
+      <c r="H97" s="20">
+        <v>2</v>
+      </c>
+      <c r="I97" s="20"/>
+      <c r="J97" s="20"/>
     </row>
     <row r="98" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A98" s="21" t="s">
+      <c r="A98" s="22" t="s">
         <v>45</v>
       </c>
-      <c r="B98" s="21" t="s">
-        <v>3</v>
-      </c>
-      <c r="C98" s="21">
+      <c r="B98" s="22" t="s">
+        <v>3</v>
+      </c>
+      <c r="C98" s="22">
         <v>9991002</v>
       </c>
-      <c r="D98" s="21"/>
-      <c r="E98" s="21">
-        <v>4</v>
-      </c>
-      <c r="F98" s="21"/>
-      <c r="G98" s="21"/>
-      <c r="H98" s="21">
-        <v>4</v>
-      </c>
-      <c r="I98" s="21">
+      <c r="D98" s="22"/>
+      <c r="E98" s="22">
+        <v>4</v>
+      </c>
+      <c r="F98" s="22"/>
+      <c r="G98" s="22"/>
+      <c r="H98" s="22">
+        <v>4</v>
+      </c>
+      <c r="I98" s="22">
         <v>0</v>
       </c>
-      <c r="J98" s="21"/>
+      <c r="J98" s="22"/>
     </row>
     <row r="99" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A99" s="7" t="s">
@@ -3880,66 +3987,66 @@
       <c r="J99" s="7"/>
     </row>
     <row r="100" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A100" s="20" t="s">
+      <c r="A100" s="21" t="s">
         <v>47</v>
       </c>
-      <c r="B100" s="19" t="s">
-        <v>4</v>
-      </c>
-      <c r="C100" s="19">
+      <c r="B100" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="C100" s="20">
         <v>9991003</v>
       </c>
-      <c r="D100" s="19"/>
-      <c r="E100" s="19"/>
-      <c r="F100" s="19">
+      <c r="D100" s="20"/>
+      <c r="E100" s="20"/>
+      <c r="F100" s="20">
         <v>2112075</v>
       </c>
-      <c r="G100" s="22">
+      <c r="G100" s="23">
         <v>46269</v>
       </c>
-      <c r="H100" s="19">
-        <v>1</v>
-      </c>
-      <c r="I100" s="19"/>
-      <c r="J100" s="19"/>
+      <c r="H100" s="20">
+        <v>1</v>
+      </c>
+      <c r="I100" s="20"/>
+      <c r="J100" s="20"/>
     </row>
     <row r="101" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A101" s="21" t="s">
+      <c r="A101" s="22" t="s">
         <v>45</v>
       </c>
-      <c r="B101" s="21" t="s">
-        <v>4</v>
-      </c>
-      <c r="C101" s="21">
+      <c r="B101" s="22" t="s">
+        <v>4</v>
+      </c>
+      <c r="C101" s="22">
         <v>9991003</v>
       </c>
-      <c r="D101" s="21"/>
-      <c r="E101" s="21">
-        <v>1</v>
-      </c>
-      <c r="F101" s="21"/>
-      <c r="G101" s="21"/>
-      <c r="H101" s="21">
-        <v>1</v>
-      </c>
-      <c r="I101" s="21">
+      <c r="D101" s="22"/>
+      <c r="E101" s="22">
+        <v>1</v>
+      </c>
+      <c r="F101" s="22"/>
+      <c r="G101" s="22"/>
+      <c r="H101" s="22">
+        <v>1</v>
+      </c>
+      <c r="I101" s="22">
         <v>0</v>
       </c>
-      <c r="J101" s="21"/>
+      <c r="J101" s="22"/>
     </row>
     <row r="103" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A103" s="16" t="s">
+      <c r="A103" s="17" t="s">
         <v>19</v>
       </c>
-      <c r="B103" s="16"/>
-      <c r="C103" s="16"/>
-      <c r="D103" s="16"/>
-      <c r="E103" s="16"/>
-      <c r="F103" s="16"/>
-      <c r="G103" s="16"/>
-      <c r="H103" s="16"/>
-      <c r="I103" s="16"/>
-      <c r="J103" s="16"/>
+      <c r="B103" s="17"/>
+      <c r="C103" s="17"/>
+      <c r="D103" s="17"/>
+      <c r="E103" s="17"/>
+      <c r="F103" s="17"/>
+      <c r="G103" s="17"/>
+      <c r="H103" s="17"/>
+      <c r="I103" s="17"/>
+      <c r="J103" s="17"/>
     </row>
     <row r="104" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A104" s="7" t="s">
@@ -3951,7 +4058,7 @@
       <c r="C104" s="7">
         <v>9991002</v>
       </c>
-      <c r="D104" s="17">
+      <c r="D104" s="18">
         <v>46358</v>
       </c>
       <c r="E104" s="7">
@@ -3986,52 +4093,52 @@
       <c r="J105" s="8"/>
     </row>
     <row r="106" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A106" s="20" t="s">
+      <c r="A106" s="21" t="s">
         <v>47</v>
       </c>
-      <c r="B106" s="19" t="s">
-        <v>3</v>
-      </c>
-      <c r="C106" s="19">
+      <c r="B106" s="20" t="s">
+        <v>3</v>
+      </c>
+      <c r="C106" s="20">
         <v>9991002</v>
       </c>
-      <c r="D106" s="19"/>
-      <c r="E106" s="19"/>
-      <c r="F106" s="19">
+      <c r="D106" s="20"/>
+      <c r="E106" s="20"/>
+      <c r="F106" s="20">
         <v>2208326</v>
       </c>
-      <c r="G106" s="19" t="s">
+      <c r="G106" s="20" t="s">
         <v>85</v>
       </c>
-      <c r="H106" s="19">
-        <v>4</v>
-      </c>
-      <c r="I106" s="19"/>
-      <c r="J106" s="19"/>
+      <c r="H106" s="20">
+        <v>4</v>
+      </c>
+      <c r="I106" s="20"/>
+      <c r="J106" s="20"/>
     </row>
     <row r="107" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A107" s="21" t="s">
+      <c r="A107" s="22" t="s">
         <v>45</v>
       </c>
-      <c r="B107" s="21" t="s">
-        <v>3</v>
-      </c>
-      <c r="C107" s="21">
+      <c r="B107" s="22" t="s">
+        <v>3</v>
+      </c>
+      <c r="C107" s="22">
         <v>9991002</v>
       </c>
-      <c r="D107" s="21"/>
-      <c r="E107" s="21">
-        <v>4</v>
-      </c>
-      <c r="F107" s="21"/>
-      <c r="G107" s="21"/>
-      <c r="H107" s="21">
-        <v>4</v>
-      </c>
-      <c r="I107" s="21">
+      <c r="D107" s="22"/>
+      <c r="E107" s="22">
+        <v>4</v>
+      </c>
+      <c r="F107" s="22"/>
+      <c r="G107" s="22"/>
+      <c r="H107" s="22">
+        <v>4</v>
+      </c>
+      <c r="I107" s="22">
         <v>0</v>
       </c>
-      <c r="J107" s="21"/>
+      <c r="J107" s="22"/>
     </row>
     <row r="108" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A108" s="7" t="s">
@@ -4056,52 +4163,52 @@
       <c r="J108" s="7"/>
     </row>
     <row r="109" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A109" s="20" t="s">
+      <c r="A109" s="21" t="s">
         <v>47</v>
       </c>
-      <c r="B109" s="19" t="s">
-        <v>4</v>
-      </c>
-      <c r="C109" s="19">
+      <c r="B109" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="C109" s="20">
         <v>9991003</v>
       </c>
-      <c r="D109" s="19"/>
-      <c r="E109" s="19"/>
-      <c r="F109" s="19">
+      <c r="D109" s="20"/>
+      <c r="E109" s="20"/>
+      <c r="F109" s="20">
         <v>2208484</v>
       </c>
-      <c r="G109" s="19" t="s">
+      <c r="G109" s="20" t="s">
         <v>102</v>
       </c>
-      <c r="H109" s="19">
-        <v>2</v>
-      </c>
-      <c r="I109" s="19"/>
-      <c r="J109" s="19"/>
+      <c r="H109" s="20">
+        <v>2</v>
+      </c>
+      <c r="I109" s="20"/>
+      <c r="J109" s="20"/>
     </row>
     <row r="110" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A110" s="21" t="s">
+      <c r="A110" s="22" t="s">
         <v>45</v>
       </c>
-      <c r="B110" s="21" t="s">
-        <v>4</v>
-      </c>
-      <c r="C110" s="21">
+      <c r="B110" s="22" t="s">
+        <v>4</v>
+      </c>
+      <c r="C110" s="22">
         <v>9991003</v>
       </c>
-      <c r="D110" s="21"/>
-      <c r="E110" s="21">
-        <v>2</v>
-      </c>
-      <c r="F110" s="21"/>
-      <c r="G110" s="21"/>
-      <c r="H110" s="21">
-        <v>2</v>
-      </c>
-      <c r="I110" s="21">
+      <c r="D110" s="22"/>
+      <c r="E110" s="22">
+        <v>2</v>
+      </c>
+      <c r="F110" s="22"/>
+      <c r="G110" s="22"/>
+      <c r="H110" s="22">
+        <v>2</v>
+      </c>
+      <c r="I110" s="22">
         <v>0</v>
       </c>
-      <c r="J110" s="21"/>
+      <c r="J110" s="22"/>
     </row>
     <row r="111" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A111" s="7" t="s">
@@ -4113,7 +4220,7 @@
       <c r="C111" s="7">
         <v>9991004</v>
       </c>
-      <c r="D111" s="17">
+      <c r="D111" s="18">
         <v>46176</v>
       </c>
       <c r="E111" s="7">
@@ -4148,52 +4255,52 @@
       <c r="J112" s="8"/>
     </row>
     <row r="113" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A113" s="20" t="s">
+      <c r="A113" s="21" t="s">
         <v>47</v>
       </c>
-      <c r="B113" s="19" t="s">
+      <c r="B113" s="20" t="s">
         <v>5</v>
       </c>
-      <c r="C113" s="19">
+      <c r="C113" s="20">
         <v>9991004</v>
       </c>
-      <c r="D113" s="19"/>
-      <c r="E113" s="19"/>
-      <c r="F113" s="19">
+      <c r="D113" s="20"/>
+      <c r="E113" s="20"/>
+      <c r="F113" s="20">
         <v>2208434</v>
       </c>
-      <c r="G113" s="19" t="s">
+      <c r="G113" s="20" t="s">
         <v>105</v>
       </c>
-      <c r="H113" s="19">
-        <v>2</v>
-      </c>
-      <c r="I113" s="19"/>
-      <c r="J113" s="19"/>
+      <c r="H113" s="20">
+        <v>2</v>
+      </c>
+      <c r="I113" s="20"/>
+      <c r="J113" s="20"/>
     </row>
     <row r="114" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A114" s="18" t="s">
+      <c r="A114" s="19" t="s">
         <v>45</v>
       </c>
-      <c r="B114" s="18" t="s">
+      <c r="B114" s="19" t="s">
         <v>5</v>
       </c>
-      <c r="C114" s="18">
+      <c r="C114" s="19">
         <v>9991004</v>
       </c>
-      <c r="D114" s="18"/>
-      <c r="E114" s="18">
-        <v>4</v>
-      </c>
-      <c r="F114" s="18"/>
-      <c r="G114" s="18"/>
-      <c r="H114" s="18">
-        <v>2</v>
-      </c>
-      <c r="I114" s="18">
-        <v>2</v>
-      </c>
-      <c r="J114" s="18">
+      <c r="D114" s="19"/>
+      <c r="E114" s="19">
+        <v>4</v>
+      </c>
+      <c r="F114" s="19"/>
+      <c r="G114" s="19"/>
+      <c r="H114" s="19">
+        <v>2</v>
+      </c>
+      <c r="I114" s="19">
+        <v>2</v>
+      </c>
+      <c r="J114" s="19">
         <v>3</v>
       </c>
     </row>
@@ -4220,52 +4327,52 @@
       <c r="J115" s="7"/>
     </row>
     <row r="116" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A116" s="20" t="s">
+      <c r="A116" s="21" t="s">
         <v>47</v>
       </c>
-      <c r="B116" s="19" t="s">
+      <c r="B116" s="20" t="s">
         <v>6</v>
       </c>
-      <c r="C116" s="19">
+      <c r="C116" s="20">
         <v>9991005</v>
       </c>
-      <c r="D116" s="19"/>
-      <c r="E116" s="19"/>
-      <c r="F116" s="19">
+      <c r="D116" s="20"/>
+      <c r="E116" s="20"/>
+      <c r="F116" s="20">
         <v>2208492</v>
       </c>
-      <c r="G116" s="19" t="s">
+      <c r="G116" s="20" t="s">
         <v>107</v>
       </c>
-      <c r="H116" s="19">
-        <v>1</v>
-      </c>
-      <c r="I116" s="19"/>
-      <c r="J116" s="19"/>
+      <c r="H116" s="20">
+        <v>1</v>
+      </c>
+      <c r="I116" s="20"/>
+      <c r="J116" s="20"/>
     </row>
     <row r="117" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A117" s="21" t="s">
+      <c r="A117" s="22" t="s">
         <v>45</v>
       </c>
-      <c r="B117" s="21" t="s">
+      <c r="B117" s="22" t="s">
         <v>6</v>
       </c>
-      <c r="C117" s="21">
+      <c r="C117" s="22">
         <v>9991005</v>
       </c>
-      <c r="D117" s="21"/>
-      <c r="E117" s="21">
-        <v>1</v>
-      </c>
-      <c r="F117" s="21"/>
-      <c r="G117" s="21"/>
-      <c r="H117" s="21">
-        <v>1</v>
-      </c>
-      <c r="I117" s="21">
+      <c r="D117" s="22"/>
+      <c r="E117" s="22">
+        <v>1</v>
+      </c>
+      <c r="F117" s="22"/>
+      <c r="G117" s="22"/>
+      <c r="H117" s="22">
+        <v>1</v>
+      </c>
+      <c r="I117" s="22">
         <v>0</v>
       </c>
-      <c r="J117" s="21"/>
+      <c r="J117" s="22"/>
     </row>
     <row r="118" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A118" s="7" t="s">
@@ -4312,44 +4419,44 @@
       <c r="J119" s="8"/>
     </row>
     <row r="120" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A120" s="18" t="s">
+      <c r="A120" s="19" t="s">
         <v>45</v>
       </c>
-      <c r="B120" s="18" t="s">
+      <c r="B120" s="19" t="s">
         <v>8</v>
       </c>
-      <c r="C120" s="18">
+      <c r="C120" s="19">
         <v>9991007</v>
       </c>
-      <c r="D120" s="18"/>
-      <c r="E120" s="18">
+      <c r="D120" s="19"/>
+      <c r="E120" s="19">
         <v>6</v>
       </c>
-      <c r="F120" s="18"/>
-      <c r="G120" s="18"/>
-      <c r="H120" s="18">
+      <c r="F120" s="19"/>
+      <c r="G120" s="19"/>
+      <c r="H120" s="19">
         <v>0</v>
       </c>
-      <c r="I120" s="18">
+      <c r="I120" s="19">
         <v>6</v>
       </c>
-      <c r="J120" s="18">
+      <c r="J120" s="19">
         <v>6</v>
       </c>
     </row>
     <row r="122" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A122" s="16" t="s">
+      <c r="A122" s="17" t="s">
         <v>110</v>
       </c>
-      <c r="B122" s="16"/>
-      <c r="C122" s="16"/>
-      <c r="D122" s="16"/>
-      <c r="E122" s="16"/>
-      <c r="F122" s="16"/>
-      <c r="G122" s="16"/>
-      <c r="H122" s="16"/>
-      <c r="I122" s="16"/>
-      <c r="J122" s="16"/>
+      <c r="B122" s="17"/>
+      <c r="C122" s="17"/>
+      <c r="D122" s="17"/>
+      <c r="E122" s="17"/>
+      <c r="F122" s="17"/>
+      <c r="G122" s="17"/>
+      <c r="H122" s="17"/>
+      <c r="I122" s="17"/>
+      <c r="J122" s="17"/>
     </row>
     <row r="123" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A123" s="7" t="s">
@@ -4361,7 +4468,7 @@
       <c r="C123" s="7">
         <v>9991002</v>
       </c>
-      <c r="D123" s="17">
+      <c r="D123" s="18">
         <v>46176</v>
       </c>
       <c r="E123" s="7">
@@ -4374,52 +4481,52 @@
       <c r="J123" s="7"/>
     </row>
     <row r="124" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A124" s="20" t="s">
+      <c r="A124" s="21" t="s">
         <v>47</v>
       </c>
-      <c r="B124" s="19" t="s">
-        <v>3</v>
-      </c>
-      <c r="C124" s="19">
+      <c r="B124" s="20" t="s">
+        <v>3</v>
+      </c>
+      <c r="C124" s="20">
         <v>9991002</v>
       </c>
-      <c r="D124" s="19"/>
-      <c r="E124" s="19"/>
-      <c r="F124" s="19">
+      <c r="D124" s="20"/>
+      <c r="E124" s="20"/>
+      <c r="F124" s="20">
         <v>2312658</v>
       </c>
-      <c r="G124" s="22">
+      <c r="G124" s="23">
         <v>46176</v>
       </c>
-      <c r="H124" s="19">
-        <v>2</v>
-      </c>
-      <c r="I124" s="19"/>
-      <c r="J124" s="19"/>
+      <c r="H124" s="20">
+        <v>2</v>
+      </c>
+      <c r="I124" s="20"/>
+      <c r="J124" s="20"/>
     </row>
     <row r="125" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A125" s="21" t="s">
+      <c r="A125" s="22" t="s">
         <v>45</v>
       </c>
-      <c r="B125" s="21" t="s">
-        <v>3</v>
-      </c>
-      <c r="C125" s="21">
+      <c r="B125" s="22" t="s">
+        <v>3</v>
+      </c>
+      <c r="C125" s="22">
         <v>9991002</v>
       </c>
-      <c r="D125" s="21"/>
-      <c r="E125" s="21">
-        <v>2</v>
-      </c>
-      <c r="F125" s="21"/>
-      <c r="G125" s="21"/>
-      <c r="H125" s="21">
-        <v>2</v>
-      </c>
-      <c r="I125" s="21">
+      <c r="D125" s="22"/>
+      <c r="E125" s="22">
+        <v>2</v>
+      </c>
+      <c r="F125" s="22"/>
+      <c r="G125" s="22"/>
+      <c r="H125" s="22">
+        <v>2</v>
+      </c>
+      <c r="I125" s="22">
         <v>0</v>
       </c>
-      <c r="J125" s="21"/>
+      <c r="J125" s="22"/>
     </row>
     <row r="126" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A126" s="7" t="s">
@@ -4466,52 +4573,52 @@
       <c r="J127" s="8"/>
     </row>
     <row r="128" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A128" s="20" t="s">
+      <c r="A128" s="21" t="s">
         <v>47</v>
       </c>
-      <c r="B128" s="19" t="s">
+      <c r="B128" s="20" t="s">
         <v>5</v>
       </c>
-      <c r="C128" s="19">
+      <c r="C128" s="20">
         <v>9991004</v>
       </c>
-      <c r="D128" s="19"/>
-      <c r="E128" s="19"/>
-      <c r="F128" s="19">
+      <c r="D128" s="20"/>
+      <c r="E128" s="20"/>
+      <c r="F128" s="20">
         <v>2312551</v>
       </c>
-      <c r="G128" s="22">
+      <c r="G128" s="23">
         <v>46083</v>
       </c>
-      <c r="H128" s="19">
+      <c r="H128" s="20">
         <v>5</v>
       </c>
-      <c r="I128" s="19"/>
-      <c r="J128" s="19"/>
+      <c r="I128" s="20"/>
+      <c r="J128" s="20"/>
     </row>
     <row r="129" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A129" s="21" t="s">
+      <c r="A129" s="22" t="s">
         <v>45</v>
       </c>
-      <c r="B129" s="21" t="s">
+      <c r="B129" s="22" t="s">
         <v>5</v>
       </c>
-      <c r="C129" s="21">
+      <c r="C129" s="22">
         <v>9991004</v>
       </c>
-      <c r="D129" s="21"/>
-      <c r="E129" s="21">
+      <c r="D129" s="22"/>
+      <c r="E129" s="22">
         <v>5</v>
       </c>
-      <c r="F129" s="21"/>
-      <c r="G129" s="21"/>
-      <c r="H129" s="21">
+      <c r="F129" s="22"/>
+      <c r="G129" s="22"/>
+      <c r="H129" s="22">
         <v>5</v>
       </c>
-      <c r="I129" s="21">
+      <c r="I129" s="22">
         <v>0</v>
       </c>
-      <c r="J129" s="21"/>
+      <c r="J129" s="22"/>
     </row>
     <row r="130" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A130" s="7" t="s">
@@ -4536,52 +4643,52 @@
       <c r="J130" s="7"/>
     </row>
     <row r="131" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A131" s="20" t="s">
+      <c r="A131" s="21" t="s">
         <v>47</v>
       </c>
-      <c r="B131" s="19" t="s">
+      <c r="B131" s="20" t="s">
         <v>6</v>
       </c>
-      <c r="C131" s="19">
+      <c r="C131" s="20">
         <v>9991005</v>
       </c>
-      <c r="D131" s="19"/>
-      <c r="E131" s="19"/>
-      <c r="F131" s="19">
+      <c r="D131" s="20"/>
+      <c r="E131" s="20"/>
+      <c r="F131" s="20">
         <v>2312747</v>
       </c>
-      <c r="G131" s="22">
+      <c r="G131" s="23">
         <v>46057</v>
       </c>
-      <c r="H131" s="19">
-        <v>1</v>
-      </c>
-      <c r="I131" s="19"/>
-      <c r="J131" s="19"/>
+      <c r="H131" s="20">
+        <v>1</v>
+      </c>
+      <c r="I131" s="20"/>
+      <c r="J131" s="20"/>
     </row>
     <row r="132" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A132" s="21" t="s">
+      <c r="A132" s="22" t="s">
         <v>45</v>
       </c>
-      <c r="B132" s="21" t="s">
+      <c r="B132" s="22" t="s">
         <v>6</v>
       </c>
-      <c r="C132" s="21">
+      <c r="C132" s="22">
         <v>9991005</v>
       </c>
-      <c r="D132" s="21"/>
-      <c r="E132" s="21">
-        <v>1</v>
-      </c>
-      <c r="F132" s="21"/>
-      <c r="G132" s="21"/>
-      <c r="H132" s="21">
-        <v>1</v>
-      </c>
-      <c r="I132" s="21">
+      <c r="D132" s="22"/>
+      <c r="E132" s="22">
+        <v>1</v>
+      </c>
+      <c r="F132" s="22"/>
+      <c r="G132" s="22"/>
+      <c r="H132" s="22">
+        <v>1</v>
+      </c>
+      <c r="I132" s="22">
         <v>0</v>
       </c>
-      <c r="J132" s="21"/>
+      <c r="J132" s="22"/>
     </row>
     <row r="133" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A133" s="7" t="s">
@@ -4593,7 +4700,7 @@
       <c r="C133" s="7">
         <v>9991006</v>
       </c>
-      <c r="D133" s="17">
+      <c r="D133" s="18">
         <v>46176</v>
       </c>
       <c r="E133" s="7">
@@ -4606,28 +4713,28 @@
       <c r="J133" s="7"/>
     </row>
     <row r="134" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A134" s="18" t="s">
+      <c r="A134" s="19" t="s">
         <v>45</v>
       </c>
-      <c r="B134" s="18" t="s">
+      <c r="B134" s="19" t="s">
         <v>7</v>
       </c>
-      <c r="C134" s="18">
+      <c r="C134" s="19">
         <v>9991006</v>
       </c>
-      <c r="D134" s="18"/>
-      <c r="E134" s="18">
-        <v>1</v>
-      </c>
-      <c r="F134" s="18"/>
-      <c r="G134" s="18"/>
-      <c r="H134" s="18">
+      <c r="D134" s="19"/>
+      <c r="E134" s="19">
+        <v>1</v>
+      </c>
+      <c r="F134" s="19"/>
+      <c r="G134" s="19"/>
+      <c r="H134" s="19">
         <v>0</v>
       </c>
-      <c r="I134" s="18">
-        <v>1</v>
-      </c>
-      <c r="J134" s="18"/>
+      <c r="I134" s="19">
+        <v>1</v>
+      </c>
+      <c r="J134" s="19"/>
     </row>
     <row r="135" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A135" s="7" t="s">
@@ -4674,128 +4781,128 @@
       <c r="J136" s="8"/>
     </row>
     <row r="137" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A137" s="20" t="s">
+      <c r="A137" s="21" t="s">
         <v>47</v>
       </c>
-      <c r="B137" s="19" t="s">
+      <c r="B137" s="20" t="s">
         <v>8</v>
       </c>
-      <c r="C137" s="19">
+      <c r="C137" s="20">
         <v>9991007</v>
       </c>
-      <c r="D137" s="19"/>
-      <c r="E137" s="19"/>
-      <c r="F137" s="19">
+      <c r="D137" s="20"/>
+      <c r="E137" s="20"/>
+      <c r="F137" s="20">
         <v>2312747</v>
       </c>
-      <c r="G137" s="22">
+      <c r="G137" s="23">
         <v>46057</v>
       </c>
-      <c r="H137" s="19">
-        <v>2</v>
-      </c>
-      <c r="I137" s="19"/>
-      <c r="J137" s="19"/>
+      <c r="H137" s="20">
+        <v>2</v>
+      </c>
+      <c r="I137" s="20"/>
+      <c r="J137" s="20"/>
     </row>
     <row r="138" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A138" s="20" t="s">
+      <c r="A138" s="21" t="s">
         <v>47</v>
       </c>
-      <c r="B138" s="19" t="s">
+      <c r="B138" s="20" t="s">
         <v>8</v>
       </c>
-      <c r="C138" s="19">
+      <c r="C138" s="20">
         <v>9991007</v>
       </c>
-      <c r="D138" s="19"/>
-      <c r="E138" s="19"/>
-      <c r="F138" s="19">
+      <c r="D138" s="20"/>
+      <c r="E138" s="20"/>
+      <c r="F138" s="20">
         <v>2312888</v>
       </c>
-      <c r="G138" s="19" t="s">
+      <c r="G138" s="20" t="s">
         <v>118</v>
       </c>
-      <c r="H138" s="19">
-        <v>3</v>
-      </c>
-      <c r="I138" s="19"/>
-      <c r="J138" s="19"/>
+      <c r="H138" s="20">
+        <v>3</v>
+      </c>
+      <c r="I138" s="20"/>
+      <c r="J138" s="20"/>
     </row>
     <row r="139" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A139" s="21" t="s">
+      <c r="A139" s="22" t="s">
         <v>45</v>
       </c>
-      <c r="B139" s="21" t="s">
+      <c r="B139" s="22" t="s">
         <v>8</v>
       </c>
-      <c r="C139" s="21">
+      <c r="C139" s="22">
         <v>9991007</v>
       </c>
-      <c r="D139" s="21"/>
-      <c r="E139" s="21">
+      <c r="D139" s="22"/>
+      <c r="E139" s="22">
         <v>5</v>
       </c>
-      <c r="F139" s="21"/>
-      <c r="G139" s="21"/>
-      <c r="H139" s="21">
+      <c r="F139" s="22"/>
+      <c r="G139" s="22"/>
+      <c r="H139" s="22">
         <v>5</v>
       </c>
-      <c r="I139" s="21">
+      <c r="I139" s="22">
         <v>0</v>
       </c>
-      <c r="J139" s="21"/>
+      <c r="J139" s="22"/>
     </row>
     <row r="141" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A141" s="16" t="s">
+      <c r="A141" s="17" t="s">
         <v>119</v>
       </c>
-      <c r="B141" s="16"/>
-      <c r="C141" s="16"/>
-      <c r="D141" s="16"/>
-      <c r="E141" s="16"/>
-      <c r="F141" s="16"/>
-      <c r="G141" s="16"/>
-      <c r="H141" s="16"/>
-      <c r="I141" s="16"/>
-      <c r="J141" s="16"/>
+      <c r="B141" s="17"/>
+      <c r="C141" s="17"/>
+      <c r="D141" s="17"/>
+      <c r="E141" s="17"/>
+      <c r="F141" s="17"/>
+      <c r="G141" s="17"/>
+      <c r="H141" s="17"/>
+      <c r="I141" s="17"/>
+      <c r="J141" s="17"/>
     </row>
     <row r="142" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A142" s="21" t="s">
+      <c r="A142" s="22" t="s">
         <v>45</v>
       </c>
-      <c r="B142" s="21">
+      <c r="B142" s="22">
         <v>99910019991001</v>
       </c>
-      <c r="C142" s="21">
+      <c r="C142" s="22">
         <v>99910019991001</v>
       </c>
-      <c r="D142" s="21"/>
-      <c r="E142" s="21">
+      <c r="D142" s="22"/>
+      <c r="E142" s="22">
         <v>0</v>
       </c>
-      <c r="F142" s="21"/>
-      <c r="G142" s="21"/>
-      <c r="H142" s="21">
+      <c r="F142" s="22"/>
+      <c r="G142" s="22"/>
+      <c r="H142" s="22">
         <v>0</v>
       </c>
-      <c r="I142" s="21">
+      <c r="I142" s="22">
         <v>0</v>
       </c>
-      <c r="J142" s="21"/>
+      <c r="J142" s="22"/>
     </row>
     <row r="144" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A144" s="16" t="s">
+      <c r="A144" s="17" t="s">
         <v>20</v>
       </c>
-      <c r="B144" s="16"/>
-      <c r="C144" s="16"/>
-      <c r="D144" s="16"/>
-      <c r="E144" s="16"/>
-      <c r="F144" s="16"/>
-      <c r="G144" s="16"/>
-      <c r="H144" s="16"/>
-      <c r="I144" s="16"/>
-      <c r="J144" s="16"/>
+      <c r="B144" s="17"/>
+      <c r="C144" s="17"/>
+      <c r="D144" s="17"/>
+      <c r="E144" s="17"/>
+      <c r="F144" s="17"/>
+      <c r="G144" s="17"/>
+      <c r="H144" s="17"/>
+      <c r="I144" s="17"/>
+      <c r="J144" s="17"/>
     </row>
     <row r="145" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A145" s="7" t="s">
@@ -4820,52 +4927,52 @@
       <c r="J145" s="7"/>
     </row>
     <row r="146" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A146" s="20" t="s">
+      <c r="A146" s="21" t="s">
         <v>47</v>
       </c>
-      <c r="B146" s="19" t="s">
-        <v>3</v>
-      </c>
-      <c r="C146" s="19">
+      <c r="B146" s="20" t="s">
+        <v>3</v>
+      </c>
+      <c r="C146" s="20">
         <v>9991002</v>
       </c>
-      <c r="D146" s="19"/>
-      <c r="E146" s="19"/>
-      <c r="F146" s="19">
+      <c r="D146" s="20"/>
+      <c r="E146" s="20"/>
+      <c r="F146" s="20">
         <v>27012316</v>
       </c>
-      <c r="G146" s="22">
+      <c r="G146" s="23">
         <v>46083</v>
       </c>
-      <c r="H146" s="19">
-        <v>2</v>
-      </c>
-      <c r="I146" s="19"/>
-      <c r="J146" s="19"/>
+      <c r="H146" s="20">
+        <v>2</v>
+      </c>
+      <c r="I146" s="20"/>
+      <c r="J146" s="20"/>
     </row>
     <row r="147" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A147" s="21" t="s">
+      <c r="A147" s="22" t="s">
         <v>45</v>
       </c>
-      <c r="B147" s="21" t="s">
-        <v>3</v>
-      </c>
-      <c r="C147" s="21">
+      <c r="B147" s="22" t="s">
+        <v>3</v>
+      </c>
+      <c r="C147" s="22">
         <v>9991002</v>
       </c>
-      <c r="D147" s="21"/>
-      <c r="E147" s="21">
-        <v>2</v>
-      </c>
-      <c r="F147" s="21"/>
-      <c r="G147" s="21"/>
-      <c r="H147" s="21">
-        <v>2</v>
-      </c>
-      <c r="I147" s="21">
+      <c r="D147" s="22"/>
+      <c r="E147" s="22">
+        <v>2</v>
+      </c>
+      <c r="F147" s="22"/>
+      <c r="G147" s="22"/>
+      <c r="H147" s="22">
+        <v>2</v>
+      </c>
+      <c r="I147" s="22">
         <v>0</v>
       </c>
-      <c r="J147" s="21"/>
+      <c r="J147" s="22"/>
     </row>
     <row r="148" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A148" s="7" t="s">
@@ -4877,7 +4984,7 @@
       <c r="C148" s="7">
         <v>9991003</v>
       </c>
-      <c r="D148" s="17">
+      <c r="D148" s="18">
         <v>46176</v>
       </c>
       <c r="E148" s="7">
@@ -4899,7 +5006,7 @@
       <c r="C149" s="8">
         <v>9991003</v>
       </c>
-      <c r="D149" s="23">
+      <c r="D149" s="24">
         <v>46207</v>
       </c>
       <c r="E149" s="8">
@@ -4912,28 +5019,28 @@
       <c r="J149" s="8"/>
     </row>
     <row r="150" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A150" s="18" t="s">
+      <c r="A150" s="19" t="s">
         <v>45</v>
       </c>
-      <c r="B150" s="18" t="s">
-        <v>4</v>
-      </c>
-      <c r="C150" s="18">
+      <c r="B150" s="19" t="s">
+        <v>4</v>
+      </c>
+      <c r="C150" s="19">
         <v>9991003</v>
       </c>
-      <c r="D150" s="18"/>
-      <c r="E150" s="18">
+      <c r="D150" s="19"/>
+      <c r="E150" s="19">
         <v>6</v>
       </c>
-      <c r="F150" s="18"/>
-      <c r="G150" s="18"/>
-      <c r="H150" s="18">
+      <c r="F150" s="19"/>
+      <c r="G150" s="19"/>
+      <c r="H150" s="19">
         <v>0</v>
       </c>
-      <c r="I150" s="18">
+      <c r="I150" s="19">
         <v>6</v>
       </c>
-      <c r="J150" s="18">
+      <c r="J150" s="19">
         <v>6</v>
       </c>
     </row>
@@ -4947,7 +5054,7 @@
       <c r="C151" s="7">
         <v>9991005</v>
       </c>
-      <c r="D151" s="17">
+      <c r="D151" s="18">
         <v>46207</v>
       </c>
       <c r="E151" s="7">
@@ -4960,52 +5067,52 @@
       <c r="J151" s="7"/>
     </row>
     <row r="152" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A152" s="20" t="s">
+      <c r="A152" s="21" t="s">
         <v>47</v>
       </c>
-      <c r="B152" s="19" t="s">
+      <c r="B152" s="20" t="s">
         <v>6</v>
       </c>
-      <c r="C152" s="19">
+      <c r="C152" s="20">
         <v>9991005</v>
       </c>
-      <c r="D152" s="19"/>
-      <c r="E152" s="19"/>
-      <c r="F152" s="19">
+      <c r="D152" s="20"/>
+      <c r="E152" s="20"/>
+      <c r="F152" s="20">
         <v>27012553</v>
       </c>
-      <c r="G152" s="19" t="s">
+      <c r="G152" s="20" t="s">
         <v>124</v>
       </c>
-      <c r="H152" s="19">
-        <v>1</v>
-      </c>
-      <c r="I152" s="19"/>
-      <c r="J152" s="19"/>
+      <c r="H152" s="20">
+        <v>1</v>
+      </c>
+      <c r="I152" s="20"/>
+      <c r="J152" s="20"/>
     </row>
     <row r="153" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A153" s="21" t="s">
+      <c r="A153" s="22" t="s">
         <v>45</v>
       </c>
-      <c r="B153" s="21" t="s">
+      <c r="B153" s="22" t="s">
         <v>6</v>
       </c>
-      <c r="C153" s="21">
+      <c r="C153" s="22">
         <v>9991005</v>
       </c>
-      <c r="D153" s="21"/>
-      <c r="E153" s="21">
-        <v>1</v>
-      </c>
-      <c r="F153" s="21"/>
-      <c r="G153" s="21"/>
-      <c r="H153" s="21">
-        <v>1</v>
-      </c>
-      <c r="I153" s="21">
+      <c r="D153" s="22"/>
+      <c r="E153" s="22">
+        <v>1</v>
+      </c>
+      <c r="F153" s="22"/>
+      <c r="G153" s="22"/>
+      <c r="H153" s="22">
+        <v>1</v>
+      </c>
+      <c r="I153" s="22">
         <v>0</v>
       </c>
-      <c r="J153" s="21"/>
+      <c r="J153" s="22"/>
     </row>
     <row r="154" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A154" s="7" t="s">
@@ -5017,7 +5124,7 @@
       <c r="C154" s="7">
         <v>9991006</v>
       </c>
-      <c r="D154" s="17">
+      <c r="D154" s="18">
         <v>46207</v>
       </c>
       <c r="E154" s="7">
@@ -5030,66 +5137,66 @@
       <c r="J154" s="7"/>
     </row>
     <row r="155" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A155" s="20" t="s">
+      <c r="A155" s="21" t="s">
         <v>47</v>
       </c>
-      <c r="B155" s="19" t="s">
+      <c r="B155" s="20" t="s">
         <v>7</v>
       </c>
-      <c r="C155" s="19">
+      <c r="C155" s="20">
         <v>9991006</v>
       </c>
-      <c r="D155" s="19"/>
-      <c r="E155" s="19"/>
-      <c r="F155" s="19">
+      <c r="D155" s="20"/>
+      <c r="E155" s="20"/>
+      <c r="F155" s="20">
         <v>27012562</v>
       </c>
-      <c r="G155" s="19" t="s">
+      <c r="G155" s="20" t="s">
         <v>81</v>
       </c>
-      <c r="H155" s="19">
-        <v>2</v>
-      </c>
-      <c r="I155" s="19"/>
-      <c r="J155" s="19"/>
+      <c r="H155" s="20">
+        <v>2</v>
+      </c>
+      <c r="I155" s="20"/>
+      <c r="J155" s="20"/>
     </row>
     <row r="156" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A156" s="21" t="s">
+      <c r="A156" s="22" t="s">
         <v>45</v>
       </c>
-      <c r="B156" s="21" t="s">
+      <c r="B156" s="22" t="s">
         <v>7</v>
       </c>
-      <c r="C156" s="21">
+      <c r="C156" s="22">
         <v>9991006</v>
       </c>
-      <c r="D156" s="21"/>
-      <c r="E156" s="21">
-        <v>2</v>
-      </c>
-      <c r="F156" s="21"/>
-      <c r="G156" s="21"/>
-      <c r="H156" s="21">
-        <v>2</v>
-      </c>
-      <c r="I156" s="21">
+      <c r="D156" s="22"/>
+      <c r="E156" s="22">
+        <v>2</v>
+      </c>
+      <c r="F156" s="22"/>
+      <c r="G156" s="22"/>
+      <c r="H156" s="22">
+        <v>2</v>
+      </c>
+      <c r="I156" s="22">
         <v>0</v>
       </c>
-      <c r="J156" s="21"/>
+      <c r="J156" s="22"/>
     </row>
     <row r="158" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A158" s="16" t="s">
+      <c r="A158" s="17" t="s">
         <v>21</v>
       </c>
-      <c r="B158" s="16"/>
-      <c r="C158" s="16"/>
-      <c r="D158" s="16"/>
-      <c r="E158" s="16"/>
-      <c r="F158" s="16"/>
-      <c r="G158" s="16"/>
-      <c r="H158" s="16"/>
-      <c r="I158" s="16"/>
-      <c r="J158" s="16"/>
+      <c r="B158" s="17"/>
+      <c r="C158" s="17"/>
+      <c r="D158" s="17"/>
+      <c r="E158" s="17"/>
+      <c r="F158" s="17"/>
+      <c r="G158" s="17"/>
+      <c r="H158" s="17"/>
+      <c r="I158" s="17"/>
+      <c r="J158" s="17"/>
     </row>
     <row r="159" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A159" s="7" t="s">
@@ -5114,52 +5221,52 @@
       <c r="J159" s="7"/>
     </row>
     <row r="160" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A160" s="20" t="s">
+      <c r="A160" s="21" t="s">
         <v>47</v>
       </c>
-      <c r="B160" s="19" t="s">
-        <v>3</v>
-      </c>
-      <c r="C160" s="19">
+      <c r="B160" s="20" t="s">
+        <v>3</v>
+      </c>
+      <c r="C160" s="20">
         <v>9991002</v>
       </c>
-      <c r="D160" s="19"/>
-      <c r="E160" s="19"/>
-      <c r="F160" s="19">
+      <c r="D160" s="20"/>
+      <c r="E160" s="20"/>
+      <c r="F160" s="20">
         <v>2811971</v>
       </c>
-      <c r="G160" s="19" t="s">
+      <c r="G160" s="20" t="s">
         <v>100</v>
       </c>
-      <c r="H160" s="19">
-        <v>1</v>
-      </c>
-      <c r="I160" s="19"/>
-      <c r="J160" s="19"/>
+      <c r="H160" s="20">
+        <v>1</v>
+      </c>
+      <c r="I160" s="20"/>
+      <c r="J160" s="20"/>
     </row>
     <row r="161" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A161" s="21" t="s">
+      <c r="A161" s="22" t="s">
         <v>45</v>
       </c>
-      <c r="B161" s="21" t="s">
-        <v>3</v>
-      </c>
-      <c r="C161" s="21">
+      <c r="B161" s="22" t="s">
+        <v>3</v>
+      </c>
+      <c r="C161" s="22">
         <v>9991002</v>
       </c>
-      <c r="D161" s="21"/>
-      <c r="E161" s="21">
-        <v>1</v>
-      </c>
-      <c r="F161" s="21"/>
-      <c r="G161" s="21"/>
-      <c r="H161" s="21">
-        <v>1</v>
-      </c>
-      <c r="I161" s="21">
+      <c r="D161" s="22"/>
+      <c r="E161" s="22">
+        <v>1</v>
+      </c>
+      <c r="F161" s="22"/>
+      <c r="G161" s="22"/>
+      <c r="H161" s="22">
+        <v>1</v>
+      </c>
+      <c r="I161" s="22">
         <v>0</v>
       </c>
-      <c r="J161" s="21"/>
+      <c r="J161" s="22"/>
     </row>
     <row r="162" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A162" s="7" t="s">
@@ -5184,52 +5291,52 @@
       <c r="J162" s="7"/>
     </row>
     <row r="163" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A163" s="20" t="s">
+      <c r="A163" s="21" t="s">
         <v>47</v>
       </c>
-      <c r="B163" s="19" t="s">
+      <c r="B163" s="20" t="s">
         <v>5</v>
       </c>
-      <c r="C163" s="19">
+      <c r="C163" s="20">
         <v>9991004</v>
       </c>
-      <c r="D163" s="19"/>
-      <c r="E163" s="19"/>
-      <c r="F163" s="19">
+      <c r="D163" s="20"/>
+      <c r="E163" s="20"/>
+      <c r="F163" s="20">
         <v>2811953</v>
       </c>
-      <c r="G163" s="22">
+      <c r="G163" s="23">
         <v>46205</v>
       </c>
-      <c r="H163" s="19">
-        <v>3</v>
-      </c>
-      <c r="I163" s="19"/>
-      <c r="J163" s="19"/>
+      <c r="H163" s="20">
+        <v>3</v>
+      </c>
+      <c r="I163" s="20"/>
+      <c r="J163" s="20"/>
     </row>
     <row r="164" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A164" s="21" t="s">
+      <c r="A164" s="22" t="s">
         <v>45</v>
       </c>
-      <c r="B164" s="21" t="s">
+      <c r="B164" s="22" t="s">
         <v>5</v>
       </c>
-      <c r="C164" s="21">
+      <c r="C164" s="22">
         <v>9991004</v>
       </c>
-      <c r="D164" s="21"/>
-      <c r="E164" s="21">
-        <v>3</v>
-      </c>
-      <c r="F164" s="21"/>
-      <c r="G164" s="21"/>
-      <c r="H164" s="21">
-        <v>3</v>
-      </c>
-      <c r="I164" s="21">
+      <c r="D164" s="22"/>
+      <c r="E164" s="22">
+        <v>3</v>
+      </c>
+      <c r="F164" s="22"/>
+      <c r="G164" s="22"/>
+      <c r="H164" s="22">
+        <v>3</v>
+      </c>
+      <c r="I164" s="22">
         <v>0</v>
       </c>
-      <c r="J164" s="21"/>
+      <c r="J164" s="22"/>
     </row>
     <row r="165" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A165" s="7" t="s">
@@ -5254,44 +5361,44 @@
       <c r="J165" s="7"/>
     </row>
     <row r="166" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A166" s="18" t="s">
+      <c r="A166" s="19" t="s">
         <v>45</v>
       </c>
-      <c r="B166" s="18" t="s">
+      <c r="B166" s="19" t="s">
         <v>7</v>
       </c>
-      <c r="C166" s="18">
+      <c r="C166" s="19">
         <v>9991006</v>
       </c>
-      <c r="D166" s="18"/>
-      <c r="E166" s="18">
-        <v>1</v>
-      </c>
-      <c r="F166" s="18"/>
-      <c r="G166" s="18"/>
-      <c r="H166" s="18">
+      <c r="D166" s="19"/>
+      <c r="E166" s="19">
+        <v>1</v>
+      </c>
+      <c r="F166" s="19"/>
+      <c r="G166" s="19"/>
+      <c r="H166" s="19">
         <v>0</v>
       </c>
-      <c r="I166" s="18">
-        <v>1</v>
-      </c>
-      <c r="J166" s="18">
+      <c r="I166" s="19">
+        <v>1</v>
+      </c>
+      <c r="J166" s="19">
         <v>1</v>
       </c>
     </row>
     <row r="168" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A168" s="16" t="s">
+      <c r="A168" s="17" t="s">
         <v>22</v>
       </c>
-      <c r="B168" s="16"/>
-      <c r="C168" s="16"/>
-      <c r="D168" s="16"/>
-      <c r="E168" s="16"/>
-      <c r="F168" s="16"/>
-      <c r="G168" s="16"/>
-      <c r="H168" s="16"/>
-      <c r="I168" s="16"/>
-      <c r="J168" s="16"/>
+      <c r="B168" s="17"/>
+      <c r="C168" s="17"/>
+      <c r="D168" s="17"/>
+      <c r="E168" s="17"/>
+      <c r="F168" s="17"/>
+      <c r="G168" s="17"/>
+      <c r="H168" s="17"/>
+      <c r="I168" s="17"/>
+      <c r="J168" s="17"/>
     </row>
     <row r="169" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A169" s="7" t="s">
@@ -5338,68 +5445,68 @@
       <c r="J170" s="8"/>
     </row>
     <row r="171" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A171" s="20" t="s">
+      <c r="A171" s="21" t="s">
         <v>47</v>
       </c>
-      <c r="B171" s="19" t="s">
-        <v>3</v>
-      </c>
-      <c r="C171" s="19">
+      <c r="B171" s="20" t="s">
+        <v>3</v>
+      </c>
+      <c r="C171" s="20">
         <v>9991002</v>
       </c>
-      <c r="D171" s="19"/>
-      <c r="E171" s="19"/>
-      <c r="F171" s="19">
+      <c r="D171" s="20"/>
+      <c r="E171" s="20"/>
+      <c r="F171" s="20">
         <v>2911604</v>
       </c>
-      <c r="G171" s="22">
+      <c r="G171" s="23">
         <v>46208</v>
       </c>
-      <c r="H171" s="19">
-        <v>1</v>
-      </c>
-      <c r="I171" s="19"/>
-      <c r="J171" s="19"/>
+      <c r="H171" s="20">
+        <v>1</v>
+      </c>
+      <c r="I171" s="20"/>
+      <c r="J171" s="20"/>
     </row>
     <row r="172" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A172" s="18" t="s">
+      <c r="A172" s="19" t="s">
         <v>45</v>
       </c>
-      <c r="B172" s="18" t="s">
-        <v>3</v>
-      </c>
-      <c r="C172" s="18">
+      <c r="B172" s="19" t="s">
+        <v>3</v>
+      </c>
+      <c r="C172" s="19">
         <v>9991002</v>
       </c>
-      <c r="D172" s="18"/>
-      <c r="E172" s="18">
-        <v>2</v>
-      </c>
-      <c r="F172" s="18"/>
-      <c r="G172" s="18"/>
-      <c r="H172" s="18">
-        <v>1</v>
-      </c>
-      <c r="I172" s="18">
-        <v>1</v>
-      </c>
-      <c r="J172" s="18">
+      <c r="D172" s="19"/>
+      <c r="E172" s="19">
+        <v>2</v>
+      </c>
+      <c r="F172" s="19"/>
+      <c r="G172" s="19"/>
+      <c r="H172" s="19">
+        <v>1</v>
+      </c>
+      <c r="I172" s="19">
+        <v>1</v>
+      </c>
+      <c r="J172" s="19">
         <v>1</v>
       </c>
     </row>
     <row r="174" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A174" s="16" t="s">
+      <c r="A174" s="17" t="s">
         <v>23</v>
       </c>
-      <c r="B174" s="16"/>
-      <c r="C174" s="16"/>
-      <c r="D174" s="16"/>
-      <c r="E174" s="16"/>
-      <c r="F174" s="16"/>
-      <c r="G174" s="16"/>
-      <c r="H174" s="16"/>
-      <c r="I174" s="16"/>
-      <c r="J174" s="16"/>
+      <c r="B174" s="17"/>
+      <c r="C174" s="17"/>
+      <c r="D174" s="17"/>
+      <c r="E174" s="17"/>
+      <c r="F174" s="17"/>
+      <c r="G174" s="17"/>
+      <c r="H174" s="17"/>
+      <c r="I174" s="17"/>
+      <c r="J174" s="17"/>
     </row>
     <row r="175" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A175" s="7" t="s">
@@ -5446,52 +5553,52 @@
       <c r="J176" s="8"/>
     </row>
     <row r="177" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A177" s="20" t="s">
+      <c r="A177" s="21" t="s">
         <v>47</v>
       </c>
-      <c r="B177" s="19" t="s">
-        <v>4</v>
-      </c>
-      <c r="C177" s="19">
+      <c r="B177" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="C177" s="20">
         <v>9991003</v>
       </c>
-      <c r="D177" s="19"/>
-      <c r="E177" s="19"/>
-      <c r="F177" s="19">
+      <c r="D177" s="20"/>
+      <c r="E177" s="20"/>
+      <c r="F177" s="20">
         <v>3120260525</v>
       </c>
-      <c r="G177" s="19" t="s">
+      <c r="G177" s="20" t="s">
         <v>43</v>
       </c>
-      <c r="H177" s="19">
+      <c r="H177" s="20">
         <v>5</v>
       </c>
-      <c r="I177" s="19"/>
-      <c r="J177" s="19"/>
+      <c r="I177" s="20"/>
+      <c r="J177" s="20"/>
     </row>
     <row r="178" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A178" s="18" t="s">
+      <c r="A178" s="19" t="s">
         <v>45</v>
       </c>
-      <c r="B178" s="18" t="s">
-        <v>4</v>
-      </c>
-      <c r="C178" s="18">
+      <c r="B178" s="19" t="s">
+        <v>4</v>
+      </c>
+      <c r="C178" s="19">
         <v>9991003</v>
       </c>
-      <c r="D178" s="18"/>
-      <c r="E178" s="18">
+      <c r="D178" s="19"/>
+      <c r="E178" s="19">
         <v>6</v>
       </c>
-      <c r="F178" s="18"/>
-      <c r="G178" s="18"/>
-      <c r="H178" s="18">
+      <c r="F178" s="19"/>
+      <c r="G178" s="19"/>
+      <c r="H178" s="19">
         <v>5</v>
       </c>
-      <c r="I178" s="18">
-        <v>1</v>
-      </c>
-      <c r="J178" s="18">
+      <c r="I178" s="19">
+        <v>1</v>
+      </c>
+      <c r="J178" s="19">
         <v>1</v>
       </c>
     </row>
@@ -5540,66 +5647,66 @@
       <c r="J180" s="8"/>
     </row>
     <row r="181" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A181" s="20" t="s">
+      <c r="A181" s="21" t="s">
         <v>47</v>
       </c>
-      <c r="B181" s="19" t="s">
+      <c r="B181" s="20" t="s">
         <v>8</v>
       </c>
-      <c r="C181" s="19">
+      <c r="C181" s="20">
         <v>9991007</v>
       </c>
-      <c r="D181" s="19"/>
-      <c r="E181" s="19"/>
-      <c r="F181" s="19">
+      <c r="D181" s="20"/>
+      <c r="E181" s="20"/>
+      <c r="F181" s="20">
         <v>3120260205</v>
       </c>
-      <c r="G181" s="22">
+      <c r="G181" s="23">
         <v>46144</v>
       </c>
-      <c r="H181" s="19">
-        <v>3</v>
-      </c>
-      <c r="I181" s="19"/>
-      <c r="J181" s="19"/>
+      <c r="H181" s="20">
+        <v>3</v>
+      </c>
+      <c r="I181" s="20"/>
+      <c r="J181" s="20"/>
     </row>
     <row r="182" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A182" s="21" t="s">
+      <c r="A182" s="22" t="s">
         <v>45</v>
       </c>
-      <c r="B182" s="21" t="s">
+      <c r="B182" s="22" t="s">
         <v>8</v>
       </c>
-      <c r="C182" s="21">
+      <c r="C182" s="22">
         <v>9991007</v>
       </c>
-      <c r="D182" s="21"/>
-      <c r="E182" s="21">
-        <v>3</v>
-      </c>
-      <c r="F182" s="21"/>
-      <c r="G182" s="21"/>
-      <c r="H182" s="21">
-        <v>3</v>
-      </c>
-      <c r="I182" s="21">
+      <c r="D182" s="22"/>
+      <c r="E182" s="22">
+        <v>3</v>
+      </c>
+      <c r="F182" s="22"/>
+      <c r="G182" s="22"/>
+      <c r="H182" s="22">
+        <v>3</v>
+      </c>
+      <c r="I182" s="22">
         <v>0</v>
       </c>
-      <c r="J182" s="21"/>
+      <c r="J182" s="22"/>
     </row>
     <row r="184" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A184" s="16" t="s">
+      <c r="A184" s="17" t="s">
         <v>136</v>
       </c>
-      <c r="B184" s="16"/>
-      <c r="C184" s="16"/>
-      <c r="D184" s="16"/>
-      <c r="E184" s="16"/>
-      <c r="F184" s="16"/>
-      <c r="G184" s="16"/>
-      <c r="H184" s="16"/>
-      <c r="I184" s="16"/>
-      <c r="J184" s="16"/>
+      <c r="B184" s="17"/>
+      <c r="C184" s="17"/>
+      <c r="D184" s="17"/>
+      <c r="E184" s="17"/>
+      <c r="F184" s="17"/>
+      <c r="G184" s="17"/>
+      <c r="H184" s="17"/>
+      <c r="I184" s="17"/>
+      <c r="J184" s="17"/>
     </row>
     <row r="185" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A185" s="7" t="s">
@@ -5624,52 +5731,52 @@
       <c r="J185" s="7"/>
     </row>
     <row r="186" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A186" s="20" t="s">
+      <c r="A186" s="21" t="s">
         <v>47</v>
       </c>
-      <c r="B186" s="19" t="s">
-        <v>2</v>
-      </c>
-      <c r="C186" s="19">
+      <c r="B186" s="20" t="s">
+        <v>2</v>
+      </c>
+      <c r="C186" s="20">
         <v>9991001</v>
       </c>
-      <c r="D186" s="19"/>
-      <c r="E186" s="19"/>
-      <c r="F186" s="19">
+      <c r="D186" s="20"/>
+      <c r="E186" s="20"/>
+      <c r="F186" s="20">
         <v>3211292</v>
       </c>
-      <c r="G186" s="22">
+      <c r="G186" s="23">
         <v>46328</v>
       </c>
-      <c r="H186" s="19">
-        <v>1</v>
-      </c>
-      <c r="I186" s="19"/>
-      <c r="J186" s="19"/>
+      <c r="H186" s="20">
+        <v>1</v>
+      </c>
+      <c r="I186" s="20"/>
+      <c r="J186" s="20"/>
     </row>
     <row r="187" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A187" s="21" t="s">
+      <c r="A187" s="22" t="s">
         <v>45</v>
       </c>
-      <c r="B187" s="21" t="s">
-        <v>2</v>
-      </c>
-      <c r="C187" s="21">
+      <c r="B187" s="22" t="s">
+        <v>2</v>
+      </c>
+      <c r="C187" s="22">
         <v>9991001</v>
       </c>
-      <c r="D187" s="21"/>
-      <c r="E187" s="21">
-        <v>1</v>
-      </c>
-      <c r="F187" s="21"/>
-      <c r="G187" s="21"/>
-      <c r="H187" s="21">
-        <v>1</v>
-      </c>
-      <c r="I187" s="21">
+      <c r="D187" s="22"/>
+      <c r="E187" s="22">
+        <v>1</v>
+      </c>
+      <c r="F187" s="22"/>
+      <c r="G187" s="22"/>
+      <c r="H187" s="22">
+        <v>1</v>
+      </c>
+      <c r="I187" s="22">
         <v>0</v>
       </c>
-      <c r="J187" s="21"/>
+      <c r="J187" s="22"/>
     </row>
     <row r="188" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A188" s="7" t="s">
@@ -5716,90 +5823,90 @@
       <c r="J189" s="8"/>
     </row>
     <row r="190" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A190" s="20" t="s">
+      <c r="A190" s="21" t="s">
         <v>47</v>
       </c>
-      <c r="B190" s="19" t="s">
-        <v>3</v>
-      </c>
-      <c r="C190" s="19">
+      <c r="B190" s="20" t="s">
+        <v>3</v>
+      </c>
+      <c r="C190" s="20">
         <v>9991002</v>
       </c>
-      <c r="D190" s="19"/>
-      <c r="E190" s="19"/>
-      <c r="F190" s="19">
+      <c r="D190" s="20"/>
+      <c r="E190" s="20"/>
+      <c r="F190" s="20">
         <v>3211274</v>
       </c>
-      <c r="G190" s="22">
+      <c r="G190" s="23">
         <v>46144</v>
       </c>
-      <c r="H190" s="19">
-        <v>2</v>
-      </c>
-      <c r="I190" s="19"/>
-      <c r="J190" s="19"/>
+      <c r="H190" s="20">
+        <v>2</v>
+      </c>
+      <c r="I190" s="20"/>
+      <c r="J190" s="20"/>
     </row>
     <row r="191" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A191" s="20" t="s">
+      <c r="A191" s="21" t="s">
         <v>47</v>
       </c>
-      <c r="B191" s="19" t="s">
-        <v>3</v>
-      </c>
-      <c r="C191" s="19">
+      <c r="B191" s="20" t="s">
+        <v>3</v>
+      </c>
+      <c r="C191" s="20">
         <v>9991002</v>
       </c>
-      <c r="D191" s="19"/>
-      <c r="E191" s="19"/>
-      <c r="F191" s="19">
+      <c r="D191" s="20"/>
+      <c r="E191" s="20"/>
+      <c r="F191" s="20">
         <v>3211301</v>
       </c>
-      <c r="G191" s="19" t="s">
+      <c r="G191" s="20" t="s">
         <v>89</v>
       </c>
-      <c r="H191" s="19">
-        <v>1</v>
-      </c>
-      <c r="I191" s="19"/>
-      <c r="J191" s="19"/>
+      <c r="H191" s="20">
+        <v>1</v>
+      </c>
+      <c r="I191" s="20"/>
+      <c r="J191" s="20"/>
     </row>
     <row r="192" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A192" s="21" t="s">
+      <c r="A192" s="22" t="s">
         <v>45</v>
       </c>
-      <c r="B192" s="21" t="s">
-        <v>3</v>
-      </c>
-      <c r="C192" s="21">
+      <c r="B192" s="22" t="s">
+        <v>3</v>
+      </c>
+      <c r="C192" s="22">
         <v>9991002</v>
       </c>
-      <c r="D192" s="21"/>
-      <c r="E192" s="21">
-        <v>3</v>
-      </c>
-      <c r="F192" s="21"/>
-      <c r="G192" s="21"/>
-      <c r="H192" s="21">
-        <v>3</v>
-      </c>
-      <c r="I192" s="21">
+      <c r="D192" s="22"/>
+      <c r="E192" s="22">
+        <v>3</v>
+      </c>
+      <c r="F192" s="22"/>
+      <c r="G192" s="22"/>
+      <c r="H192" s="22">
+        <v>3</v>
+      </c>
+      <c r="I192" s="22">
         <v>0</v>
       </c>
-      <c r="J192" s="21"/>
+      <c r="J192" s="22"/>
     </row>
     <row r="194" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A194" s="16" t="s">
+      <c r="A194" s="17" t="s">
         <v>140</v>
       </c>
-      <c r="B194" s="16"/>
-      <c r="C194" s="16"/>
-      <c r="D194" s="16"/>
-      <c r="E194" s="16"/>
-      <c r="F194" s="16"/>
-      <c r="G194" s="16"/>
-      <c r="H194" s="16"/>
-      <c r="I194" s="16"/>
-      <c r="J194" s="16"/>
+      <c r="B194" s="17"/>
+      <c r="C194" s="17"/>
+      <c r="D194" s="17"/>
+      <c r="E194" s="17"/>
+      <c r="F194" s="17"/>
+      <c r="G194" s="17"/>
+      <c r="H194" s="17"/>
+      <c r="I194" s="17"/>
+      <c r="J194" s="17"/>
     </row>
     <row r="195" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A195" s="7" t="s">
@@ -5824,52 +5931,52 @@
       <c r="J195" s="7"/>
     </row>
     <row r="196" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A196" s="20" t="s">
+      <c r="A196" s="21" t="s">
         <v>47</v>
       </c>
-      <c r="B196" s="19" t="s">
-        <v>3</v>
-      </c>
-      <c r="C196" s="19">
+      <c r="B196" s="20" t="s">
+        <v>3</v>
+      </c>
+      <c r="C196" s="20">
         <v>9991002</v>
       </c>
-      <c r="D196" s="19"/>
-      <c r="E196" s="19"/>
-      <c r="F196" s="19">
+      <c r="D196" s="20"/>
+      <c r="E196" s="20"/>
+      <c r="F196" s="20">
         <v>3411486</v>
       </c>
-      <c r="G196" s="22">
+      <c r="G196" s="23">
         <v>46328</v>
       </c>
-      <c r="H196" s="19">
-        <v>2</v>
-      </c>
-      <c r="I196" s="19"/>
-      <c r="J196" s="19"/>
+      <c r="H196" s="20">
+        <v>2</v>
+      </c>
+      <c r="I196" s="20"/>
+      <c r="J196" s="20"/>
     </row>
     <row r="197" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A197" s="21" t="s">
+      <c r="A197" s="22" t="s">
         <v>45</v>
       </c>
-      <c r="B197" s="21" t="s">
-        <v>3</v>
-      </c>
-      <c r="C197" s="21">
+      <c r="B197" s="22" t="s">
+        <v>3</v>
+      </c>
+      <c r="C197" s="22">
         <v>9991002</v>
       </c>
-      <c r="D197" s="21"/>
-      <c r="E197" s="21">
-        <v>2</v>
-      </c>
-      <c r="F197" s="21"/>
-      <c r="G197" s="21"/>
-      <c r="H197" s="21">
-        <v>2</v>
-      </c>
-      <c r="I197" s="21">
+      <c r="D197" s="22"/>
+      <c r="E197" s="22">
+        <v>2</v>
+      </c>
+      <c r="F197" s="22"/>
+      <c r="G197" s="22"/>
+      <c r="H197" s="22">
+        <v>2</v>
+      </c>
+      <c r="I197" s="22">
         <v>0</v>
       </c>
-      <c r="J197" s="21"/>
+      <c r="J197" s="22"/>
     </row>
     <row r="198" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A198" s="7" t="s">
@@ -5894,52 +6001,52 @@
       <c r="J198" s="7"/>
     </row>
     <row r="199" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A199" s="20" t="s">
+      <c r="A199" s="21" t="s">
         <v>47</v>
       </c>
-      <c r="B199" s="19" t="s">
-        <v>4</v>
-      </c>
-      <c r="C199" s="19">
+      <c r="B199" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="C199" s="20">
         <v>9991003</v>
       </c>
-      <c r="D199" s="19"/>
-      <c r="E199" s="19"/>
-      <c r="F199" s="19">
+      <c r="D199" s="20"/>
+      <c r="E199" s="20"/>
+      <c r="F199" s="20">
         <v>3411496</v>
       </c>
-      <c r="G199" s="19" t="s">
+      <c r="G199" s="20" t="s">
         <v>89</v>
       </c>
-      <c r="H199" s="19">
-        <v>1</v>
-      </c>
-      <c r="I199" s="19"/>
-      <c r="J199" s="19"/>
+      <c r="H199" s="20">
+        <v>1</v>
+      </c>
+      <c r="I199" s="20"/>
+      <c r="J199" s="20"/>
     </row>
     <row r="200" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A200" s="21" t="s">
+      <c r="A200" s="22" t="s">
         <v>45</v>
       </c>
-      <c r="B200" s="21" t="s">
-        <v>4</v>
-      </c>
-      <c r="C200" s="21">
+      <c r="B200" s="22" t="s">
+        <v>4</v>
+      </c>
+      <c r="C200" s="22">
         <v>9991003</v>
       </c>
-      <c r="D200" s="21"/>
-      <c r="E200" s="21">
-        <v>1</v>
-      </c>
-      <c r="F200" s="21"/>
-      <c r="G200" s="21"/>
-      <c r="H200" s="21">
-        <v>1</v>
-      </c>
-      <c r="I200" s="21">
+      <c r="D200" s="22"/>
+      <c r="E200" s="22">
+        <v>1</v>
+      </c>
+      <c r="F200" s="22"/>
+      <c r="G200" s="22"/>
+      <c r="H200" s="22">
+        <v>1</v>
+      </c>
+      <c r="I200" s="22">
         <v>0</v>
       </c>
-      <c r="J200" s="21"/>
+      <c r="J200" s="22"/>
     </row>
     <row r="201" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A201" s="7" t="s">
@@ -5964,66 +6071,66 @@
       <c r="J201" s="7"/>
     </row>
     <row r="202" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A202" s="20" t="s">
+      <c r="A202" s="21" t="s">
         <v>47</v>
       </c>
-      <c r="B202" s="19" t="s">
+      <c r="B202" s="20" t="s">
         <v>7</v>
       </c>
-      <c r="C202" s="19">
+      <c r="C202" s="20">
         <v>9991006</v>
       </c>
-      <c r="D202" s="19"/>
-      <c r="E202" s="19"/>
-      <c r="F202" s="19">
+      <c r="D202" s="20"/>
+      <c r="E202" s="20"/>
+      <c r="F202" s="20">
         <v>3411653</v>
       </c>
-      <c r="G202" s="22">
+      <c r="G202" s="23">
         <v>46238</v>
       </c>
-      <c r="H202" s="19">
-        <v>2</v>
-      </c>
-      <c r="I202" s="19"/>
-      <c r="J202" s="19"/>
+      <c r="H202" s="20">
+        <v>2</v>
+      </c>
+      <c r="I202" s="20"/>
+      <c r="J202" s="20"/>
     </row>
     <row r="203" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A203" s="21" t="s">
+      <c r="A203" s="22" t="s">
         <v>45</v>
       </c>
-      <c r="B203" s="21" t="s">
+      <c r="B203" s="22" t="s">
         <v>7</v>
       </c>
-      <c r="C203" s="21">
+      <c r="C203" s="22">
         <v>9991006</v>
       </c>
-      <c r="D203" s="21"/>
-      <c r="E203" s="21">
-        <v>2</v>
-      </c>
-      <c r="F203" s="21"/>
-      <c r="G203" s="21"/>
-      <c r="H203" s="21">
-        <v>2</v>
-      </c>
-      <c r="I203" s="21">
+      <c r="D203" s="22"/>
+      <c r="E203" s="22">
+        <v>2</v>
+      </c>
+      <c r="F203" s="22"/>
+      <c r="G203" s="22"/>
+      <c r="H203" s="22">
+        <v>2</v>
+      </c>
+      <c r="I203" s="22">
         <v>0</v>
       </c>
-      <c r="J203" s="21"/>
+      <c r="J203" s="22"/>
     </row>
     <row r="205" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A205" s="16" t="s">
+      <c r="A205" s="17" t="s">
         <v>24</v>
       </c>
-      <c r="B205" s="16"/>
-      <c r="C205" s="16"/>
-      <c r="D205" s="16"/>
-      <c r="E205" s="16"/>
-      <c r="F205" s="16"/>
-      <c r="G205" s="16"/>
-      <c r="H205" s="16"/>
-      <c r="I205" s="16"/>
-      <c r="J205" s="16"/>
+      <c r="B205" s="17"/>
+      <c r="C205" s="17"/>
+      <c r="D205" s="17"/>
+      <c r="E205" s="17"/>
+      <c r="F205" s="17"/>
+      <c r="G205" s="17"/>
+      <c r="H205" s="17"/>
+      <c r="I205" s="17"/>
+      <c r="J205" s="17"/>
     </row>
     <row r="206" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A206" s="7" t="s">
@@ -6048,28 +6155,28 @@
       <c r="J206" s="7"/>
     </row>
     <row r="207" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A207" s="18" t="s">
+      <c r="A207" s="19" t="s">
         <v>45</v>
       </c>
-      <c r="B207" s="18" t="s">
-        <v>2</v>
-      </c>
-      <c r="C207" s="18">
+      <c r="B207" s="19" t="s">
+        <v>2</v>
+      </c>
+      <c r="C207" s="19">
         <v>9991001</v>
       </c>
-      <c r="D207" s="18"/>
-      <c r="E207" s="18">
-        <v>2</v>
-      </c>
-      <c r="F207" s="18"/>
-      <c r="G207" s="18"/>
-      <c r="H207" s="18">
+      <c r="D207" s="19"/>
+      <c r="E207" s="19">
+        <v>2</v>
+      </c>
+      <c r="F207" s="19"/>
+      <c r="G207" s="19"/>
+      <c r="H207" s="19">
         <v>0</v>
       </c>
-      <c r="I207" s="18">
-        <v>2</v>
-      </c>
-      <c r="J207" s="18">
+      <c r="I207" s="19">
+        <v>2</v>
+      </c>
+      <c r="J207" s="19">
         <v>2</v>
       </c>
     </row>
@@ -6096,28 +6203,28 @@
       <c r="J208" s="7"/>
     </row>
     <row r="209" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A209" s="18" t="s">
+      <c r="A209" s="19" t="s">
         <v>45</v>
       </c>
-      <c r="B209" s="18" t="s">
-        <v>4</v>
-      </c>
-      <c r="C209" s="18">
+      <c r="B209" s="19" t="s">
+        <v>4</v>
+      </c>
+      <c r="C209" s="19">
         <v>9991003</v>
       </c>
-      <c r="D209" s="18"/>
-      <c r="E209" s="18">
-        <v>2</v>
-      </c>
-      <c r="F209" s="18"/>
-      <c r="G209" s="18"/>
-      <c r="H209" s="18">
+      <c r="D209" s="19"/>
+      <c r="E209" s="19">
+        <v>2</v>
+      </c>
+      <c r="F209" s="19"/>
+      <c r="G209" s="19"/>
+      <c r="H209" s="19">
         <v>0</v>
       </c>
-      <c r="I209" s="18">
-        <v>2</v>
-      </c>
-      <c r="J209" s="18">
+      <c r="I209" s="19">
+        <v>2</v>
+      </c>
+      <c r="J209" s="19">
         <v>2</v>
       </c>
     </row>
@@ -6131,7 +6238,7 @@
       <c r="C210" s="7">
         <v>9991004</v>
       </c>
-      <c r="D210" s="17">
+      <c r="D210" s="18">
         <v>46358</v>
       </c>
       <c r="E210" s="7">
@@ -6166,52 +6273,52 @@
       <c r="J211" s="8"/>
     </row>
     <row r="212" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A212" s="20" t="s">
+      <c r="A212" s="21" t="s">
         <v>47</v>
       </c>
-      <c r="B212" s="19" t="s">
+      <c r="B212" s="20" t="s">
         <v>5</v>
       </c>
-      <c r="C212" s="19">
+      <c r="C212" s="20">
         <v>9991004</v>
       </c>
-      <c r="D212" s="19"/>
-      <c r="E212" s="19"/>
-      <c r="F212" s="19">
+      <c r="D212" s="20"/>
+      <c r="E212" s="20"/>
+      <c r="F212" s="20">
         <v>3612319</v>
       </c>
-      <c r="G212" s="19" t="s">
+      <c r="G212" s="20" t="s">
         <v>54</v>
       </c>
-      <c r="H212" s="19">
-        <v>2</v>
-      </c>
-      <c r="I212" s="19"/>
-      <c r="J212" s="19"/>
+      <c r="H212" s="20">
+        <v>2</v>
+      </c>
+      <c r="I212" s="20"/>
+      <c r="J212" s="20"/>
     </row>
     <row r="213" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A213" s="18" t="s">
+      <c r="A213" s="19" t="s">
         <v>45</v>
       </c>
-      <c r="B213" s="18" t="s">
+      <c r="B213" s="19" t="s">
         <v>5</v>
       </c>
-      <c r="C213" s="18">
+      <c r="C213" s="19">
         <v>9991004</v>
       </c>
-      <c r="D213" s="18"/>
-      <c r="E213" s="18">
-        <v>3</v>
-      </c>
-      <c r="F213" s="18"/>
-      <c r="G213" s="18"/>
-      <c r="H213" s="18">
-        <v>2</v>
-      </c>
-      <c r="I213" s="18">
-        <v>1</v>
-      </c>
-      <c r="J213" s="18">
+      <c r="D213" s="19"/>
+      <c r="E213" s="19">
+        <v>3</v>
+      </c>
+      <c r="F213" s="19"/>
+      <c r="G213" s="19"/>
+      <c r="H213" s="19">
+        <v>2</v>
+      </c>
+      <c r="I213" s="19">
+        <v>1</v>
+      </c>
+      <c r="J213" s="19">
         <v>1</v>
       </c>
     </row>
@@ -6225,7 +6332,7 @@
       <c r="C214" s="7">
         <v>9991005</v>
       </c>
-      <c r="D214" s="17">
+      <c r="D214" s="18">
         <v>46331</v>
       </c>
       <c r="E214" s="7">
@@ -6238,44 +6345,44 @@
       <c r="J214" s="7"/>
     </row>
     <row r="215" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A215" s="18" t="s">
+      <c r="A215" s="19" t="s">
         <v>45</v>
       </c>
-      <c r="B215" s="18" t="s">
+      <c r="B215" s="19" t="s">
         <v>6</v>
       </c>
-      <c r="C215" s="18">
+      <c r="C215" s="19">
         <v>9991005</v>
       </c>
-      <c r="D215" s="18"/>
-      <c r="E215" s="18">
-        <v>3</v>
-      </c>
-      <c r="F215" s="18"/>
-      <c r="G215" s="18"/>
-      <c r="H215" s="18">
+      <c r="D215" s="19"/>
+      <c r="E215" s="19">
+        <v>3</v>
+      </c>
+      <c r="F215" s="19"/>
+      <c r="G215" s="19"/>
+      <c r="H215" s="19">
         <v>0</v>
       </c>
-      <c r="I215" s="18">
-        <v>3</v>
-      </c>
-      <c r="J215" s="18">
+      <c r="I215" s="19">
+        <v>3</v>
+      </c>
+      <c r="J215" s="19">
         <v>3</v>
       </c>
     </row>
     <row r="217" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A217" s="16" t="s">
+      <c r="A217" s="17" t="s">
         <v>25</v>
       </c>
-      <c r="B217" s="16"/>
-      <c r="C217" s="16"/>
-      <c r="D217" s="16"/>
-      <c r="E217" s="16"/>
-      <c r="F217" s="16"/>
-      <c r="G217" s="16"/>
-      <c r="H217" s="16"/>
-      <c r="I217" s="16"/>
-      <c r="J217" s="16"/>
+      <c r="B217" s="17"/>
+      <c r="C217" s="17"/>
+      <c r="D217" s="17"/>
+      <c r="E217" s="17"/>
+      <c r="F217" s="17"/>
+      <c r="G217" s="17"/>
+      <c r="H217" s="17"/>
+      <c r="I217" s="17"/>
+      <c r="J217" s="17"/>
     </row>
     <row r="218" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A218" s="7" t="s">
@@ -6287,7 +6394,7 @@
       <c r="C218" s="7">
         <v>9991003</v>
       </c>
-      <c r="D218" s="17">
+      <c r="D218" s="18">
         <v>46175</v>
       </c>
       <c r="E218" s="7">
@@ -6300,52 +6407,52 @@
       <c r="J218" s="7"/>
     </row>
     <row r="219" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A219" s="20" t="s">
+      <c r="A219" s="21" t="s">
         <v>47</v>
       </c>
-      <c r="B219" s="19" t="s">
-        <v>4</v>
-      </c>
-      <c r="C219" s="19">
+      <c r="B219" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="C219" s="20">
         <v>9991003</v>
       </c>
-      <c r="D219" s="19"/>
-      <c r="E219" s="19"/>
-      <c r="F219" s="19">
+      <c r="D219" s="20"/>
+      <c r="E219" s="20"/>
+      <c r="F219" s="20">
         <v>3712501</v>
       </c>
-      <c r="G219" s="19" t="s">
+      <c r="G219" s="20" t="s">
         <v>152</v>
       </c>
-      <c r="H219" s="19">
-        <v>2</v>
-      </c>
-      <c r="I219" s="19"/>
-      <c r="J219" s="19"/>
+      <c r="H219" s="20">
+        <v>2</v>
+      </c>
+      <c r="I219" s="20"/>
+      <c r="J219" s="20"/>
     </row>
     <row r="220" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A220" s="21" t="s">
+      <c r="A220" s="22" t="s">
         <v>45</v>
       </c>
-      <c r="B220" s="21" t="s">
-        <v>4</v>
-      </c>
-      <c r="C220" s="21">
+      <c r="B220" s="22" t="s">
+        <v>4</v>
+      </c>
+      <c r="C220" s="22">
         <v>9991003</v>
       </c>
-      <c r="D220" s="21"/>
-      <c r="E220" s="21">
-        <v>2</v>
-      </c>
-      <c r="F220" s="21"/>
-      <c r="G220" s="21"/>
-      <c r="H220" s="21">
-        <v>2</v>
-      </c>
-      <c r="I220" s="21">
+      <c r="D220" s="22"/>
+      <c r="E220" s="22">
+        <v>2</v>
+      </c>
+      <c r="F220" s="22"/>
+      <c r="G220" s="22"/>
+      <c r="H220" s="22">
+        <v>2</v>
+      </c>
+      <c r="I220" s="22">
         <v>0</v>
       </c>
-      <c r="J220" s="21"/>
+      <c r="J220" s="22"/>
     </row>
     <row r="221" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A221" s="7" t="s">
@@ -6370,44 +6477,44 @@
       <c r="J221" s="7"/>
     </row>
     <row r="222" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A222" s="18" t="s">
+      <c r="A222" s="19" t="s">
         <v>45</v>
       </c>
-      <c r="B222" s="18" t="s">
+      <c r="B222" s="19" t="s">
         <v>8</v>
       </c>
-      <c r="C222" s="18">
+      <c r="C222" s="19">
         <v>9991007</v>
       </c>
-      <c r="D222" s="18"/>
-      <c r="E222" s="18">
-        <v>4</v>
-      </c>
-      <c r="F222" s="18"/>
-      <c r="G222" s="18"/>
-      <c r="H222" s="18">
+      <c r="D222" s="19"/>
+      <c r="E222" s="19">
+        <v>4</v>
+      </c>
+      <c r="F222" s="19"/>
+      <c r="G222" s="19"/>
+      <c r="H222" s="19">
         <v>0</v>
       </c>
-      <c r="I222" s="18">
-        <v>4</v>
-      </c>
-      <c r="J222" s="18">
+      <c r="I222" s="19">
+        <v>4</v>
+      </c>
+      <c r="J222" s="19">
         <v>4</v>
       </c>
     </row>
     <row r="224" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A224" s="16" t="s">
+      <c r="A224" s="17" t="s">
         <v>26</v>
       </c>
-      <c r="B224" s="16"/>
-      <c r="C224" s="16"/>
-      <c r="D224" s="16"/>
-      <c r="E224" s="16"/>
-      <c r="F224" s="16"/>
-      <c r="G224" s="16"/>
-      <c r="H224" s="16"/>
-      <c r="I224" s="16"/>
-      <c r="J224" s="16"/>
+      <c r="B224" s="17"/>
+      <c r="C224" s="17"/>
+      <c r="D224" s="17"/>
+      <c r="E224" s="17"/>
+      <c r="F224" s="17"/>
+      <c r="G224" s="17"/>
+      <c r="H224" s="17"/>
+      <c r="I224" s="17"/>
+      <c r="J224" s="17"/>
     </row>
     <row r="225" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A225" s="7" t="s">
@@ -6432,52 +6539,52 @@
       <c r="J225" s="7"/>
     </row>
     <row r="226" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A226" s="20" t="s">
+      <c r="A226" s="21" t="s">
         <v>47</v>
       </c>
-      <c r="B226" s="19" t="s">
-        <v>2</v>
-      </c>
-      <c r="C226" s="19">
+      <c r="B226" s="20" t="s">
+        <v>2</v>
+      </c>
+      <c r="C226" s="20">
         <v>9991001</v>
       </c>
-      <c r="D226" s="19"/>
-      <c r="E226" s="19"/>
-      <c r="F226" s="19">
+      <c r="D226" s="20"/>
+      <c r="E226" s="20"/>
+      <c r="F226" s="20">
         <v>3811978</v>
       </c>
-      <c r="G226" s="19" t="s">
+      <c r="G226" s="20" t="s">
         <v>144</v>
       </c>
-      <c r="H226" s="19">
-        <v>3</v>
-      </c>
-      <c r="I226" s="19"/>
-      <c r="J226" s="19"/>
+      <c r="H226" s="20">
+        <v>3</v>
+      </c>
+      <c r="I226" s="20"/>
+      <c r="J226" s="20"/>
     </row>
     <row r="227" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A227" s="21" t="s">
+      <c r="A227" s="22" t="s">
         <v>45</v>
       </c>
-      <c r="B227" s="21" t="s">
-        <v>2</v>
-      </c>
-      <c r="C227" s="21">
+      <c r="B227" s="22" t="s">
+        <v>2</v>
+      </c>
+      <c r="C227" s="22">
         <v>9991001</v>
       </c>
-      <c r="D227" s="21"/>
-      <c r="E227" s="21">
-        <v>3</v>
-      </c>
-      <c r="F227" s="21"/>
-      <c r="G227" s="21"/>
-      <c r="H227" s="21">
-        <v>3</v>
-      </c>
-      <c r="I227" s="21">
+      <c r="D227" s="22"/>
+      <c r="E227" s="22">
+        <v>3</v>
+      </c>
+      <c r="F227" s="22"/>
+      <c r="G227" s="22"/>
+      <c r="H227" s="22">
+        <v>3</v>
+      </c>
+      <c r="I227" s="22">
         <v>0</v>
       </c>
-      <c r="J227" s="21"/>
+      <c r="J227" s="22"/>
     </row>
     <row r="228" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A228" s="7" t="s">
@@ -6524,76 +6631,76 @@
       <c r="J229" s="8"/>
     </row>
     <row r="230" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A230" s="20" t="s">
+      <c r="A230" s="21" t="s">
         <v>47</v>
       </c>
-      <c r="B230" s="19" t="s">
-        <v>3</v>
-      </c>
-      <c r="C230" s="19">
+      <c r="B230" s="20" t="s">
+        <v>3</v>
+      </c>
+      <c r="C230" s="20">
         <v>9991002</v>
       </c>
-      <c r="D230" s="19"/>
-      <c r="E230" s="19"/>
-      <c r="F230" s="19">
+      <c r="D230" s="20"/>
+      <c r="E230" s="20"/>
+      <c r="F230" s="20">
         <v>3811978</v>
       </c>
-      <c r="G230" s="19" t="s">
+      <c r="G230" s="20" t="s">
         <v>144</v>
       </c>
-      <c r="H230" s="19">
-        <v>1</v>
-      </c>
-      <c r="I230" s="19"/>
-      <c r="J230" s="19"/>
+      <c r="H230" s="20">
+        <v>1</v>
+      </c>
+      <c r="I230" s="20"/>
+      <c r="J230" s="20"/>
     </row>
     <row r="231" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A231" s="20" t="s">
+      <c r="A231" s="21" t="s">
         <v>47</v>
       </c>
-      <c r="B231" s="19" t="s">
-        <v>3</v>
-      </c>
-      <c r="C231" s="19">
+      <c r="B231" s="20" t="s">
+        <v>3</v>
+      </c>
+      <c r="C231" s="20">
         <v>9991002</v>
       </c>
-      <c r="D231" s="19"/>
-      <c r="E231" s="19"/>
-      <c r="F231" s="19">
+      <c r="D231" s="20"/>
+      <c r="E231" s="20"/>
+      <c r="F231" s="20">
         <v>3811984</v>
       </c>
-      <c r="G231" s="19" t="s">
+      <c r="G231" s="20" t="s">
         <v>157</v>
       </c>
-      <c r="H231" s="19">
-        <v>1</v>
-      </c>
-      <c r="I231" s="19"/>
-      <c r="J231" s="19"/>
+      <c r="H231" s="20">
+        <v>1</v>
+      </c>
+      <c r="I231" s="20"/>
+      <c r="J231" s="20"/>
     </row>
     <row r="232" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A232" s="21" t="s">
+      <c r="A232" s="22" t="s">
         <v>45</v>
       </c>
-      <c r="B232" s="21" t="s">
-        <v>3</v>
-      </c>
-      <c r="C232" s="21">
+      <c r="B232" s="22" t="s">
+        <v>3</v>
+      </c>
+      <c r="C232" s="22">
         <v>9991002</v>
       </c>
-      <c r="D232" s="21"/>
-      <c r="E232" s="21">
-        <v>2</v>
-      </c>
-      <c r="F232" s="21"/>
-      <c r="G232" s="21"/>
-      <c r="H232" s="21">
-        <v>2</v>
-      </c>
-      <c r="I232" s="21">
+      <c r="D232" s="22"/>
+      <c r="E232" s="22">
+        <v>2</v>
+      </c>
+      <c r="F232" s="22"/>
+      <c r="G232" s="22"/>
+      <c r="H232" s="22">
+        <v>2</v>
+      </c>
+      <c r="I232" s="22">
         <v>0</v>
       </c>
-      <c r="J232" s="21"/>
+      <c r="J232" s="22"/>
     </row>
     <row r="233" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A233" s="7" t="s">
@@ -6605,7 +6712,7 @@
       <c r="C233" s="7">
         <v>9991005</v>
       </c>
-      <c r="D233" s="17">
+      <c r="D233" s="18">
         <v>46361</v>
       </c>
       <c r="E233" s="7">
@@ -6640,76 +6747,76 @@
       <c r="J234" s="8"/>
     </row>
     <row r="235" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A235" s="20" t="s">
+      <c r="A235" s="21" t="s">
         <v>47</v>
       </c>
-      <c r="B235" s="19" t="s">
+      <c r="B235" s="20" t="s">
         <v>6</v>
       </c>
-      <c r="C235" s="19">
+      <c r="C235" s="20">
         <v>9991005</v>
       </c>
-      <c r="D235" s="19"/>
-      <c r="E235" s="19"/>
-      <c r="F235" s="19">
+      <c r="D235" s="20"/>
+      <c r="E235" s="20"/>
+      <c r="F235" s="20">
         <v>3811814</v>
       </c>
-      <c r="G235" s="22">
+      <c r="G235" s="23">
         <v>46083</v>
       </c>
-      <c r="H235" s="19">
-        <v>3</v>
-      </c>
-      <c r="I235" s="19"/>
-      <c r="J235" s="19"/>
+      <c r="H235" s="20">
+        <v>3</v>
+      </c>
+      <c r="I235" s="20"/>
+      <c r="J235" s="20"/>
     </row>
     <row r="236" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A236" s="20" t="s">
+      <c r="A236" s="21" t="s">
         <v>47</v>
       </c>
-      <c r="B236" s="19" t="s">
+      <c r="B236" s="20" t="s">
         <v>6</v>
       </c>
-      <c r="C236" s="19">
+      <c r="C236" s="20">
         <v>9991005</v>
       </c>
-      <c r="D236" s="19"/>
-      <c r="E236" s="19"/>
-      <c r="F236" s="19">
+      <c r="D236" s="20"/>
+      <c r="E236" s="20"/>
+      <c r="F236" s="20">
         <v>3812131</v>
       </c>
-      <c r="G236" s="19" t="s">
+      <c r="G236" s="20" t="s">
         <v>160</v>
       </c>
-      <c r="H236" s="19">
-        <v>2</v>
-      </c>
-      <c r="I236" s="19"/>
-      <c r="J236" s="19"/>
+      <c r="H236" s="20">
+        <v>2</v>
+      </c>
+      <c r="I236" s="20"/>
+      <c r="J236" s="20"/>
     </row>
     <row r="237" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A237" s="21" t="s">
+      <c r="A237" s="22" t="s">
         <v>45</v>
       </c>
-      <c r="B237" s="21" t="s">
+      <c r="B237" s="22" t="s">
         <v>6</v>
       </c>
-      <c r="C237" s="21">
+      <c r="C237" s="22">
         <v>9991005</v>
       </c>
-      <c r="D237" s="21"/>
-      <c r="E237" s="21">
+      <c r="D237" s="22"/>
+      <c r="E237" s="22">
         <v>5</v>
       </c>
-      <c r="F237" s="21"/>
-      <c r="G237" s="21"/>
-      <c r="H237" s="21">
+      <c r="F237" s="22"/>
+      <c r="G237" s="22"/>
+      <c r="H237" s="22">
         <v>5</v>
       </c>
-      <c r="I237" s="21">
+      <c r="I237" s="22">
         <v>0</v>
       </c>
-      <c r="J237" s="21"/>
+      <c r="J237" s="22"/>
     </row>
     <row r="238" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A238" s="7" t="s">
@@ -6721,7 +6828,7 @@
       <c r="C238" s="7">
         <v>9991007</v>
       </c>
-      <c r="D238" s="17">
+      <c r="D238" s="18">
         <v>46176</v>
       </c>
       <c r="E238" s="7">
@@ -6734,80 +6841,80 @@
       <c r="J238" s="7"/>
     </row>
     <row r="239" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A239" s="18" t="s">
+      <c r="A239" s="19" t="s">
         <v>45</v>
       </c>
-      <c r="B239" s="18" t="s">
+      <c r="B239" s="19" t="s">
         <v>8</v>
       </c>
-      <c r="C239" s="18">
+      <c r="C239" s="19">
         <v>9991007</v>
       </c>
-      <c r="D239" s="18"/>
-      <c r="E239" s="18">
-        <v>2</v>
-      </c>
-      <c r="F239" s="18"/>
-      <c r="G239" s="18"/>
-      <c r="H239" s="18">
+      <c r="D239" s="19"/>
+      <c r="E239" s="19">
+        <v>2</v>
+      </c>
+      <c r="F239" s="19"/>
+      <c r="G239" s="19"/>
+      <c r="H239" s="19">
         <v>0</v>
       </c>
-      <c r="I239" s="18">
-        <v>2</v>
-      </c>
-      <c r="J239" s="18"/>
+      <c r="I239" s="19">
+        <v>2</v>
+      </c>
+      <c r="J239" s="19"/>
     </row>
     <row r="241" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A241" s="16" t="s">
+      <c r="A241" s="17" t="s">
         <v>27</v>
       </c>
-      <c r="B241" s="16"/>
-      <c r="C241" s="16"/>
-      <c r="D241" s="16"/>
-      <c r="E241" s="16"/>
-      <c r="F241" s="16"/>
-      <c r="G241" s="16"/>
-      <c r="H241" s="16"/>
-      <c r="I241" s="16"/>
-      <c r="J241" s="16"/>
+      <c r="B241" s="17"/>
+      <c r="C241" s="17"/>
+      <c r="D241" s="17"/>
+      <c r="E241" s="17"/>
+      <c r="F241" s="17"/>
+      <c r="G241" s="17"/>
+      <c r="H241" s="17"/>
+      <c r="I241" s="17"/>
+      <c r="J241" s="17"/>
     </row>
     <row r="242" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A242" s="21" t="s">
+      <c r="A242" s="22" t="s">
         <v>45</v>
       </c>
-      <c r="B242" s="21">
+      <c r="B242" s="22">
         <v>99910049991004</v>
       </c>
-      <c r="C242" s="21">
+      <c r="C242" s="22">
         <v>99910049991004</v>
       </c>
-      <c r="D242" s="21"/>
-      <c r="E242" s="21">
+      <c r="D242" s="22"/>
+      <c r="E242" s="22">
         <v>0</v>
       </c>
-      <c r="F242" s="21"/>
-      <c r="G242" s="21"/>
-      <c r="H242" s="21">
+      <c r="F242" s="22"/>
+      <c r="G242" s="22"/>
+      <c r="H242" s="22">
         <v>0</v>
       </c>
-      <c r="I242" s="21">
+      <c r="I242" s="22">
         <v>0</v>
       </c>
-      <c r="J242" s="21"/>
+      <c r="J242" s="22"/>
     </row>
     <row r="244" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A244" s="16" t="s">
+      <c r="A244" s="17" t="s">
         <v>28</v>
       </c>
-      <c r="B244" s="16"/>
-      <c r="C244" s="16"/>
-      <c r="D244" s="16"/>
-      <c r="E244" s="16"/>
-      <c r="F244" s="16"/>
-      <c r="G244" s="16"/>
-      <c r="H244" s="16"/>
-      <c r="I244" s="16"/>
-      <c r="J244" s="16"/>
+      <c r="B244" s="17"/>
+      <c r="C244" s="17"/>
+      <c r="D244" s="17"/>
+      <c r="E244" s="17"/>
+      <c r="F244" s="17"/>
+      <c r="G244" s="17"/>
+      <c r="H244" s="17"/>
+      <c r="I244" s="17"/>
+      <c r="J244" s="17"/>
     </row>
     <row r="245" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A245" s="7" t="s">
@@ -6832,82 +6939,82 @@
       <c r="J245" s="7"/>
     </row>
     <row r="246" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A246" s="18" t="s">
+      <c r="A246" s="19" t="s">
         <v>45</v>
       </c>
-      <c r="B246" s="18" t="s">
-        <v>4</v>
-      </c>
-      <c r="C246" s="18">
+      <c r="B246" s="19" t="s">
+        <v>4</v>
+      </c>
+      <c r="C246" s="19">
         <v>9991003</v>
       </c>
-      <c r="D246" s="18"/>
-      <c r="E246" s="18">
-        <v>1</v>
-      </c>
-      <c r="F246" s="18"/>
-      <c r="G246" s="18"/>
-      <c r="H246" s="18">
+      <c r="D246" s="19"/>
+      <c r="E246" s="19">
+        <v>1</v>
+      </c>
+      <c r="F246" s="19"/>
+      <c r="G246" s="19"/>
+      <c r="H246" s="19">
         <v>0</v>
       </c>
-      <c r="I246" s="18">
-        <v>1</v>
-      </c>
-      <c r="J246" s="18">
+      <c r="I246" s="19">
+        <v>1</v>
+      </c>
+      <c r="J246" s="19">
         <v>1</v>
       </c>
     </row>
     <row r="248" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A248" s="16" t="s">
+      <c r="A248" s="17" t="s">
         <v>163</v>
       </c>
-      <c r="B248" s="16"/>
-      <c r="C248" s="16"/>
-      <c r="D248" s="16"/>
-      <c r="E248" s="16"/>
-      <c r="F248" s="16"/>
-      <c r="G248" s="16"/>
-      <c r="H248" s="16"/>
-      <c r="I248" s="16"/>
-      <c r="J248" s="16"/>
+      <c r="B248" s="17"/>
+      <c r="C248" s="17"/>
+      <c r="D248" s="17"/>
+      <c r="E248" s="17"/>
+      <c r="F248" s="17"/>
+      <c r="G248" s="17"/>
+      <c r="H248" s="17"/>
+      <c r="I248" s="17"/>
+      <c r="J248" s="17"/>
     </row>
     <row r="249" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A249" s="21" t="s">
+      <c r="A249" s="22" t="s">
         <v>45</v>
       </c>
-      <c r="B249" s="21">
+      <c r="B249" s="22">
         <v>99910059991005</v>
       </c>
-      <c r="C249" s="21">
+      <c r="C249" s="22">
         <v>99910059991005</v>
       </c>
-      <c r="D249" s="21"/>
-      <c r="E249" s="21">
+      <c r="D249" s="22"/>
+      <c r="E249" s="22">
         <v>0</v>
       </c>
-      <c r="F249" s="21"/>
-      <c r="G249" s="21"/>
-      <c r="H249" s="21">
+      <c r="F249" s="22"/>
+      <c r="G249" s="22"/>
+      <c r="H249" s="22">
         <v>0</v>
       </c>
-      <c r="I249" s="21">
+      <c r="I249" s="22">
         <v>0</v>
       </c>
-      <c r="J249" s="21"/>
+      <c r="J249" s="22"/>
     </row>
     <row r="251" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A251" s="16" t="s">
+      <c r="A251" s="17" t="s">
         <v>29</v>
       </c>
-      <c r="B251" s="16"/>
-      <c r="C251" s="16"/>
-      <c r="D251" s="16"/>
-      <c r="E251" s="16"/>
-      <c r="F251" s="16"/>
-      <c r="G251" s="16"/>
-      <c r="H251" s="16"/>
-      <c r="I251" s="16"/>
-      <c r="J251" s="16"/>
+      <c r="B251" s="17"/>
+      <c r="C251" s="17"/>
+      <c r="D251" s="17"/>
+      <c r="E251" s="17"/>
+      <c r="F251" s="17"/>
+      <c r="G251" s="17"/>
+      <c r="H251" s="17"/>
+      <c r="I251" s="17"/>
+      <c r="J251" s="17"/>
     </row>
     <row r="252" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A252" s="7" t="s">
@@ -6919,7 +7026,7 @@
       <c r="C252" s="7">
         <v>9991003</v>
       </c>
-      <c r="D252" s="17">
+      <c r="D252" s="18">
         <v>46176</v>
       </c>
       <c r="E252" s="7">
@@ -6954,68 +7061,68 @@
       <c r="J253" s="8"/>
     </row>
     <row r="254" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A254" s="20" t="s">
+      <c r="A254" s="21" t="s">
         <v>47</v>
       </c>
-      <c r="B254" s="19" t="s">
-        <v>4</v>
-      </c>
-      <c r="C254" s="19">
+      <c r="B254" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="C254" s="20">
         <v>9991003</v>
       </c>
-      <c r="D254" s="19"/>
-      <c r="E254" s="19"/>
-      <c r="F254" s="19">
+      <c r="D254" s="20"/>
+      <c r="E254" s="20"/>
+      <c r="F254" s="20">
         <v>44008524</v>
       </c>
-      <c r="G254" s="22">
+      <c r="G254" s="23">
         <v>46175</v>
       </c>
-      <c r="H254" s="19">
-        <v>1</v>
-      </c>
-      <c r="I254" s="19"/>
-      <c r="J254" s="19"/>
+      <c r="H254" s="20">
+        <v>1</v>
+      </c>
+      <c r="I254" s="20"/>
+      <c r="J254" s="20"/>
     </row>
     <row r="255" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A255" s="18" t="s">
+      <c r="A255" s="19" t="s">
         <v>45</v>
       </c>
-      <c r="B255" s="18" t="s">
-        <v>4</v>
-      </c>
-      <c r="C255" s="18">
+      <c r="B255" s="19" t="s">
+        <v>4</v>
+      </c>
+      <c r="C255" s="19">
         <v>9991003</v>
       </c>
-      <c r="D255" s="18"/>
-      <c r="E255" s="18">
-        <v>2</v>
-      </c>
-      <c r="F255" s="18"/>
-      <c r="G255" s="18"/>
-      <c r="H255" s="18">
-        <v>1</v>
-      </c>
-      <c r="I255" s="18">
-        <v>1</v>
-      </c>
-      <c r="J255" s="18">
+      <c r="D255" s="19"/>
+      <c r="E255" s="19">
+        <v>2</v>
+      </c>
+      <c r="F255" s="19"/>
+      <c r="G255" s="19"/>
+      <c r="H255" s="19">
+        <v>1</v>
+      </c>
+      <c r="I255" s="19">
+        <v>1</v>
+      </c>
+      <c r="J255" s="19">
         <v>1</v>
       </c>
     </row>
     <row r="257" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A257" s="16" t="s">
+      <c r="A257" s="17" t="s">
         <v>30</v>
       </c>
-      <c r="B257" s="16"/>
-      <c r="C257" s="16"/>
-      <c r="D257" s="16"/>
-      <c r="E257" s="16"/>
-      <c r="F257" s="16"/>
-      <c r="G257" s="16"/>
-      <c r="H257" s="16"/>
-      <c r="I257" s="16"/>
-      <c r="J257" s="16"/>
+      <c r="B257" s="17"/>
+      <c r="C257" s="17"/>
+      <c r="D257" s="17"/>
+      <c r="E257" s="17"/>
+      <c r="F257" s="17"/>
+      <c r="G257" s="17"/>
+      <c r="H257" s="17"/>
+      <c r="I257" s="17"/>
+      <c r="J257" s="17"/>
     </row>
     <row r="258" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A258" s="7" t="s">
@@ -7040,52 +7147,52 @@
       <c r="J258" s="7"/>
     </row>
     <row r="259" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A259" s="20" t="s">
+      <c r="A259" s="21" t="s">
         <v>47</v>
       </c>
-      <c r="B259" s="19" t="s">
-        <v>3</v>
-      </c>
-      <c r="C259" s="19">
+      <c r="B259" s="20" t="s">
+        <v>3</v>
+      </c>
+      <c r="C259" s="20">
         <v>9991002</v>
       </c>
-      <c r="D259" s="19"/>
-      <c r="E259" s="19"/>
-      <c r="F259" s="19">
+      <c r="D259" s="20"/>
+      <c r="E259" s="20"/>
+      <c r="F259" s="20">
         <v>45008008</v>
       </c>
-      <c r="G259" s="22">
+      <c r="G259" s="23">
         <v>46145</v>
       </c>
-      <c r="H259" s="19">
-        <v>2</v>
-      </c>
-      <c r="I259" s="19"/>
-      <c r="J259" s="19"/>
+      <c r="H259" s="20">
+        <v>2</v>
+      </c>
+      <c r="I259" s="20"/>
+      <c r="J259" s="20"/>
     </row>
     <row r="260" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A260" s="21" t="s">
+      <c r="A260" s="22" t="s">
         <v>45</v>
       </c>
-      <c r="B260" s="21" t="s">
-        <v>3</v>
-      </c>
-      <c r="C260" s="21">
+      <c r="B260" s="22" t="s">
+        <v>3</v>
+      </c>
+      <c r="C260" s="22">
         <v>9991002</v>
       </c>
-      <c r="D260" s="21"/>
-      <c r="E260" s="21">
-        <v>2</v>
-      </c>
-      <c r="F260" s="21"/>
-      <c r="G260" s="21"/>
-      <c r="H260" s="21">
-        <v>2</v>
-      </c>
-      <c r="I260" s="21">
+      <c r="D260" s="22"/>
+      <c r="E260" s="22">
+        <v>2</v>
+      </c>
+      <c r="F260" s="22"/>
+      <c r="G260" s="22"/>
+      <c r="H260" s="22">
+        <v>2</v>
+      </c>
+      <c r="I260" s="22">
         <v>0</v>
       </c>
-      <c r="J260" s="21"/>
+      <c r="J260" s="22"/>
     </row>
     <row r="261" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A261" s="7" t="s">
@@ -7097,7 +7204,7 @@
       <c r="C261" s="7">
         <v>9991003</v>
       </c>
-      <c r="D261" s="17">
+      <c r="D261" s="18">
         <v>46055</v>
       </c>
       <c r="E261" s="7">
@@ -7119,7 +7226,7 @@
       <c r="C262" s="8">
         <v>9991003</v>
       </c>
-      <c r="D262" s="23">
+      <c r="D262" s="24">
         <v>46055</v>
       </c>
       <c r="E262" s="8">
@@ -7132,100 +7239,100 @@
       <c r="J262" s="8"/>
     </row>
     <row r="263" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A263" s="20" t="s">
+      <c r="A263" s="21" t="s">
         <v>47</v>
       </c>
-      <c r="B263" s="19" t="s">
-        <v>4</v>
-      </c>
-      <c r="C263" s="19">
+      <c r="B263" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="C263" s="20">
         <v>9991003</v>
       </c>
-      <c r="D263" s="19"/>
-      <c r="E263" s="19"/>
-      <c r="F263" s="19">
+      <c r="D263" s="20"/>
+      <c r="E263" s="20"/>
+      <c r="F263" s="20">
         <v>45007918</v>
       </c>
-      <c r="G263" s="22">
+      <c r="G263" s="23">
         <v>46083</v>
       </c>
-      <c r="H263" s="19">
-        <v>2</v>
-      </c>
-      <c r="I263" s="19"/>
-      <c r="J263" s="19"/>
+      <c r="H263" s="20">
+        <v>2</v>
+      </c>
+      <c r="I263" s="20"/>
+      <c r="J263" s="20"/>
     </row>
     <row r="264" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A264" s="20" t="s">
+      <c r="A264" s="21" t="s">
         <v>47</v>
       </c>
-      <c r="B264" s="19" t="s">
-        <v>4</v>
-      </c>
-      <c r="C264" s="19">
+      <c r="B264" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="C264" s="20">
         <v>9991003</v>
       </c>
-      <c r="D264" s="19"/>
-      <c r="E264" s="19"/>
-      <c r="F264" s="19">
+      <c r="D264" s="20"/>
+      <c r="E264" s="20"/>
+      <c r="F264" s="20">
         <v>45007924</v>
       </c>
-      <c r="G264" s="22">
+      <c r="G264" s="23">
         <v>46144</v>
       </c>
-      <c r="H264" s="19">
-        <v>3</v>
-      </c>
-      <c r="I264" s="19"/>
-      <c r="J264" s="19"/>
+      <c r="H264" s="20">
+        <v>3</v>
+      </c>
+      <c r="I264" s="20"/>
+      <c r="J264" s="20"/>
     </row>
     <row r="265" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A265" s="20" t="s">
+      <c r="A265" s="21" t="s">
         <v>47</v>
       </c>
-      <c r="B265" s="19" t="s">
-        <v>4</v>
-      </c>
-      <c r="C265" s="19">
+      <c r="B265" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="C265" s="20">
         <v>9991003</v>
       </c>
-      <c r="D265" s="19"/>
-      <c r="E265" s="19"/>
-      <c r="F265" s="19">
+      <c r="D265" s="20"/>
+      <c r="E265" s="20"/>
+      <c r="F265" s="20">
         <v>45008089</v>
       </c>
-      <c r="G265" s="22">
+      <c r="G265" s="23">
         <v>46026</v>
       </c>
-      <c r="H265" s="19">
-        <v>1</v>
-      </c>
-      <c r="I265" s="19"/>
-      <c r="J265" s="19"/>
+      <c r="H265" s="20">
+        <v>1</v>
+      </c>
+      <c r="I265" s="20"/>
+      <c r="J265" s="20"/>
     </row>
     <row r="266" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A266" s="21" t="s">
+      <c r="A266" s="22" t="s">
         <v>45</v>
       </c>
-      <c r="B266" s="21" t="s">
-        <v>4</v>
-      </c>
-      <c r="C266" s="21">
+      <c r="B266" s="22" t="s">
+        <v>4</v>
+      </c>
+      <c r="C266" s="22">
         <v>9991003</v>
       </c>
-      <c r="D266" s="21"/>
-      <c r="E266" s="21">
+      <c r="D266" s="22"/>
+      <c r="E266" s="22">
         <v>5</v>
       </c>
-      <c r="F266" s="21"/>
-      <c r="G266" s="21"/>
-      <c r="H266" s="21">
+      <c r="F266" s="22"/>
+      <c r="G266" s="22"/>
+      <c r="H266" s="22">
         <v>6</v>
       </c>
-      <c r="I266" s="21">
+      <c r="I266" s="22">
         <v>-1</v>
       </c>
-      <c r="J266" s="21"/>
+      <c r="J266" s="22"/>
     </row>
     <row r="267" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A267" s="7" t="s">
@@ -7294,100 +7401,100 @@
       <c r="J269" s="7"/>
     </row>
     <row r="270" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A270" s="20" t="s">
+      <c r="A270" s="21" t="s">
         <v>47</v>
       </c>
-      <c r="B270" s="19" t="s">
+      <c r="B270" s="20" t="s">
         <v>5</v>
       </c>
-      <c r="C270" s="19">
+      <c r="C270" s="20">
         <v>9991004</v>
       </c>
-      <c r="D270" s="19"/>
-      <c r="E270" s="19"/>
-      <c r="F270" s="19">
+      <c r="D270" s="20"/>
+      <c r="E270" s="20"/>
+      <c r="F270" s="20">
         <v>45007915</v>
       </c>
-      <c r="G270" s="22">
+      <c r="G270" s="23">
         <v>46055</v>
       </c>
-      <c r="H270" s="19">
-        <v>1</v>
-      </c>
-      <c r="I270" s="19"/>
-      <c r="J270" s="19"/>
+      <c r="H270" s="20">
+        <v>1</v>
+      </c>
+      <c r="I270" s="20"/>
+      <c r="J270" s="20"/>
     </row>
     <row r="271" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A271" s="20" t="s">
+      <c r="A271" s="21" t="s">
         <v>47</v>
       </c>
-      <c r="B271" s="19" t="s">
+      <c r="B271" s="20" t="s">
         <v>5</v>
       </c>
-      <c r="C271" s="19">
+      <c r="C271" s="20">
         <v>9991004</v>
       </c>
-      <c r="D271" s="19"/>
-      <c r="E271" s="19"/>
-      <c r="F271" s="19">
+      <c r="D271" s="20"/>
+      <c r="E271" s="20"/>
+      <c r="F271" s="20">
         <v>45007987</v>
       </c>
-      <c r="G271" s="19" t="s">
+      <c r="G271" s="20" t="s">
         <v>171</v>
       </c>
-      <c r="H271" s="19">
-        <v>1</v>
-      </c>
-      <c r="I271" s="19"/>
-      <c r="J271" s="19"/>
+      <c r="H271" s="20">
+        <v>1</v>
+      </c>
+      <c r="I271" s="20"/>
+      <c r="J271" s="20"/>
     </row>
     <row r="272" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A272" s="20" t="s">
+      <c r="A272" s="21" t="s">
         <v>47</v>
       </c>
-      <c r="B272" s="19" t="s">
+      <c r="B272" s="20" t="s">
         <v>5</v>
       </c>
-      <c r="C272" s="19">
+      <c r="C272" s="20">
         <v>9991004</v>
       </c>
-      <c r="D272" s="19"/>
-      <c r="E272" s="19"/>
-      <c r="F272" s="19">
+      <c r="D272" s="20"/>
+      <c r="E272" s="20"/>
+      <c r="F272" s="20">
         <v>45008120</v>
       </c>
-      <c r="G272" s="19" t="s">
+      <c r="G272" s="20" t="s">
         <v>102</v>
       </c>
-      <c r="H272" s="19">
-        <v>1</v>
-      </c>
-      <c r="I272" s="19"/>
-      <c r="J272" s="19"/>
+      <c r="H272" s="20">
+        <v>1</v>
+      </c>
+      <c r="I272" s="20"/>
+      <c r="J272" s="20"/>
     </row>
     <row r="273" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A273" s="21" t="s">
+      <c r="A273" s="22" t="s">
         <v>45</v>
       </c>
-      <c r="B273" s="21" t="s">
+      <c r="B273" s="22" t="s">
         <v>5</v>
       </c>
-      <c r="C273" s="21">
+      <c r="C273" s="22">
         <v>9991004</v>
       </c>
-      <c r="D273" s="21"/>
-      <c r="E273" s="21">
-        <v>3</v>
-      </c>
-      <c r="F273" s="21"/>
-      <c r="G273" s="21"/>
-      <c r="H273" s="21">
-        <v>3</v>
-      </c>
-      <c r="I273" s="21">
+      <c r="D273" s="22"/>
+      <c r="E273" s="22">
+        <v>3</v>
+      </c>
+      <c r="F273" s="22"/>
+      <c r="G273" s="22"/>
+      <c r="H273" s="22">
+        <v>3</v>
+      </c>
+      <c r="I273" s="22">
         <v>0</v>
       </c>
-      <c r="J273" s="21"/>
+      <c r="J273" s="22"/>
     </row>
     <row r="274" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A274" s="7" t="s">
@@ -7399,7 +7506,7 @@
       <c r="C274" s="7">
         <v>9991006</v>
       </c>
-      <c r="D274" s="17">
+      <c r="D274" s="18">
         <v>46055</v>
       </c>
       <c r="E274" s="7">
@@ -7434,76 +7541,76 @@
       <c r="J275" s="8"/>
     </row>
     <row r="276" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A276" s="20" t="s">
+      <c r="A276" s="21" t="s">
         <v>47</v>
       </c>
-      <c r="B276" s="19" t="s">
+      <c r="B276" s="20" t="s">
         <v>7</v>
       </c>
-      <c r="C276" s="19">
+      <c r="C276" s="20">
         <v>9991006</v>
       </c>
-      <c r="D276" s="19"/>
-      <c r="E276" s="19"/>
-      <c r="F276" s="19">
+      <c r="D276" s="20"/>
+      <c r="E276" s="20"/>
+      <c r="F276" s="20">
         <v>45007903</v>
       </c>
-      <c r="G276" s="19" t="s">
+      <c r="G276" s="20" t="s">
         <v>61</v>
       </c>
-      <c r="H276" s="19">
-        <v>2</v>
-      </c>
-      <c r="I276" s="19"/>
-      <c r="J276" s="19"/>
+      <c r="H276" s="20">
+        <v>2</v>
+      </c>
+      <c r="I276" s="20"/>
+      <c r="J276" s="20"/>
     </row>
     <row r="277" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A277" s="20" t="s">
+      <c r="A277" s="21" t="s">
         <v>47</v>
       </c>
-      <c r="B277" s="19" t="s">
+      <c r="B277" s="20" t="s">
         <v>7</v>
       </c>
-      <c r="C277" s="19">
+      <c r="C277" s="20">
         <v>9991006</v>
       </c>
-      <c r="D277" s="19"/>
-      <c r="E277" s="19"/>
-      <c r="F277" s="19">
+      <c r="D277" s="20"/>
+      <c r="E277" s="20"/>
+      <c r="F277" s="20">
         <v>45007939</v>
       </c>
-      <c r="G277" s="22">
+      <c r="G277" s="23">
         <v>46297</v>
       </c>
-      <c r="H277" s="19">
-        <v>2</v>
-      </c>
-      <c r="I277" s="19"/>
-      <c r="J277" s="19"/>
+      <c r="H277" s="20">
+        <v>2</v>
+      </c>
+      <c r="I277" s="20"/>
+      <c r="J277" s="20"/>
     </row>
     <row r="278" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A278" s="21" t="s">
+      <c r="A278" s="22" t="s">
         <v>45</v>
       </c>
-      <c r="B278" s="21" t="s">
+      <c r="B278" s="22" t="s">
         <v>7</v>
       </c>
-      <c r="C278" s="21">
+      <c r="C278" s="22">
         <v>9991006</v>
       </c>
-      <c r="D278" s="21"/>
-      <c r="E278" s="21">
-        <v>4</v>
-      </c>
-      <c r="F278" s="21"/>
-      <c r="G278" s="21"/>
-      <c r="H278" s="21">
-        <v>4</v>
-      </c>
-      <c r="I278" s="21">
+      <c r="D278" s="22"/>
+      <c r="E278" s="22">
+        <v>4</v>
+      </c>
+      <c r="F278" s="22"/>
+      <c r="G278" s="22"/>
+      <c r="H278" s="22">
+        <v>4</v>
+      </c>
+      <c r="I278" s="22">
         <v>0</v>
       </c>
-      <c r="J278" s="21"/>
+      <c r="J278" s="22"/>
     </row>
     <row r="279" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A279" s="7" t="s">
@@ -7528,28 +7635,28 @@
       <c r="J279" s="7"/>
     </row>
     <row r="280" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A280" s="18" t="s">
+      <c r="A280" s="19" t="s">
         <v>45</v>
       </c>
-      <c r="B280" s="18" t="s">
+      <c r="B280" s="19" t="s">
         <v>8</v>
       </c>
-      <c r="C280" s="18">
+      <c r="C280" s="19">
         <v>9991007</v>
       </c>
-      <c r="D280" s="18"/>
-      <c r="E280" s="18">
-        <v>1</v>
-      </c>
-      <c r="F280" s="18"/>
-      <c r="G280" s="18"/>
-      <c r="H280" s="18">
+      <c r="D280" s="19"/>
+      <c r="E280" s="19">
+        <v>1</v>
+      </c>
+      <c r="F280" s="19"/>
+      <c r="G280" s="19"/>
+      <c r="H280" s="19">
         <v>0</v>
       </c>
-      <c r="I280" s="18">
-        <v>1</v>
-      </c>
-      <c r="J280" s="18">
+      <c r="I280" s="19">
+        <v>1</v>
+      </c>
+      <c r="J280" s="19">
         <v>1</v>
       </c>
     </row>
@@ -7585,7 +7692,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4B6828F3-55CB-4C96-B272-274D62A3543A}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B9D2C73A-C1B1-47B1-AE16-CD1EF42C812F}">
   <dimension ref="A1:G57"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -7632,726 +7739,726 @@
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A3" s="16" t="s">
+      <c r="A3" s="17" t="s">
         <v>15</v>
       </c>
-      <c r="B3" s="16"/>
-      <c r="C3" s="16"/>
-      <c r="D3" s="16"/>
-      <c r="E3" s="16"/>
-      <c r="F3" s="16"/>
-      <c r="G3" s="16"/>
+      <c r="B3" s="17"/>
+      <c r="C3" s="17"/>
+      <c r="D3" s="17"/>
+      <c r="E3" s="17"/>
+      <c r="F3" s="17"/>
+      <c r="G3" s="17"/>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A4" s="18" t="s">
-        <v>4</v>
-      </c>
-      <c r="B4" s="18">
+      <c r="A4" s="19" t="s">
+        <v>4</v>
+      </c>
+      <c r="B4" s="19">
         <v>9991003</v>
       </c>
-      <c r="C4" s="18">
-        <v>3</v>
-      </c>
-      <c r="D4" s="18">
+      <c r="C4" s="19">
+        <v>3</v>
+      </c>
+      <c r="D4" s="19">
         <v>0</v>
       </c>
-      <c r="E4" s="18">
-        <v>3</v>
-      </c>
-      <c r="F4" s="18" t="s">
+      <c r="E4" s="19">
+        <v>3</v>
+      </c>
+      <c r="F4" s="19" t="s">
         <v>177</v>
       </c>
-      <c r="G4" s="18">
+      <c r="G4" s="19">
         <v>3</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A6" s="16" t="s">
+      <c r="A6" s="17" t="s">
         <v>16</v>
       </c>
-      <c r="B6" s="16"/>
-      <c r="C6" s="16"/>
-      <c r="D6" s="16"/>
-      <c r="E6" s="16"/>
-      <c r="F6" s="16"/>
-      <c r="G6" s="16"/>
+      <c r="B6" s="17"/>
+      <c r="C6" s="17"/>
+      <c r="D6" s="17"/>
+      <c r="E6" s="17"/>
+      <c r="F6" s="17"/>
+      <c r="G6" s="17"/>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A7" s="18" t="s">
+      <c r="A7" s="19" t="s">
         <v>6</v>
       </c>
-      <c r="B7" s="18">
+      <c r="B7" s="19">
         <v>9991005</v>
       </c>
-      <c r="C7" s="18">
-        <v>2</v>
-      </c>
-      <c r="D7" s="18">
+      <c r="C7" s="19">
+        <v>2</v>
+      </c>
+      <c r="D7" s="19">
         <v>0</v>
       </c>
-      <c r="E7" s="18">
-        <v>2</v>
-      </c>
-      <c r="F7" s="18" t="s">
+      <c r="E7" s="19">
+        <v>2</v>
+      </c>
+      <c r="F7" s="19" t="s">
         <v>57</v>
       </c>
-      <c r="G7" s="18">
+      <c r="G7" s="19">
         <v>2</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A9" s="16" t="s">
+      <c r="A9" s="17" t="s">
         <v>17</v>
       </c>
-      <c r="B9" s="16"/>
-      <c r="C9" s="16"/>
-      <c r="D9" s="16"/>
-      <c r="E9" s="16"/>
-      <c r="F9" s="16"/>
-      <c r="G9" s="16"/>
+      <c r="B9" s="17"/>
+      <c r="C9" s="17"/>
+      <c r="D9" s="17"/>
+      <c r="E9" s="17"/>
+      <c r="F9" s="17"/>
+      <c r="G9" s="17"/>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A10" s="18" t="s">
-        <v>3</v>
-      </c>
-      <c r="B10" s="18">
+      <c r="A10" s="19" t="s">
+        <v>3</v>
+      </c>
+      <c r="B10" s="19">
         <v>9991002</v>
       </c>
-      <c r="C10" s="18">
-        <v>2</v>
-      </c>
-      <c r="D10" s="18">
+      <c r="C10" s="19">
+        <v>2</v>
+      </c>
+      <c r="D10" s="19">
         <v>0</v>
       </c>
-      <c r="E10" s="18">
-        <v>2</v>
-      </c>
-      <c r="F10" s="18" t="s">
+      <c r="E10" s="19">
+        <v>2</v>
+      </c>
+      <c r="F10" s="19" t="s">
         <v>63</v>
       </c>
-      <c r="G10" s="18">
+      <c r="G10" s="19">
         <v>2</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A11" s="18" t="s">
-        <v>4</v>
-      </c>
-      <c r="B11" s="18">
+      <c r="A11" s="19" t="s">
+        <v>4</v>
+      </c>
+      <c r="B11" s="19">
         <v>9991003</v>
       </c>
-      <c r="C11" s="18">
-        <v>4</v>
-      </c>
-      <c r="D11" s="18">
-        <v>2</v>
-      </c>
-      <c r="E11" s="18">
-        <v>2</v>
-      </c>
-      <c r="F11" s="18" t="s">
+      <c r="C11" s="19">
+        <v>4</v>
+      </c>
+      <c r="D11" s="19">
+        <v>2</v>
+      </c>
+      <c r="E11" s="19">
+        <v>2</v>
+      </c>
+      <c r="F11" s="19" t="s">
         <v>178</v>
       </c>
-      <c r="G11" s="18">
+      <c r="G11" s="19">
         <v>2</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A12" s="18" t="s">
+      <c r="A12" s="19" t="s">
         <v>6</v>
       </c>
-      <c r="B12" s="18">
+      <c r="B12" s="19">
         <v>9991005</v>
       </c>
-      <c r="C12" s="18">
-        <v>4</v>
-      </c>
-      <c r="D12" s="18">
-        <v>3</v>
-      </c>
-      <c r="E12" s="18">
-        <v>1</v>
-      </c>
-      <c r="F12" s="18" t="s">
+      <c r="C12" s="19">
+        <v>4</v>
+      </c>
+      <c r="D12" s="19">
+        <v>3</v>
+      </c>
+      <c r="E12" s="19">
+        <v>1</v>
+      </c>
+      <c r="F12" s="19" t="s">
         <v>179</v>
       </c>
-      <c r="G12" s="18">
+      <c r="G12" s="19">
         <v>1</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A13" s="18" t="s">
+      <c r="A13" s="19" t="s">
         <v>8</v>
       </c>
-      <c r="B13" s="18">
+      <c r="B13" s="19">
         <v>9991007</v>
       </c>
-      <c r="C13" s="18">
-        <v>1</v>
-      </c>
-      <c r="D13" s="18">
+      <c r="C13" s="19">
+        <v>1</v>
+      </c>
+      <c r="D13" s="19">
         <v>0</v>
       </c>
-      <c r="E13" s="18">
-        <v>1</v>
-      </c>
-      <c r="F13" s="18" t="s">
+      <c r="E13" s="19">
+        <v>1</v>
+      </c>
+      <c r="F13" s="19" t="s">
         <v>67</v>
       </c>
-      <c r="G13" s="18">
+      <c r="G13" s="19">
         <v>1</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A15" s="16" t="s">
+      <c r="A15" s="17" t="s">
         <v>18</v>
       </c>
-      <c r="B15" s="16"/>
-      <c r="C15" s="16"/>
-      <c r="D15" s="16"/>
-      <c r="E15" s="16"/>
-      <c r="F15" s="16"/>
-      <c r="G15" s="16"/>
+      <c r="B15" s="17"/>
+      <c r="C15" s="17"/>
+      <c r="D15" s="17"/>
+      <c r="E15" s="17"/>
+      <c r="F15" s="17"/>
+      <c r="G15" s="17"/>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A16" s="18" t="s">
-        <v>3</v>
-      </c>
-      <c r="B16" s="18">
+      <c r="A16" s="19" t="s">
+        <v>3</v>
+      </c>
+      <c r="B16" s="19">
         <v>9991002</v>
       </c>
-      <c r="C16" s="18">
-        <v>4</v>
-      </c>
-      <c r="D16" s="18">
-        <v>3</v>
-      </c>
-      <c r="E16" s="18">
-        <v>1</v>
-      </c>
-      <c r="F16" s="18" t="s">
+      <c r="C16" s="19">
+        <v>4</v>
+      </c>
+      <c r="D16" s="19">
+        <v>3</v>
+      </c>
+      <c r="E16" s="19">
+        <v>1</v>
+      </c>
+      <c r="F16" s="19" t="s">
         <v>180</v>
       </c>
-      <c r="G16" s="18">
+      <c r="G16" s="19">
         <v>1</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A17" s="18" t="s">
-        <v>4</v>
-      </c>
-      <c r="B17" s="18">
+      <c r="A17" s="19" t="s">
+        <v>4</v>
+      </c>
+      <c r="B17" s="19">
         <v>9991003</v>
       </c>
-      <c r="C17" s="18">
+      <c r="C17" s="19">
         <v>9</v>
       </c>
-      <c r="D17" s="18">
+      <c r="D17" s="19">
         <v>8</v>
       </c>
-      <c r="E17" s="18">
-        <v>1</v>
-      </c>
-      <c r="F17" s="18" t="s">
+      <c r="E17" s="19">
+        <v>1</v>
+      </c>
+      <c r="F17" s="19" t="s">
         <v>181</v>
       </c>
-      <c r="G17" s="18">
+      <c r="G17" s="19">
         <v>1</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A19" s="16" t="s">
+      <c r="A19" s="17" t="s">
         <v>19</v>
       </c>
-      <c r="B19" s="16"/>
-      <c r="C19" s="16"/>
-      <c r="D19" s="16"/>
-      <c r="E19" s="16"/>
-      <c r="F19" s="16"/>
-      <c r="G19" s="16"/>
+      <c r="B19" s="17"/>
+      <c r="C19" s="17"/>
+      <c r="D19" s="17"/>
+      <c r="E19" s="17"/>
+      <c r="F19" s="17"/>
+      <c r="G19" s="17"/>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A20" s="18" t="s">
+      <c r="A20" s="19" t="s">
         <v>5</v>
       </c>
-      <c r="B20" s="18">
+      <c r="B20" s="19">
         <v>9991004</v>
       </c>
-      <c r="C20" s="18">
-        <v>4</v>
-      </c>
-      <c r="D20" s="18">
-        <v>2</v>
-      </c>
-      <c r="E20" s="18">
-        <v>2</v>
-      </c>
-      <c r="F20" s="18" t="s">
+      <c r="C20" s="19">
+        <v>4</v>
+      </c>
+      <c r="D20" s="19">
+        <v>2</v>
+      </c>
+      <c r="E20" s="19">
+        <v>2</v>
+      </c>
+      <c r="F20" s="19" t="s">
         <v>182</v>
       </c>
-      <c r="G20" s="18">
+      <c r="G20" s="19">
         <v>3</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A21" s="18" t="s">
+      <c r="A21" s="19" t="s">
         <v>8</v>
       </c>
-      <c r="B21" s="18">
+      <c r="B21" s="19">
         <v>9991007</v>
       </c>
-      <c r="C21" s="18">
+      <c r="C21" s="19">
         <v>6</v>
       </c>
-      <c r="D21" s="18">
+      <c r="D21" s="19">
         <v>0</v>
       </c>
-      <c r="E21" s="18">
+      <c r="E21" s="19">
         <v>6</v>
       </c>
-      <c r="F21" s="18" t="s">
+      <c r="F21" s="19" t="s">
         <v>183</v>
       </c>
-      <c r="G21" s="18">
+      <c r="G21" s="19">
         <v>6</v>
       </c>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A23" s="16" t="s">
+      <c r="A23" s="17" t="s">
         <v>110</v>
       </c>
-      <c r="B23" s="16"/>
-      <c r="C23" s="16"/>
-      <c r="D23" s="16"/>
-      <c r="E23" s="16"/>
-      <c r="F23" s="16"/>
-      <c r="G23" s="16"/>
+      <c r="B23" s="17"/>
+      <c r="C23" s="17"/>
+      <c r="D23" s="17"/>
+      <c r="E23" s="17"/>
+      <c r="F23" s="17"/>
+      <c r="G23" s="17"/>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A24" s="18" t="s">
+      <c r="A24" s="19" t="s">
         <v>7</v>
       </c>
-      <c r="B24" s="18">
+      <c r="B24" s="19">
         <v>9991006</v>
       </c>
-      <c r="C24" s="18">
-        <v>1</v>
-      </c>
-      <c r="D24" s="18">
+      <c r="C24" s="19">
+        <v>1</v>
+      </c>
+      <c r="D24" s="19">
         <v>0</v>
       </c>
-      <c r="E24" s="18">
-        <v>1</v>
-      </c>
-      <c r="F24" s="18" t="s">
+      <c r="E24" s="19">
+        <v>1</v>
+      </c>
+      <c r="F24" s="19" t="s">
         <v>115</v>
       </c>
-      <c r="G24" s="18"/>
+      <c r="G24" s="19"/>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A26" s="16" t="s">
+      <c r="A26" s="17" t="s">
         <v>20</v>
       </c>
-      <c r="B26" s="16"/>
-      <c r="C26" s="16"/>
-      <c r="D26" s="16"/>
-      <c r="E26" s="16"/>
-      <c r="F26" s="16"/>
-      <c r="G26" s="16"/>
+      <c r="B26" s="17"/>
+      <c r="C26" s="17"/>
+      <c r="D26" s="17"/>
+      <c r="E26" s="17"/>
+      <c r="F26" s="17"/>
+      <c r="G26" s="17"/>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A27" s="18" t="s">
-        <v>4</v>
-      </c>
-      <c r="B27" s="18">
+      <c r="A27" s="19" t="s">
+        <v>4</v>
+      </c>
+      <c r="B27" s="19">
         <v>9991003</v>
       </c>
-      <c r="C27" s="18">
+      <c r="C27" s="19">
         <v>6</v>
       </c>
-      <c r="D27" s="18">
+      <c r="D27" s="19">
         <v>0</v>
       </c>
-      <c r="E27" s="18">
+      <c r="E27" s="19">
         <v>6</v>
       </c>
-      <c r="F27" s="18" t="s">
+      <c r="F27" s="19" t="s">
         <v>184</v>
       </c>
-      <c r="G27" s="18">
+      <c r="G27" s="19">
         <v>6</v>
       </c>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A29" s="16" t="s">
+      <c r="A29" s="17" t="s">
         <v>21</v>
       </c>
-      <c r="B29" s="16"/>
-      <c r="C29" s="16"/>
-      <c r="D29" s="16"/>
-      <c r="E29" s="16"/>
-      <c r="F29" s="16"/>
-      <c r="G29" s="16"/>
+      <c r="B29" s="17"/>
+      <c r="C29" s="17"/>
+      <c r="D29" s="17"/>
+      <c r="E29" s="17"/>
+      <c r="F29" s="17"/>
+      <c r="G29" s="17"/>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A30" s="18" t="s">
+      <c r="A30" s="19" t="s">
         <v>7</v>
       </c>
-      <c r="B30" s="18">
+      <c r="B30" s="19">
         <v>9991006</v>
       </c>
-      <c r="C30" s="18">
-        <v>1</v>
-      </c>
-      <c r="D30" s="18">
+      <c r="C30" s="19">
+        <v>1</v>
+      </c>
+      <c r="D30" s="19">
         <v>0</v>
       </c>
-      <c r="E30" s="18">
-        <v>1</v>
-      </c>
-      <c r="F30" s="18" t="s">
+      <c r="E30" s="19">
+        <v>1</v>
+      </c>
+      <c r="F30" s="19" t="s">
         <v>128</v>
       </c>
-      <c r="G30" s="18">
+      <c r="G30" s="19">
         <v>1</v>
       </c>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A32" s="16" t="s">
+      <c r="A32" s="17" t="s">
         <v>22</v>
       </c>
-      <c r="B32" s="16"/>
-      <c r="C32" s="16"/>
-      <c r="D32" s="16"/>
-      <c r="E32" s="16"/>
-      <c r="F32" s="16"/>
-      <c r="G32" s="16"/>
+      <c r="B32" s="17"/>
+      <c r="C32" s="17"/>
+      <c r="D32" s="17"/>
+      <c r="E32" s="17"/>
+      <c r="F32" s="17"/>
+      <c r="G32" s="17"/>
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A33" s="18" t="s">
-        <v>3</v>
-      </c>
-      <c r="B33" s="18">
+      <c r="A33" s="19" t="s">
+        <v>3</v>
+      </c>
+      <c r="B33" s="19">
         <v>9991002</v>
       </c>
-      <c r="C33" s="18">
-        <v>2</v>
-      </c>
-      <c r="D33" s="18">
-        <v>1</v>
-      </c>
-      <c r="E33" s="18">
-        <v>1</v>
-      </c>
-      <c r="F33" s="18" t="s">
+      <c r="C33" s="19">
+        <v>2</v>
+      </c>
+      <c r="D33" s="19">
+        <v>1</v>
+      </c>
+      <c r="E33" s="19">
+        <v>1</v>
+      </c>
+      <c r="F33" s="19" t="s">
         <v>185</v>
       </c>
-      <c r="G33" s="18">
+      <c r="G33" s="19">
         <v>1</v>
       </c>
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A35" s="16" t="s">
+      <c r="A35" s="17" t="s">
         <v>23</v>
       </c>
-      <c r="B35" s="16"/>
-      <c r="C35" s="16"/>
-      <c r="D35" s="16"/>
-      <c r="E35" s="16"/>
-      <c r="F35" s="16"/>
-      <c r="G35" s="16"/>
+      <c r="B35" s="17"/>
+      <c r="C35" s="17"/>
+      <c r="D35" s="17"/>
+      <c r="E35" s="17"/>
+      <c r="F35" s="17"/>
+      <c r="G35" s="17"/>
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A36" s="18" t="s">
-        <v>4</v>
-      </c>
-      <c r="B36" s="18">
+      <c r="A36" s="19" t="s">
+        <v>4</v>
+      </c>
+      <c r="B36" s="19">
         <v>9991003</v>
       </c>
-      <c r="C36" s="18">
+      <c r="C36" s="19">
         <v>6</v>
       </c>
-      <c r="D36" s="18">
+      <c r="D36" s="19">
         <v>5</v>
       </c>
-      <c r="E36" s="18">
-        <v>1</v>
-      </c>
-      <c r="F36" s="18" t="s">
+      <c r="E36" s="19">
+        <v>1</v>
+      </c>
+      <c r="F36" s="19" t="s">
         <v>186</v>
       </c>
-      <c r="G36" s="18">
+      <c r="G36" s="19">
         <v>1</v>
       </c>
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A38" s="16" t="s">
+      <c r="A38" s="17" t="s">
         <v>24</v>
       </c>
-      <c r="B38" s="16"/>
-      <c r="C38" s="16"/>
-      <c r="D38" s="16"/>
-      <c r="E38" s="16"/>
-      <c r="F38" s="16"/>
-      <c r="G38" s="16"/>
+      <c r="B38" s="17"/>
+      <c r="C38" s="17"/>
+      <c r="D38" s="17"/>
+      <c r="E38" s="17"/>
+      <c r="F38" s="17"/>
+      <c r="G38" s="17"/>
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A39" s="18" t="s">
-        <v>2</v>
-      </c>
-      <c r="B39" s="18">
+      <c r="A39" s="19" t="s">
+        <v>2</v>
+      </c>
+      <c r="B39" s="19">
         <v>9991001</v>
       </c>
-      <c r="C39" s="18">
-        <v>2</v>
-      </c>
-      <c r="D39" s="18">
+      <c r="C39" s="19">
+        <v>2</v>
+      </c>
+      <c r="D39" s="19">
         <v>0</v>
       </c>
-      <c r="E39" s="18">
-        <v>2</v>
-      </c>
-      <c r="F39" s="18" t="s">
+      <c r="E39" s="19">
+        <v>2</v>
+      </c>
+      <c r="F39" s="19" t="s">
         <v>145</v>
       </c>
-      <c r="G39" s="18">
+      <c r="G39" s="19">
         <v>2</v>
       </c>
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A40" s="18" t="s">
-        <v>4</v>
-      </c>
-      <c r="B40" s="18">
+      <c r="A40" s="19" t="s">
+        <v>4</v>
+      </c>
+      <c r="B40" s="19">
         <v>9991003</v>
       </c>
-      <c r="C40" s="18">
-        <v>2</v>
-      </c>
-      <c r="D40" s="18">
+      <c r="C40" s="19">
+        <v>2</v>
+      </c>
+      <c r="D40" s="19">
         <v>0</v>
       </c>
-      <c r="E40" s="18">
-        <v>2</v>
-      </c>
-      <c r="F40" s="18" t="s">
+      <c r="E40" s="19">
+        <v>2</v>
+      </c>
+      <c r="F40" s="19" t="s">
         <v>146</v>
       </c>
-      <c r="G40" s="18">
+      <c r="G40" s="19">
         <v>2</v>
       </c>
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A41" s="18" t="s">
+      <c r="A41" s="19" t="s">
         <v>5</v>
       </c>
-      <c r="B41" s="18">
+      <c r="B41" s="19">
         <v>9991004</v>
       </c>
-      <c r="C41" s="18">
-        <v>3</v>
-      </c>
-      <c r="D41" s="18">
-        <v>2</v>
-      </c>
-      <c r="E41" s="18">
-        <v>1</v>
-      </c>
-      <c r="F41" s="18" t="s">
+      <c r="C41" s="19">
+        <v>3</v>
+      </c>
+      <c r="D41" s="19">
+        <v>2</v>
+      </c>
+      <c r="E41" s="19">
+        <v>1</v>
+      </c>
+      <c r="F41" s="19" t="s">
         <v>187</v>
       </c>
-      <c r="G41" s="18">
+      <c r="G41" s="19">
         <v>1</v>
       </c>
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A42" s="18" t="s">
+      <c r="A42" s="19" t="s">
         <v>6</v>
       </c>
-      <c r="B42" s="18">
+      <c r="B42" s="19">
         <v>9991005</v>
       </c>
-      <c r="C42" s="18">
-        <v>3</v>
-      </c>
-      <c r="D42" s="18">
+      <c r="C42" s="19">
+        <v>3</v>
+      </c>
+      <c r="D42" s="19">
         <v>0</v>
       </c>
-      <c r="E42" s="18">
-        <v>3</v>
-      </c>
-      <c r="F42" s="18" t="s">
+      <c r="E42" s="19">
+        <v>3</v>
+      </c>
+      <c r="F42" s="19" t="s">
         <v>150</v>
       </c>
-      <c r="G42" s="18">
+      <c r="G42" s="19">
         <v>3</v>
       </c>
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A44" s="16" t="s">
+      <c r="A44" s="17" t="s">
         <v>25</v>
       </c>
-      <c r="B44" s="16"/>
-      <c r="C44" s="16"/>
-      <c r="D44" s="16"/>
-      <c r="E44" s="16"/>
-      <c r="F44" s="16"/>
-      <c r="G44" s="16"/>
+      <c r="B44" s="17"/>
+      <c r="C44" s="17"/>
+      <c r="D44" s="17"/>
+      <c r="E44" s="17"/>
+      <c r="F44" s="17"/>
+      <c r="G44" s="17"/>
     </row>
     <row r="45" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A45" s="18" t="s">
+      <c r="A45" s="19" t="s">
         <v>8</v>
       </c>
-      <c r="B45" s="18">
+      <c r="B45" s="19">
         <v>9991007</v>
       </c>
-      <c r="C45" s="18">
-        <v>4</v>
-      </c>
-      <c r="D45" s="18">
+      <c r="C45" s="19">
+        <v>4</v>
+      </c>
+      <c r="D45" s="19">
         <v>0</v>
       </c>
-      <c r="E45" s="18">
-        <v>4</v>
-      </c>
-      <c r="F45" s="18" t="s">
+      <c r="E45" s="19">
+        <v>4</v>
+      </c>
+      <c r="F45" s="19" t="s">
         <v>153</v>
       </c>
-      <c r="G45" s="18">
+      <c r="G45" s="19">
         <v>4</v>
       </c>
     </row>
     <row r="47" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A47" s="16" t="s">
+      <c r="A47" s="17" t="s">
         <v>26</v>
       </c>
-      <c r="B47" s="16"/>
-      <c r="C47" s="16"/>
-      <c r="D47" s="16"/>
-      <c r="E47" s="16"/>
-      <c r="F47" s="16"/>
-      <c r="G47" s="16"/>
+      <c r="B47" s="17"/>
+      <c r="C47" s="17"/>
+      <c r="D47" s="17"/>
+      <c r="E47" s="17"/>
+      <c r="F47" s="17"/>
+      <c r="G47" s="17"/>
     </row>
     <row r="48" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A48" s="18" t="s">
+      <c r="A48" s="19" t="s">
         <v>8</v>
       </c>
-      <c r="B48" s="18">
+      <c r="B48" s="19">
         <v>9991007</v>
       </c>
-      <c r="C48" s="18">
-        <v>2</v>
-      </c>
-      <c r="D48" s="18">
+      <c r="C48" s="19">
+        <v>2</v>
+      </c>
+      <c r="D48" s="19">
         <v>0</v>
       </c>
-      <c r="E48" s="18">
-        <v>2</v>
-      </c>
-      <c r="F48" s="18" t="s">
+      <c r="E48" s="19">
+        <v>2</v>
+      </c>
+      <c r="F48" s="19" t="s">
         <v>161</v>
       </c>
-      <c r="G48" s="18"/>
+      <c r="G48" s="19"/>
     </row>
     <row r="50" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A50" s="16" t="s">
+      <c r="A50" s="17" t="s">
         <v>28</v>
       </c>
-      <c r="B50" s="16"/>
-      <c r="C50" s="16"/>
-      <c r="D50" s="16"/>
-      <c r="E50" s="16"/>
-      <c r="F50" s="16"/>
-      <c r="G50" s="16"/>
+      <c r="B50" s="17"/>
+      <c r="C50" s="17"/>
+      <c r="D50" s="17"/>
+      <c r="E50" s="17"/>
+      <c r="F50" s="17"/>
+      <c r="G50" s="17"/>
     </row>
     <row r="51" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A51" s="18" t="s">
-        <v>4</v>
-      </c>
-      <c r="B51" s="18">
+      <c r="A51" s="19" t="s">
+        <v>4</v>
+      </c>
+      <c r="B51" s="19">
         <v>9991003</v>
       </c>
-      <c r="C51" s="18">
-        <v>1</v>
-      </c>
-      <c r="D51" s="18">
+      <c r="C51" s="19">
+        <v>1</v>
+      </c>
+      <c r="D51" s="19">
         <v>0</v>
       </c>
-      <c r="E51" s="18">
-        <v>1</v>
-      </c>
-      <c r="F51" s="18" t="s">
+      <c r="E51" s="19">
+        <v>1</v>
+      </c>
+      <c r="F51" s="19" t="s">
         <v>162</v>
       </c>
-      <c r="G51" s="18">
+      <c r="G51" s="19">
         <v>1</v>
       </c>
     </row>
     <row r="53" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A53" s="16" t="s">
+      <c r="A53" s="17" t="s">
         <v>29</v>
       </c>
-      <c r="B53" s="16"/>
-      <c r="C53" s="16"/>
-      <c r="D53" s="16"/>
-      <c r="E53" s="16"/>
-      <c r="F53" s="16"/>
-      <c r="G53" s="16"/>
+      <c r="B53" s="17"/>
+      <c r="C53" s="17"/>
+      <c r="D53" s="17"/>
+      <c r="E53" s="17"/>
+      <c r="F53" s="17"/>
+      <c r="G53" s="17"/>
     </row>
     <row r="54" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A54" s="18" t="s">
-        <v>4</v>
-      </c>
-      <c r="B54" s="18">
+      <c r="A54" s="19" t="s">
+        <v>4</v>
+      </c>
+      <c r="B54" s="19">
         <v>9991003</v>
       </c>
-      <c r="C54" s="18">
-        <v>2</v>
-      </c>
-      <c r="D54" s="18">
-        <v>1</v>
-      </c>
-      <c r="E54" s="18">
-        <v>1</v>
-      </c>
-      <c r="F54" s="18" t="s">
+      <c r="C54" s="19">
+        <v>2</v>
+      </c>
+      <c r="D54" s="19">
+        <v>1</v>
+      </c>
+      <c r="E54" s="19">
+        <v>1</v>
+      </c>
+      <c r="F54" s="19" t="s">
         <v>188</v>
       </c>
-      <c r="G54" s="18">
+      <c r="G54" s="19">
         <v>1</v>
       </c>
     </row>
     <row r="56" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A56" s="16" t="s">
+      <c r="A56" s="17" t="s">
         <v>30</v>
       </c>
-      <c r="B56" s="16"/>
-      <c r="C56" s="16"/>
-      <c r="D56" s="16"/>
-      <c r="E56" s="16"/>
-      <c r="F56" s="16"/>
-      <c r="G56" s="16"/>
+      <c r="B56" s="17"/>
+      <c r="C56" s="17"/>
+      <c r="D56" s="17"/>
+      <c r="E56" s="17"/>
+      <c r="F56" s="17"/>
+      <c r="G56" s="17"/>
     </row>
     <row r="57" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A57" s="18" t="s">
+      <c r="A57" s="19" t="s">
         <v>8</v>
       </c>
-      <c r="B57" s="18">
+      <c r="B57" s="19">
         <v>9991007</v>
       </c>
-      <c r="C57" s="18">
-        <v>1</v>
-      </c>
-      <c r="D57" s="18">
+      <c r="C57" s="19">
+        <v>1</v>
+      </c>
+      <c r="D57" s="19">
         <v>0</v>
       </c>
-      <c r="E57" s="18">
-        <v>1</v>
-      </c>
-      <c r="F57" s="18" t="s">
+      <c r="E57" s="19">
+        <v>1</v>
+      </c>
+      <c r="F57" s="19" t="s">
         <v>174</v>
       </c>
-      <c r="G57" s="18">
+      <c r="G57" s="19">
         <v>1</v>
       </c>
     </row>
